--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -420,7 +420,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:Z1076"/>
+  <dimension ref="A1:Z1077"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col outlineLevel="1" width="13" customWidth="1" min="22" max="26"/>
@@ -569,7 +569,7 @@
         <v>45098</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>44063</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>45182</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>43689</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44077</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45077</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44698</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44771</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>43647</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44789</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44312</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44335</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44779</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45076</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45303</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>43447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>43538</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44021</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44546</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44572</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>44614</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44662</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44727</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44819</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45006</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45076</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45099</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45201</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45205</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45244</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>43573</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44376</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44684</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>45092</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>43480</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44376</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44474</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44739</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44875</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44984</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44998</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45002</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45016</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45054</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45055</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45190</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45230</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45246</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>43369</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>43508</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43846</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43882</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44235</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44495</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44525</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44555</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44610</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44644</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44729</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44778</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44865</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44874</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44874</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44967</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45063</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45092</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45154</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45205</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45238</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45238</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45253</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43462</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43689</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43742</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>43959</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44007</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44043</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44090</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44455</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44509</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44511</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44606</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44607</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44712</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44728</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44796</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44874</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44874</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44875</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44938</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45013</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45021</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45021</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45048</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45063</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45070</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45070</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45075</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45078</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45107</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45121</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45135</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45238</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45246</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45246</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45246</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45323</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>43320</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>43327</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>43343</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>43343</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43355</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43360</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43376</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43381</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43384</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43398</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43410</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>43423</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43423</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43423</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43431</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43432</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>43432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>43448</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>43468</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>43469</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>43469</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43472</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>43472</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43473</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>43474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>43475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43476</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>43479</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43479</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43479</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>43479</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>43480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>43482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>43482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>43483</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43483</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43484</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43485</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43485</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43485</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43485</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43485</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43486</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43486</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43487</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43489</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43489</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>43489</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>43493</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>43493</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>43493</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>43494</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>43494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>43495</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>43500</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>43500</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>43502</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>43503</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43507</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43507</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>43508</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>43508</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>43509</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>43514</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>43515</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>43517</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>43518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>43518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>43518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>43518</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>43521</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>43522</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>43523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>43524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>43524</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43524</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>43529</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>43530</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>43531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43535</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43535</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43536</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43537</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>43537</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43538</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43545</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43545</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>43550</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>43560</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>43561</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>43562</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>43562</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>43573</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>43580</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>43590</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43590</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43591</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43605</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43607</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>43607</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43607</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>43612</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>43613</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>43613</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>43618</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>43623</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>43635</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>43642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>43642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>43647</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>43651</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>43651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>43651</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>43651</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>43651</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>43686</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>43692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>43699</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43699</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43706</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>43713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>43717</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>43723</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>43723</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>43739</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>43748</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>43755</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>43761</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>43767</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>43773</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>43782</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>43787</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>43790</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>43795</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>43797</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>43802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>43808</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>43810</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>43812</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>43817</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>43821</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>43821</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>43821</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>43838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>43844</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>43844</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>43850</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>43852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>43855</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>43864</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>43865</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>43867</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>43873</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>43882</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>43885</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>43885</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>43895</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>43901</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>43902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>43903</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>43906</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>43909</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>43909</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>43910</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>43920</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>43936</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>43969</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>43986</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44007</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44021</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44038</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44038</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44038</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44040</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44040</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44060</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44061</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44064</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44077</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44092</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44118</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44131</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44133</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44133</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44133</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44140</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44151</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44151</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44155</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44160</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44165</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44173</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44183</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44186</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44196</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44221</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44224</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44238</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44243</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>44257</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44279</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44287</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44295</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44295</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44295</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44298</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44308</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44308</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44308</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44308</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44309</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44327</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44330</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44336</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44337</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44341</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44354</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44354</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44361</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44365</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44365</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44368</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44371</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44376</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44376</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44376</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44376</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44377</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44406</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44420</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44425</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44425</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44425</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44425</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44450</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44460</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44461</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44461</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44462</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44466</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44467</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44476</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44476</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44482</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44488</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44491</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44491</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44496</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44498</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44501</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44501</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44504</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44504</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44511</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44512</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44512</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44512</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>44515</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44515</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44515</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44515</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44519</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44522</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44522</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44523</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>44525</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44531</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44533</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44546</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44546</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44548</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44550</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44552</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44560</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44560</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44560</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44572</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44573</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44576</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44577</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44578</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44578</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44586</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44586</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44587</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44588</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>44588</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44589</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44589</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44591</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44591</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44591</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44591</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44591</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44596</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44597</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44598</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44598</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44598</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44598</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44605</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>44607</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44607</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44608</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44608</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44609</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44610</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44613</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44613</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44613</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44614</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>44614</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44618</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44620</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44622</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44622</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44622</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44622</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44628</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>44631</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44631</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44635</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44635</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44635</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44636</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44643</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44643</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44643</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44644</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44649</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44651</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44651</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44651</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44651</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>44655</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44659</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44659</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44660</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44660</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44660</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44661</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44661</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44664</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44664</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>44664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44665</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>44665</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44667</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44669</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44669</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>44670</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44676</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44676</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44683</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44684</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44687</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44687</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44687</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44687</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44687</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44687</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44691</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44691</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44692</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44694</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>44699</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44706</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>44710</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44710</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44712</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44714</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44715</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44715</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44715</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44718</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44718</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44725</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44725</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44725</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>44726</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44726</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44728</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44729</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44732</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44732</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44734</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>44734</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>44734</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44734</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44739</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44739</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44739</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44746</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44755</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44757</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44768</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44768</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44768</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44770</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44770</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44771</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>44775</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44775</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44775</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>44783</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44783</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44783</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44795</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44796</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44796</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44803</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44805</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44809</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44810</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>44810</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>44813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44813</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44814</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44818</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44824</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44824</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44825</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44826</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44838</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44838</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>44839</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>44839</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44840</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44841</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>44841</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44848</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>44858</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44858</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44860</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>44861</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44872</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44874</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44874</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>44876</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>44890</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44896</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44896</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>44901</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44905</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44915</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>44916</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44923</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>44923</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44923</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44923</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44928</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44928</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44929</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44936</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>44938</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>44938</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44938</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44945</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>44945</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44948</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44949</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44950</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44953</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44953</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>44954</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44957</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44959</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44959</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44960</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>44963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44970</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>44970</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44970</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>44972</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>44972</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>44972</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44973</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>44973</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>44978</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44978</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44979</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44980</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44981</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>44981</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44985</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44987</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>44991</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44991</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44991</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44991</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>44991</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>44991</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44991</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44992</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>44992</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>44993</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44995</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44998</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44998</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44999</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45005</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45005</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45006</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45006</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45006</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45007</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45007</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45007</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45007</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>45007</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45012</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45012</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45014</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45014</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45015</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45015</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45015</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45019</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45027</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45028</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45030</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45033</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45033</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45033</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45034</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45040</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45040</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45040</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45040</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45041</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45042</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45042</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45042</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45042</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45042</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45044</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45044</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45044</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45044</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45045</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45045</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45045</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45045</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45045</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45047</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45047</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45048</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45048</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45048</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45048</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45051</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45051</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45054</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45054</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45054</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45054</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45056</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45057</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45058</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45058</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45058</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45058</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45063</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45063</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45063</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>45068</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45070</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45070</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45070</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45072</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45072</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45072</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45075</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45075</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45075</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45076</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45076</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45079</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45080</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45080</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45082</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45082</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45083</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45084</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45084</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45084</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45086</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45089</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45090</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45090</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45090</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45090</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45090</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45093</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45093</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45093</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>45096</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45096</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45097</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>45097</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45098</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45102</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45102</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45102</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>45102</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45102</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45102</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45102</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45106</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45106</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45107</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45107</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45110</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>45111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45112</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45112</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45112</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45112</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45112</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45114</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45114</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45114</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45114</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45114</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45114</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45114</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45114</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45117</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45119</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45119</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>45119</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45120</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45121</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>45121</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45122</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45123</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45123</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45124</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45135</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>45138</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45139</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45139</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45142</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45142</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45142</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45142</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45146</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45146</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45146</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45146</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45146</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45146</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45146</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45152</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45152</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45154</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45154</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45154</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45154</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45155</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>45156</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -60425,7 +60425,7 @@
         <v>45157</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45157</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>45157</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45160</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45160</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45161</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45161</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45162</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45162</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45162</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>45163</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45169</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45172</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>45173</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45174</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45175</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45176</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45176</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>45187</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>45187</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45189</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>45189</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45191</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45194</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45194</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45194</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45194</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45194</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45194</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45194</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45195</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45196</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
         <v>45196</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -62959,7 +62959,7 @@
         <v>45197</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45198</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45201</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45201</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>45202</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45202</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45202</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45203</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>45204</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>45205</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45208</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45209</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>45210</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45210</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45210</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45210</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45212</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>45212</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45212</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45213</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45213</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45213</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45215</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45215</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45215</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>45218</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>45225</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45225</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45225</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45225</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45225</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45225</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45226</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -64982,7 +64982,7 @@
         <v>45229</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45229</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45230</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>45230</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45230</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45230</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>45230</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45230</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45230</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45232</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>45233</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45233</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45233</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -65753,7 +65753,7 @@
         <v>45237</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>45238</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>45239</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45240</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45243</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45243</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45244</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45244</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45244</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45250</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45250</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45250</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45250</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45250</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -66819,7 +66819,7 @@
         <v>45252</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -66876,7 +66876,7 @@
         <v>45252</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -66933,7 +66933,7 @@
         <v>45252</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -66990,7 +66990,7 @@
         <v>45253</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67047,7 +67047,7 @@
         <v>45253</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45253</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67161,7 +67161,7 @@
         <v>45253</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67218,7 +67218,7 @@
         <v>45253</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45253</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>45257</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45258</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -67565,7 +67565,7 @@
         <v>45259</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>45260</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>45261</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -67736,7 +67736,7 @@
         <v>45264</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>45271</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>45282</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>45313</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45315</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68093,7 +68093,7 @@
         <v>45329</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>45329</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -68264,7 +68264,7 @@
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -68321,7 +68321,7 @@
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -68383,7 +68383,7 @@
         <v>45335</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>45335</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -68490,14 +68490,14 @@
     <row r="1072" ht="15" customHeight="1">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>A 6121-2024</t>
+          <t>A 6120-2024</t>
         </is>
       </c>
       <c r="B1072" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -68510,7 +68510,7 @@
         </is>
       </c>
       <c r="G1072" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1072" t="n">
         <v>0</v>
@@ -68547,14 +68547,14 @@
     <row r="1073" ht="15" customHeight="1">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>A 6143-2024</t>
+          <t>A 6121-2024</t>
         </is>
       </c>
       <c r="B1073" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -68567,7 +68567,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -68611,7 +68611,7 @@
         <v>45337</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -68668,7 +68668,7 @@
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -68715,17 +68715,17 @@
       </c>
       <c r="R1075" s="2" t="inlineStr"/>
     </row>
-    <row r="1076">
+    <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6120-2024</t>
+          <t>A 6143-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45338</v>
+        <v>45340</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -68771,6 +68771,63 @@
         <v>0</v>
       </c>
       <c r="R1076" s="2" t="inlineStr"/>
+    </row>
+    <row r="1077">
+      <c r="A1077" t="inlineStr">
+        <is>
+          <t>A 6418-2024</t>
+        </is>
+      </c>
+      <c r="B1077" s="1" t="n">
+        <v>45338</v>
+      </c>
+      <c r="C1077" s="1" t="n">
+        <v>45340</v>
+      </c>
+      <c r="D1077" t="inlineStr">
+        <is>
+          <t>UPPSALA LÄN</t>
+        </is>
+      </c>
+      <c r="E1077" t="inlineStr">
+        <is>
+          <t>ÖSTHAMMAR</t>
+        </is>
+      </c>
+      <c r="G1077" t="n">
+        <v>3.4</v>
+      </c>
+      <c r="H1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="I1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="J1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="K1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="L1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="M1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="N1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="O1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="P1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="Q1077" t="n">
+        <v>0</v>
+      </c>
+      <c r="R1077" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45098</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>44063</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>45182</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>43689</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44077</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45077</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44698</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44771</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>43647</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44789</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44312</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44335</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44779</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45076</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45303</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>43447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>43538</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44021</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44546</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44572</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>44614</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44662</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44727</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44819</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45006</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45076</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45099</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45201</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45205</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45244</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>43573</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44376</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44684</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>45092</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>43480</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44376</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44474</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44739</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44875</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44984</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44998</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45002</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45016</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45054</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45055</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45190</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45230</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45246</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>43369</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>43508</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43846</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43882</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44235</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44495</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44525</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44555</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44610</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44644</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44729</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44778</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44865</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44874</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44874</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44967</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45063</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45092</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45154</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45205</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45238</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45238</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45253</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43462</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43689</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43742</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>43959</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44007</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44043</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44090</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44455</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44509</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44511</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44606</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44607</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44712</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44728</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44796</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44874</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44874</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44875</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44938</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45013</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45021</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45021</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45048</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45063</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45070</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45070</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45075</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45078</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45107</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45121</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45135</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45238</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45246</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45246</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45246</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45323</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>43320</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>43327</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>43343</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>43343</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43355</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43360</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43376</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43381</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43384</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43398</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43410</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>43423</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43423</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43423</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43431</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43432</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>43432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>43448</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>43468</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>43469</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>43469</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43472</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>43472</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43473</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>43474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>43475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43476</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>43479</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43479</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43479</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>43479</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>43480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>43482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>43482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>43483</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43483</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43484</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43485</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43485</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43485</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43485</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43485</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43486</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43486</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43487</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43489</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43489</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>43489</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>43493</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>43493</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>43493</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>43494</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>43494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>43495</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>43500</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>43500</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>43502</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>43503</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43507</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43507</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>43508</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>43508</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>43509</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>43514</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>43515</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>43517</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>43518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>43518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>43518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>43518</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>43521</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>43522</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>43523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>43524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>43524</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43524</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>43529</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>43530</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>43531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43535</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43535</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43536</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43537</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>43537</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43538</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43545</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43545</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>43550</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>43560</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>43561</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>43562</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>43562</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>43573</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>43580</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>43590</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43590</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43591</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43605</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43607</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>43607</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43607</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>43612</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>43613</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>43613</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>43618</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>43623</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>43635</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>43642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>43642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>43647</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>43651</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>43651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>43651</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>43651</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>43651</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>43686</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>43692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>43699</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43699</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43706</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>43713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>43717</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>43723</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>43723</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>43739</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>43748</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>43755</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>43761</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>43767</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>43773</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>43782</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>43787</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>43790</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>43795</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>43797</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>43802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>43808</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>43810</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>43812</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>43817</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>43821</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>43821</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>43821</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>43838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>43844</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>43844</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>43850</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>43852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>43855</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>43864</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>43865</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>43867</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>43873</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>43882</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>43885</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>43885</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>43895</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>43901</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>43902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>43903</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>43906</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>43909</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>43909</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>43910</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>43920</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>43936</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>43969</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>43986</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44007</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44021</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44038</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44038</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44038</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44040</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44040</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44060</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44061</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44064</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44077</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44092</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44118</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44131</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44133</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44133</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44133</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44140</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44151</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44151</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44155</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44160</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44165</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44173</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44183</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44186</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44196</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44221</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44224</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44238</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44243</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>44257</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44279</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44287</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44295</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44295</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44295</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44298</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44308</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44308</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44308</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44308</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44309</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44327</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44330</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44336</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44337</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44341</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44354</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44354</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44361</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44365</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44365</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44368</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44371</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44376</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44376</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44376</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44376</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44377</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44406</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44420</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44425</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44425</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44425</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44425</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44450</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44460</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44461</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44461</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44462</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44466</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44467</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44476</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44476</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44482</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44488</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44491</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44491</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44496</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44498</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44501</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44501</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44504</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44504</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44511</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44512</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44512</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44512</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>44515</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44515</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44515</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44515</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44519</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44522</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44522</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44523</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>44525</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44531</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44533</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44546</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44546</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44548</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44550</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44552</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44560</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44560</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44560</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44572</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44573</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44576</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44577</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44578</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44578</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44586</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44586</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44587</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44588</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>44588</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44589</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44589</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44591</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44591</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44591</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44591</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44591</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44596</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44597</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44598</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44598</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44598</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44598</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44605</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>44607</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44607</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44608</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44608</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44609</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44610</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44613</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44613</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44613</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44614</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>44614</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44618</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44620</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44622</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44622</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44622</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44622</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44628</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>44631</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44631</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44635</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44635</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44635</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44636</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44643</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44643</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44643</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44644</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44649</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44651</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44651</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44651</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44651</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>44655</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44659</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44659</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44660</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44660</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44660</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44661</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44661</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44664</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44664</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>44664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44665</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>44665</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44667</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44669</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44669</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>44670</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44676</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44676</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44683</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44684</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44687</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44687</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44687</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44687</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44687</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44687</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44691</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44691</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44692</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44694</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>44699</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44706</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>44710</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44710</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44712</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44714</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44715</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44715</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44715</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44718</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44718</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44725</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44725</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44725</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>44726</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44726</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44728</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44729</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44732</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44732</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44734</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>44734</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>44734</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44734</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44739</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44739</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44739</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44746</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44755</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44757</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44768</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44768</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44768</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44770</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44770</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44771</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>44775</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44775</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44775</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>44783</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44783</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44783</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44795</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44796</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44796</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44803</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44805</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44809</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44810</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>44810</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>44813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44813</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44814</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44818</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44824</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44824</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44825</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44826</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44838</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44838</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>44839</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>44839</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44840</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44841</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>44841</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44848</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>44858</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44858</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44860</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>44861</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44872</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44874</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44874</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>44876</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>44890</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44896</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44896</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>44901</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44905</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44915</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>44916</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44923</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>44923</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44923</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44923</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44928</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44928</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44929</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44936</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>44938</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>44938</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44938</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44945</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>44945</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44948</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44949</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44950</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44953</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44953</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>44954</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44957</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44959</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44959</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44960</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>44963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44970</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>44970</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44970</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>44972</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>44972</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>44972</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44973</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>44973</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>44978</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44978</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44979</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44980</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44981</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>44981</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44985</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44987</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>44991</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44991</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44991</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44991</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>44991</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>44991</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44991</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44992</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>44992</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>44993</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44995</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44998</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44998</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44999</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45005</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45005</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45006</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45006</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45006</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45007</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45007</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45007</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45007</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>45007</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45012</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45012</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45014</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45014</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45015</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45015</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45015</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45019</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45027</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45028</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45030</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45033</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45033</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45033</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45034</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45040</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45040</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45040</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45040</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45041</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45042</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45042</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45042</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45042</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45042</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45044</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45044</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45044</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45044</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45045</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45045</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45045</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45045</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45045</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45047</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45047</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45048</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45048</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45048</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45048</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45051</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45051</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45054</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45054</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45054</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45054</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45056</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45057</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45058</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45058</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45058</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45058</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45063</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45063</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45063</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>45068</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45070</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45070</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45070</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45072</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45072</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45072</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45075</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45075</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45075</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45076</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45076</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45079</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45080</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45080</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45082</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45082</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45083</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45084</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45084</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45084</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45086</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45089</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45090</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45090</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45090</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45090</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45090</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45093</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45093</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45093</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>45096</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45096</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45097</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>45097</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45098</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45102</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45102</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45102</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>45102</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45102</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45102</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45102</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45106</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45106</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45107</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45107</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45110</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>45111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45112</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45112</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45112</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45112</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45112</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45114</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45114</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45114</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45114</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45114</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45114</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45114</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45114</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45117</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45119</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45119</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>45119</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45120</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45121</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>45121</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45122</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45123</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45123</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45124</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45135</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>45138</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45139</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45139</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45142</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45142</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45142</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45142</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45146</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45146</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45146</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45146</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45146</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45146</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45146</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45152</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45152</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45154</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45154</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45154</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45154</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45155</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>45156</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -60425,7 +60425,7 @@
         <v>45157</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45157</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>45157</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45160</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45160</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45161</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45161</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45162</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45162</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45162</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>45163</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45169</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45172</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>45173</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45174</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45175</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45176</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45176</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>45187</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>45187</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45189</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>45189</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45191</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45194</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45194</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45194</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45194</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45194</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45194</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45194</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45195</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45196</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
         <v>45196</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -62959,7 +62959,7 @@
         <v>45197</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45198</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45201</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45201</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>45202</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45202</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45202</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45203</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>45204</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>45205</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45208</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45209</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>45210</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45210</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45210</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45210</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45212</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>45212</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45212</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45213</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45213</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45213</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45215</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45215</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45215</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>45218</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>45225</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45225</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45225</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45225</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45225</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45225</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45226</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -64982,7 +64982,7 @@
         <v>45229</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45229</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45230</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>45230</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45230</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45230</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>45230</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45230</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45230</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45232</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>45233</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45233</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45233</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -65753,7 +65753,7 @@
         <v>45237</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>45238</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>45239</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45240</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45243</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45243</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45244</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45244</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45244</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45250</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45250</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45250</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45250</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45250</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -66819,7 +66819,7 @@
         <v>45252</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -66876,7 +66876,7 @@
         <v>45252</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -66933,7 +66933,7 @@
         <v>45252</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -66990,7 +66990,7 @@
         <v>45253</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67047,7 +67047,7 @@
         <v>45253</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45253</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67161,7 +67161,7 @@
         <v>45253</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67218,7 +67218,7 @@
         <v>45253</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45253</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>45257</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45258</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -67565,7 +67565,7 @@
         <v>45259</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>45260</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>45261</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -67736,7 +67736,7 @@
         <v>45264</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>45271</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>45282</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>45313</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45315</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68086,14 +68086,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 4984-2024</t>
+          <t>A 5042-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68106,7 +68106,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -68143,14 +68143,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 5042-2024</t>
+          <t>A 4984-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68163,7 +68163,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -68207,7 +68207,7 @@
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -68257,14 +68257,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5198-2024</t>
+          <t>A 5161-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -68276,13 +68276,8 @@
           <t>ÖSTHAMMAR</t>
         </is>
       </c>
-      <c r="F1068" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G1068" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -68319,14 +68314,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5161-2024</t>
+          <t>A 5198-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -68338,8 +68333,13 @@
           <t>ÖSTHAMMAR</t>
         </is>
       </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G1069" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -68383,7 +68383,7 @@
         <v>45335</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>45335</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -68490,14 +68490,14 @@
     <row r="1072" ht="15" customHeight="1">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>A 6121-2024</t>
+          <t>A 6120-2024</t>
         </is>
       </c>
       <c r="B1072" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -68510,7 +68510,7 @@
         </is>
       </c>
       <c r="G1072" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1072" t="n">
         <v>0</v>
@@ -68547,14 +68547,14 @@
     <row r="1073" ht="15" customHeight="1">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>A 6120-2024</t>
+          <t>A 6121-2024</t>
         </is>
       </c>
       <c r="B1073" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -68567,7 +68567,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -68611,7 +68611,7 @@
         <v>45337</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -68668,7 +68668,7 @@
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -68725,7 +68725,7 @@
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -68782,7 +68782,7 @@
         <v>45338</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -68839,7 +68839,7 @@
         <v>45341</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -68896,7 +68896,7 @@
         <v>45341</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45343</v>
+        <v>45344</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45098</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>44063</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>45182</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>43689</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44077</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45077</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44698</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44771</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>43647</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44789</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44312</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44335</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44779</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45076</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45303</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>43447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>43538</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44021</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44546</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44572</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>44614</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44662</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44727</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44819</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45006</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45076</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45099</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45201</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45205</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45244</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>43573</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44376</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44684</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>45092</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>43480</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44376</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44474</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44739</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44875</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44984</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44998</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45002</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45016</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45054</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45055</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45190</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45230</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45246</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>43369</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>43508</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43846</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43882</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44235</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44495</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44525</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44555</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44610</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44644</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44729</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44778</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44865</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44874</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44874</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44967</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45063</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45092</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45154</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45205</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45238</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45238</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45253</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43462</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43689</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43742</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>43959</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44007</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44043</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44090</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44455</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44509</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44511</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44606</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44607</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44712</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44728</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44796</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44874</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44874</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44875</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44938</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45013</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45021</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45021</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45048</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45063</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45070</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45070</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45075</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45078</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45107</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45121</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45135</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45238</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45246</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45246</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45246</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45323</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>43320</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>43327</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>43343</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>43343</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43355</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43360</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43376</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43381</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43384</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43398</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43410</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>43423</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43423</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43423</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43431</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43432</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>43432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>43448</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>43468</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>43469</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>43469</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43472</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>43472</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43473</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>43474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>43475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43476</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>43479</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43479</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43479</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>43479</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>43480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>43482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>43482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>43483</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43483</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43484</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43485</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43485</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43485</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43485</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43485</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43486</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43486</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43487</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43489</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43489</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>43489</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>43493</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>43493</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>43493</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>43494</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>43494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>43495</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>43500</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>43500</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>43502</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>43503</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43507</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43507</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>43508</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>43508</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>43509</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>43514</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>43515</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>43517</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>43518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>43518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>43518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>43518</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>43521</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>43522</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>43523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>43524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>43524</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43524</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>43529</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>43530</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>43531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43535</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43535</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43536</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43537</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>43537</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43538</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43545</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43545</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>43550</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>43560</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>43561</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>43562</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>43562</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>43573</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>43580</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>43590</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43590</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43591</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43605</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43607</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>43607</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43607</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>43612</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>43613</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>43613</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>43618</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>43623</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>43635</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>43642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>43642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>43647</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>43651</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>43651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>43651</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>43651</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>43651</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>43686</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>43692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>43699</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43699</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43706</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>43713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>43717</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>43723</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>43723</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>43739</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>43748</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>43755</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>43761</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>43767</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>43773</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>43782</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>43787</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>43790</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>43795</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>43797</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>43802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>43808</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>43810</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>43812</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>43817</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>43821</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>43821</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>43821</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>43838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>43844</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>43844</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>43850</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>43852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>43855</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>43864</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>43865</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>43867</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>43873</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>43882</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>43885</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>43885</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>43895</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>43901</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>43902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>43903</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>43906</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>43909</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>43909</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>43910</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>43920</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>43936</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>43969</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>43986</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44007</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44021</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44038</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44038</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44038</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44040</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44040</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44060</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44061</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44064</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44077</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44092</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44118</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44131</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44133</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44133</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44133</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44140</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44151</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44151</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44155</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44160</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44165</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44173</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44183</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44186</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44196</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44221</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44224</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44238</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44243</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>44257</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44279</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44287</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44295</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44295</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44295</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44298</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44308</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44308</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44308</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44308</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44309</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44327</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44330</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44336</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44337</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44341</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44354</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44354</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44361</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44365</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44365</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44368</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44371</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44376</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44376</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44376</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44376</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44377</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44406</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44420</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44425</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44425</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44425</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44425</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44450</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44460</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44461</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44461</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44462</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44466</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44467</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44476</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44476</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44482</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44488</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44491</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44491</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44496</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44498</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44501</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44501</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44504</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44504</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44511</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44512</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44512</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44512</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>44515</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44515</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44515</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44515</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44519</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44522</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44522</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44523</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>44525</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44531</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44533</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44546</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44546</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44548</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44550</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44552</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44560</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44560</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44560</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44572</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44573</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44576</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44577</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44578</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44578</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44586</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44586</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44587</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44588</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>44588</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44589</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44589</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44591</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44591</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44591</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44591</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44591</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44596</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44597</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44598</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44598</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44598</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44598</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44605</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>44607</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44607</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44608</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44608</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44609</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44610</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44613</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44613</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44613</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44614</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>44614</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44618</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44620</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44622</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44622</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44622</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44622</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44628</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>44631</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44631</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44635</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44635</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44635</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44636</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44643</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44643</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44643</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44644</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44649</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44651</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44651</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44651</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44651</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>44655</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44659</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44659</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44660</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44660</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44660</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44661</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44661</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44664</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44664</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>44664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44665</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>44665</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44667</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44669</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44669</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>44670</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44676</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44676</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44683</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44684</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44687</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44687</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44687</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44687</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44687</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44687</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44691</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44691</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44692</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44694</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>44699</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44706</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>44710</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44710</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44712</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44714</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44715</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44715</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44715</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44718</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44718</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44725</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44725</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44725</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>44726</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44726</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44728</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44729</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44732</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44732</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44734</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>44734</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>44734</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44734</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44739</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44739</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44739</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44746</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44755</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44757</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44768</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44768</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44768</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44770</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44770</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44771</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>44775</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44775</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44775</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>44783</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44783</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44783</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44795</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44796</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44796</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44803</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44805</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44809</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44810</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>44810</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>44813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44813</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44814</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44818</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44824</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44824</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44825</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44826</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44838</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44838</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>44839</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>44839</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44840</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44841</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>44841</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44848</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>44858</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44858</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44860</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>44861</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44872</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44874</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44874</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>44876</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>44890</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44896</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44896</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>44901</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44905</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44915</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>44916</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44923</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>44923</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44923</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44923</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44928</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44928</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44929</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44936</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>44938</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>44938</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44938</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44945</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>44945</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44948</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44949</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44950</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44953</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44953</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>44954</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44957</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44959</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44959</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44960</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>44963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44970</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>44970</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44970</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>44972</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>44972</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>44972</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44973</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>44973</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>44978</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44978</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44979</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44980</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44981</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>44981</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44985</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44987</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>44991</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44991</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44991</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44991</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>44991</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>44991</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44991</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44992</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>44992</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>44993</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44995</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44998</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44998</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44999</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45005</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45005</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45006</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45006</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45006</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45007</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45007</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45007</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45007</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>45007</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45012</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45012</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45014</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45014</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45015</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45015</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45015</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45019</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45027</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45028</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45030</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45033</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45033</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45033</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45034</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45040</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45040</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45040</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45040</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45041</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45042</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45042</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45042</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45042</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45042</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45044</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45044</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45044</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45044</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45045</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45045</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45045</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45045</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45045</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45047</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45047</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45048</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45048</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45048</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45048</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45051</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45051</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45054</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45054</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45054</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45054</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45056</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45057</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45058</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45058</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45058</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45058</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45063</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45063</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45063</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>45068</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45070</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45070</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45070</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45072</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45072</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45072</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45075</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45075</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45075</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45076</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45076</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45079</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45080</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45080</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45082</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45082</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45083</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45084</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45084</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45084</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45086</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45089</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45090</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45090</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45090</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45090</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45090</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45093</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45093</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45093</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>45096</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45096</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45097</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>45097</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45098</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45102</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45102</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45102</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>45102</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45102</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45102</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45102</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45106</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45106</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45107</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45107</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45110</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>45111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45112</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45112</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45112</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45112</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45112</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45114</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45114</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45114</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45114</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45114</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45114</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45114</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45114</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45117</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45119</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45119</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>45119</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45120</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45121</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>45121</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45122</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45123</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45123</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45124</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45135</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>45138</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45139</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45139</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45142</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45142</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45142</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45142</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45146</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45146</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45146</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45146</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45146</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45146</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45146</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45152</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45152</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45154</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45154</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45154</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45154</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45155</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>45156</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -60425,7 +60425,7 @@
         <v>45157</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45157</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>45157</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45160</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45160</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45161</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45161</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45162</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45162</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45162</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>45163</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45169</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45172</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>45173</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45174</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45175</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45176</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45176</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>45187</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>45187</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45189</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>45189</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45191</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45194</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45194</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45194</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45194</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45194</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45194</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45194</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45195</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45196</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
         <v>45196</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -62959,7 +62959,7 @@
         <v>45197</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45198</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45201</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45201</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>45202</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45202</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45202</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45203</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>45204</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>45205</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45208</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45209</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>45210</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45210</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45210</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45210</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45212</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>45212</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45212</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45213</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45213</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45213</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45215</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45215</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45215</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>45218</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>45225</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45225</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45225</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45225</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45225</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45225</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45226</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -64982,7 +64982,7 @@
         <v>45229</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45229</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45230</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>45230</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45230</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45230</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>45230</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45230</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45230</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45232</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>45233</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45233</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45233</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -65753,7 +65753,7 @@
         <v>45237</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>45238</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>45239</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45240</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45243</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45243</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45244</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45244</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45244</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45250</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45250</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45250</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45250</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45250</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -66819,7 +66819,7 @@
         <v>45252</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -66876,7 +66876,7 @@
         <v>45252</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -66933,7 +66933,7 @@
         <v>45252</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -66990,7 +66990,7 @@
         <v>45253</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67047,7 +67047,7 @@
         <v>45253</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45253</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67161,7 +67161,7 @@
         <v>45253</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67218,7 +67218,7 @@
         <v>45253</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45253</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>45257</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45258</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -67565,7 +67565,7 @@
         <v>45259</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>45260</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>45261</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -67736,7 +67736,7 @@
         <v>45264</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>45271</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>45282</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>45313</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45315</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68093,7 +68093,7 @@
         <v>45329</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>45329</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68200,14 +68200,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5149-2024</t>
+          <t>A 5161-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -68220,7 +68220,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -68257,14 +68257,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5161-2024</t>
+          <t>A 5149-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -68277,7 +68277,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -68321,7 +68321,7 @@
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -68383,7 +68383,7 @@
         <v>45335</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>45335</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -68490,14 +68490,14 @@
     <row r="1072" ht="15" customHeight="1">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>A 6120-2024</t>
+          <t>A 6143-2024</t>
         </is>
       </c>
       <c r="B1072" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -68547,14 +68547,14 @@
     <row r="1073" ht="15" customHeight="1">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>A 6121-2024</t>
+          <t>A 6102-2024</t>
         </is>
       </c>
       <c r="B1073" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -68567,7 +68567,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -68604,14 +68604,14 @@
     <row r="1074" ht="15" customHeight="1">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>A 6143-2024</t>
+          <t>A 6106-2024</t>
         </is>
       </c>
       <c r="B1074" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -68624,7 +68624,7 @@
         </is>
       </c>
       <c r="G1074" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H1074" t="n">
         <v>0</v>
@@ -68661,14 +68661,14 @@
     <row r="1075" ht="15" customHeight="1">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>A 6102-2024</t>
+          <t>A 6120-2024</t>
         </is>
       </c>
       <c r="B1075" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="H1075" t="n">
         <v>0</v>
@@ -68718,14 +68718,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6106-2024</t>
+          <t>A 6121-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -68738,7 +68738,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -68782,7 +68782,7 @@
         <v>45338</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -68839,7 +68839,7 @@
         <v>45341</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -68896,7 +68896,7 @@
         <v>45341</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45344</v>
+        <v>45345</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45098</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>44063</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>45182</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>43689</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44077</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45077</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44698</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44771</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>43647</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44789</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44312</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44335</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44779</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45076</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45303</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>43447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>43538</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44021</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44546</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44572</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>44614</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44662</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44727</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44819</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45006</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45076</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45099</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45201</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45205</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45244</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>43573</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44376</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44684</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>45092</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>43480</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44376</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44474</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44739</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44875</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44984</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44998</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45002</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45016</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45054</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45055</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45190</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45230</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45246</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>43369</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>43508</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43846</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43882</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44235</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44495</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44525</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44555</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44610</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44644</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44729</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44778</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44865</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44874</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44874</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44967</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45063</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45092</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45154</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45205</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45238</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45238</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45253</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43462</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43689</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43742</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>43959</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44007</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44043</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44090</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44455</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44509</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44511</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44606</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44607</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44712</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44728</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44796</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44874</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44874</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44875</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44938</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45013</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45021</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45021</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45048</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45063</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45070</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45070</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45075</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45078</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45107</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45121</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45135</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45238</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45246</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45246</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45246</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45323</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>43320</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>43327</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>43343</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>43343</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43355</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43360</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43376</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43381</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43384</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43398</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43410</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>43423</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43423</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43423</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43431</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43432</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>43432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>43448</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>43468</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>43469</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>43469</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43472</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>43472</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43473</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>43474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>43475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43476</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>43479</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43479</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43479</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>43479</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>43480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>43482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>43482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>43483</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43483</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43484</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43485</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43485</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43485</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43485</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43485</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43486</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43486</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43487</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43489</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43489</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>43489</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>43493</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>43493</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>43493</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>43494</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>43494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>43495</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>43500</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>43500</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>43502</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>43503</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43507</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43507</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>43508</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>43508</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>43509</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>43514</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>43515</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>43517</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>43518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>43518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>43518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>43518</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>43521</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>43522</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>43523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>43524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>43524</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43524</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>43529</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>43530</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>43531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43535</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43535</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43536</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43537</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>43537</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43538</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43545</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43545</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>43550</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>43560</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>43561</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>43562</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>43562</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>43573</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>43580</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>43590</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43590</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43591</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43605</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43607</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>43607</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43607</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>43612</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>43613</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>43613</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>43618</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>43623</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>43635</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>43642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>43642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>43647</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>43651</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>43651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>43651</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>43651</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>43651</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>43686</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>43692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>43699</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43699</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43706</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>43713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>43717</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>43723</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>43723</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>43739</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>43748</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>43755</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>43761</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>43767</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>43773</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>43782</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>43787</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>43790</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>43795</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>43797</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>43802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>43808</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>43810</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>43812</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>43817</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>43821</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>43821</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>43821</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>43838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>43844</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>43844</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>43850</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>43852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>43855</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>43864</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>43865</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>43867</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>43873</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>43882</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>43885</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>43885</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>43895</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>43901</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>43902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>43903</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>43906</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>43909</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>43909</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>43910</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>43920</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>43936</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>43969</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>43986</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44007</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44021</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44038</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44038</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44038</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44040</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44040</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44060</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44061</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44064</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44077</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44092</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44118</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44131</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44133</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44133</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44133</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44140</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44151</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44151</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44155</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44160</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44165</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44173</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44183</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44186</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44196</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44221</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44224</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44238</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44243</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>44257</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44279</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44287</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44295</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44295</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44295</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44298</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44308</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44308</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44308</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44308</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44309</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44327</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44330</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44336</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44337</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44341</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44354</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44354</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44361</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44365</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44365</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44368</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44371</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44376</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44376</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44376</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44376</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44377</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44406</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44420</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44425</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44425</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44425</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44425</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44450</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44460</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44461</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44461</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44462</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44466</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44467</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44476</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44476</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44482</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44488</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44491</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44491</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44496</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44498</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44501</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44501</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44504</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44504</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44511</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44512</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44512</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44512</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>44515</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44515</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44515</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44515</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44519</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44522</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44522</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44523</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>44525</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44531</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44533</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44546</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44546</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44548</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44550</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44552</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44560</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44560</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44560</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44572</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44573</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44576</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44577</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44578</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44578</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44586</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44586</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44587</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44588</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>44588</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44589</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44589</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44591</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44591</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44591</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44591</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44591</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44596</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44597</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44598</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44598</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44598</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44598</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44605</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>44607</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44607</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44608</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44608</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44609</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44610</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44613</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44613</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44613</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44614</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>44614</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44618</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44620</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44622</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44622</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44622</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44622</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44628</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>44631</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44631</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44635</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44635</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44635</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44636</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44643</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44643</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44643</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44644</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44649</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44651</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44651</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44651</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44651</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>44655</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44659</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44659</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44660</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44660</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44660</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44661</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44661</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44664</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44664</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>44664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44665</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>44665</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44667</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44669</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44669</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>44670</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44676</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44676</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44683</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44684</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44687</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44687</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44687</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44687</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44687</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44687</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44691</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44691</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44692</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44694</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>44699</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44706</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>44710</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44710</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44712</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44714</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44715</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44715</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44715</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44718</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44718</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44725</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44725</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44725</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>44726</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44726</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44728</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44729</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44732</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44732</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44734</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>44734</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>44734</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44734</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44739</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44739</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44739</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44746</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44755</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44757</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44768</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44768</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44768</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44770</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44770</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44771</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>44775</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44775</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44775</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>44783</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44783</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44783</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44795</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44796</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44796</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44803</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44805</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44809</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44810</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>44810</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>44813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44813</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44814</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44818</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44824</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44824</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44825</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44826</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44838</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44838</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>44839</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>44839</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44840</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44841</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>44841</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44848</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>44858</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44858</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44860</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>44861</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44872</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44874</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44874</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>44876</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>44890</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44896</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44896</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>44901</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44905</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44915</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>44916</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44923</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>44923</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44923</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44923</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44928</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44928</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44929</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44936</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>44938</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>44938</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44938</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44945</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>44945</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44948</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44949</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44950</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44953</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44953</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>44954</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44957</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44959</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44959</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44960</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>44963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44970</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>44970</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44970</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>44972</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>44972</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>44972</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44973</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>44973</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>44978</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44978</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44979</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44980</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44981</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>44981</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44985</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44987</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>44991</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44991</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44991</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44991</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>44991</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>44991</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44991</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44992</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>44992</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>44993</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44995</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44998</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44998</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44999</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45005</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45005</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45006</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45006</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45006</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45007</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45007</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45007</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45007</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>45007</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45012</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45012</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45014</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45014</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45015</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45015</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45015</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45019</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45027</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45028</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45030</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45033</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45033</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45033</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45034</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45040</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45040</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45040</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45040</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45041</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45042</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45042</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45042</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45042</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45042</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45044</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45044</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45044</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45044</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45045</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45045</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45045</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45045</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45045</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45047</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45047</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45048</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45048</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45048</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45048</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45051</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45051</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45054</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45054</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45054</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45054</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45056</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45057</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45058</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45058</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45058</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45058</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45063</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45063</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45063</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>45068</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45070</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45070</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45070</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45072</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45072</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45072</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45075</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45075</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45075</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45076</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45076</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45079</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45080</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45080</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45082</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45082</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45083</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45084</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45084</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45084</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45086</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45089</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45090</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45090</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45090</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45090</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45090</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45093</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45093</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45093</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>45096</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45096</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45097</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>45097</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45098</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45102</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45102</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45102</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>45102</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45102</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45102</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45102</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45106</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45106</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45107</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45107</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45110</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>45111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45112</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45112</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45112</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45112</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45112</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45114</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45114</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45114</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45114</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45114</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45114</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45114</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45114</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45117</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45119</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45119</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>45119</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45120</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45121</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>45121</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45122</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45123</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45123</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45124</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45135</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>45138</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45139</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45139</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45142</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45142</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45142</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45142</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45146</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45146</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45146</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45146</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45146</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45146</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45146</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45152</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45152</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45154</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45154</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45154</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45154</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45155</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>45156</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -60425,7 +60425,7 @@
         <v>45157</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45157</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>45157</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45160</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45160</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45161</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45161</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45162</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45162</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45162</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>45163</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45169</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45172</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>45173</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45174</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45175</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45176</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45176</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>45187</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>45187</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45189</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>45189</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45191</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45194</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45194</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45194</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45194</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45194</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45194</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45194</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45195</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45196</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
         <v>45196</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -62959,7 +62959,7 @@
         <v>45197</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45198</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45201</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45201</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>45202</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45202</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45202</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45203</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>45204</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>45205</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45208</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45209</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>45210</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45210</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45210</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45210</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45212</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>45212</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45212</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45213</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45213</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45213</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45215</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45215</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45215</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>45218</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>45225</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45225</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45225</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45225</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45225</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45225</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45226</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -64982,7 +64982,7 @@
         <v>45229</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45229</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45230</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>45230</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45230</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45230</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>45230</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45230</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45230</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45232</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>45233</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45233</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45233</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -65753,7 +65753,7 @@
         <v>45237</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>45238</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>45239</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45240</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45243</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45243</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45244</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45244</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45244</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45250</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45250</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45250</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45250</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45250</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -66819,7 +66819,7 @@
         <v>45252</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -66876,7 +66876,7 @@
         <v>45252</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -66933,7 +66933,7 @@
         <v>45252</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -66990,7 +66990,7 @@
         <v>45253</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67047,7 +67047,7 @@
         <v>45253</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45253</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67161,7 +67161,7 @@
         <v>45253</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67218,7 +67218,7 @@
         <v>45253</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45253</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>45257</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45258</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -67565,7 +67565,7 @@
         <v>45259</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>45260</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>45261</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -67736,7 +67736,7 @@
         <v>45264</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>45271</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>45282</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>45313</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45315</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68086,14 +68086,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 5042-2024</t>
+          <t>A 4984-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68106,7 +68106,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -68143,14 +68143,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 4984-2024</t>
+          <t>A 5042-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68163,7 +68163,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -68200,14 +68200,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5149-2024</t>
+          <t>A 5161-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -68220,7 +68220,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -68257,14 +68257,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5161-2024</t>
+          <t>A 5149-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -68277,7 +68277,7 @@
         </is>
       </c>
       <c r="G1068" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -68314,14 +68314,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5216-2024</t>
+          <t>A 5198-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -68333,8 +68333,13 @@
           <t>ÖSTHAMMAR</t>
         </is>
       </c>
+      <c r="F1069" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G1069" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -68371,14 +68376,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5198-2024</t>
+          <t>A 5216-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -68390,13 +68395,8 @@
           <t>ÖSTHAMMAR</t>
         </is>
       </c>
-      <c r="F1070" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G1070" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -68440,7 +68440,7 @@
         <v>45330</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -68490,14 +68490,14 @@
     <row r="1072" ht="15" customHeight="1">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>A 5860-2024</t>
+          <t>A 5851-2024</t>
         </is>
       </c>
       <c r="B1072" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -68510,7 +68510,7 @@
         </is>
       </c>
       <c r="G1072" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="H1072" t="n">
         <v>0</v>
@@ -68547,14 +68547,14 @@
     <row r="1073" ht="15" customHeight="1">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>A 5851-2024</t>
+          <t>A 5860-2024</t>
         </is>
       </c>
       <c r="B1073" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -68567,7 +68567,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -68611,7 +68611,7 @@
         <v>45337</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -68661,14 +68661,14 @@
     <row r="1075" ht="15" customHeight="1">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>A 6102-2024</t>
+          <t>A 6143-2024</t>
         </is>
       </c>
       <c r="B1075" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="H1075" t="n">
         <v>0</v>
@@ -68718,14 +68718,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6106-2024</t>
+          <t>A 6102-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -68738,7 +68738,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -68775,14 +68775,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 6120-2024</t>
+          <t>A 6106-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -68795,7 +68795,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>
@@ -68832,14 +68832,14 @@
     <row r="1078" ht="15" customHeight="1">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>A 6143-2024</t>
+          <t>A 6120-2024</t>
         </is>
       </c>
       <c r="B1078" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -68896,7 +68896,7 @@
         <v>45338</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -68953,7 +68953,7 @@
         <v>45341</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -69010,7 +69010,7 @@
         <v>45341</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45346</v>
+        <v>45347</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45098</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>44063</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>45182</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>43689</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44077</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45077</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44698</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44771</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>43647</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44789</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44312</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44335</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44779</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45076</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45303</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>43447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>43538</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44021</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44546</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44572</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>44614</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44662</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44727</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44819</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45006</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45076</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45099</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45201</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45205</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45244</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>43573</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44376</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44684</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>45092</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>43480</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44376</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44474</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44739</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44875</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44984</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44998</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45002</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45016</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45054</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45055</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45190</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45230</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45246</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>43369</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>43508</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43846</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43882</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44235</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44495</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44525</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44555</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44610</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44644</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44729</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44778</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44865</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44874</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44874</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44967</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45063</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45092</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45154</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45205</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45238</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45238</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45253</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43462</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43689</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43742</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>43959</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44007</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44043</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44090</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44455</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44509</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44511</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44606</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44607</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44712</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44728</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44796</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44874</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44874</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44875</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44938</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45013</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45021</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45021</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45048</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45063</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45070</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45070</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45075</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45078</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45107</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45121</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45135</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45238</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45246</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45246</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45246</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45323</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>43320</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>43327</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>43343</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>43343</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43355</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43360</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43376</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43381</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43384</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43398</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43410</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>43423</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43423</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43423</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43431</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43432</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>43432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>43448</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>43468</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>43469</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>43469</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43472</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>43472</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43473</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>43474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>43475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43476</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>43479</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43479</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43479</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>43479</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>43480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>43482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>43482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>43483</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43483</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43484</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43485</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43485</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43485</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43485</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43485</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43486</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43486</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43487</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43489</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43489</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>43489</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>43493</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>43493</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>43493</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>43494</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>43494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>43495</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>43500</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>43500</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>43502</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>43503</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43507</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43507</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>43508</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>43508</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>43509</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>43514</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>43515</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>43517</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>43518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>43518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>43518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>43518</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>43521</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>43522</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>43523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>43524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>43524</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43524</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>43529</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>43530</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>43531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43535</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43535</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43536</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43537</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>43537</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43538</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43545</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43545</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>43550</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>43560</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>43561</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>43562</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>43562</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>43573</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>43580</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>43590</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43590</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43591</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43605</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43607</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>43607</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43607</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>43612</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>43613</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>43613</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>43618</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>43623</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>43635</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>43642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>43642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>43647</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>43651</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>43651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>43651</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>43651</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>43651</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>43686</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>43692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>43699</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43699</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43706</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>43713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>43717</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>43723</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>43723</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>43739</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>43748</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>43755</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>43761</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>43767</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>43773</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>43782</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>43787</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>43790</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>43795</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>43797</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>43802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>43808</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>43810</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>43812</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>43817</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>43821</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>43821</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>43821</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>43838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>43844</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>43844</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>43850</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>43852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>43855</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>43864</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>43865</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>43867</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>43873</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>43882</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>43885</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>43885</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>43895</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>43901</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>43902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>43903</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>43906</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>43909</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>43909</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>43910</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>43920</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>43936</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>43969</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>43986</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44007</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44021</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44038</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44038</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44038</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44040</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44040</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44060</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44061</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44064</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44077</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44092</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44118</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44131</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44133</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44133</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44133</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44140</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44151</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44151</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44155</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44160</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44165</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44173</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44183</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44186</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44196</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44221</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44224</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44238</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44243</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>44257</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44279</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44287</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44295</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44295</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44295</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44298</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44308</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44308</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44308</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44308</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44309</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44327</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44330</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44336</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44337</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44341</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44354</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44354</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44361</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44365</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44365</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44368</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44371</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44376</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44376</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44376</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44376</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44377</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44406</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44420</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44425</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44425</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44425</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44425</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44450</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44460</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44461</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44461</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44462</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44466</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44467</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44476</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44476</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44482</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44488</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44491</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44491</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44496</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44498</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44501</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44501</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44504</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44504</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44511</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44512</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44512</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44512</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>44515</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44515</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44515</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44515</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44519</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44522</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44522</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44523</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>44525</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44531</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44533</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44546</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44546</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44548</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44550</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44552</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44560</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44560</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44560</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44572</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44573</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44576</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44577</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44578</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44578</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44586</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44586</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44587</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44588</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>44588</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44589</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44589</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44591</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44591</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44591</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44591</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44591</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44596</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44597</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44598</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44598</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44598</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44598</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44605</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>44607</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44607</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44608</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44608</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44609</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44610</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44613</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44613</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44613</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44614</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>44614</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44618</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44620</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44622</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44622</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44622</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44622</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44628</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>44631</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44631</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44635</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44635</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44635</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44636</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44643</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44643</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44643</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44644</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44649</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44651</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44651</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44651</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44651</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>44655</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44659</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44659</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44660</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44660</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44660</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44661</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44661</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44664</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44664</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>44664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44665</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>44665</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44667</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44669</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44669</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>44670</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44676</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44676</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44683</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44684</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44687</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44687</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44687</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44687</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44687</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44687</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44691</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44691</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44692</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44694</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>44699</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44706</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>44710</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44710</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44712</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44714</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44715</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44715</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44715</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44718</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44718</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44725</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44725</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44725</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>44726</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44726</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44728</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44729</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44732</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44732</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44734</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>44734</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>44734</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44734</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44739</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44739</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44739</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44746</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44755</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44757</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44768</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44768</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44768</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44770</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44770</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44771</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>44775</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44775</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44775</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>44783</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44783</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44783</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44795</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44796</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44796</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44803</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44805</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44809</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44810</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>44810</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>44813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44813</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44814</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44818</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44824</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44824</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44825</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44826</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44838</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44838</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>44839</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>44839</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44840</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44841</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>44841</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44848</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>44858</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44858</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44860</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>44861</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44872</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44874</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44874</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>44876</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>44890</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44896</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44896</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>44901</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44905</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44915</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>44916</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44923</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>44923</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44923</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44923</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44928</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44928</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44929</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44936</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>44938</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>44938</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44938</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44945</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>44945</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44948</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44949</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44950</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44953</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44953</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>44954</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44957</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44959</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44959</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44960</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>44963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44970</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>44970</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44970</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>44972</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>44972</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>44972</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44973</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>44973</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>44978</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44978</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44979</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44980</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44981</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>44981</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44985</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44987</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>44991</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44991</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44991</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44991</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>44991</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>44991</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44991</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44992</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>44992</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>44993</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44995</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44998</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44998</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44999</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45005</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45005</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45006</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45006</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45006</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45007</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45007</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45007</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45007</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>45007</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45012</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45012</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45014</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45014</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45015</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45015</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45015</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45019</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45027</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45028</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45030</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45033</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45033</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45033</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45034</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45040</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45040</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45040</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45040</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45041</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45042</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45042</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45042</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45042</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45042</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45044</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45044</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45044</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45044</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45045</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45045</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45045</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45045</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45045</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45047</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45047</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45048</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45048</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45048</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45048</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45051</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45051</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45054</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45054</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45054</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45054</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45056</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45057</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45058</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45058</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45058</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45058</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45063</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45063</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45063</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>45068</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45070</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45070</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45070</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45072</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45072</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45072</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45075</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45075</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45075</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45076</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45076</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45079</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45080</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45080</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45082</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45082</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45083</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45084</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45084</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45084</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45086</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45089</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45090</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45090</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45090</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45090</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45090</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45093</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45093</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45093</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>45096</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45096</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45097</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>45097</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45098</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45102</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45102</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45102</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>45102</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45102</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45102</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45102</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45106</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45106</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45107</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45107</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45110</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>45111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45112</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45112</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45112</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45112</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45112</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45114</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45114</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45114</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45114</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45114</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45114</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45114</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45114</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45117</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45119</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45119</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>45119</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45120</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45121</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>45121</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45122</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45123</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45123</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45124</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45135</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>45138</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45139</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45139</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45142</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45142</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45142</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45142</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45146</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45146</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45146</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45146</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45146</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45146</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45146</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45152</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45152</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45154</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45154</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45154</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45154</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45155</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>45156</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -60425,7 +60425,7 @@
         <v>45157</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45157</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>45157</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45160</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45160</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45161</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45161</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45162</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45162</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45162</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>45163</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45169</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45172</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>45173</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45174</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45175</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45176</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45176</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>45187</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>45187</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45189</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>45189</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45191</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45194</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45194</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45194</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45194</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45194</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45194</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45194</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45195</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45196</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
         <v>45196</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -62959,7 +62959,7 @@
         <v>45197</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45198</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45201</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45201</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>45202</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45202</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45202</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45203</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>45204</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>45205</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45208</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45209</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>45210</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45210</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45210</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45210</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45212</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>45212</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45212</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45213</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45213</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45213</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45215</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45215</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45215</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>45218</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>45225</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45225</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45225</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45225</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45225</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45225</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45226</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -64982,7 +64982,7 @@
         <v>45229</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45229</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45230</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>45230</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45230</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45230</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>45230</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45230</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45230</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45232</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>45233</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45233</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45233</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -65753,7 +65753,7 @@
         <v>45237</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>45238</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>45239</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45240</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45243</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45243</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45244</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45244</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45244</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45250</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45250</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45250</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45250</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45250</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -66819,7 +66819,7 @@
         <v>45252</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -66876,7 +66876,7 @@
         <v>45252</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -66933,7 +66933,7 @@
         <v>45252</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -66990,7 +66990,7 @@
         <v>45253</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67047,7 +67047,7 @@
         <v>45253</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45253</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67161,7 +67161,7 @@
         <v>45253</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67218,7 +67218,7 @@
         <v>45253</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45253</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>45257</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45258</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -67565,7 +67565,7 @@
         <v>45259</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>45260</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>45261</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -67736,7 +67736,7 @@
         <v>45264</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>45271</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>45282</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>45313</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45315</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68093,7 +68093,7 @@
         <v>45329</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>45329</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -68264,7 +68264,7 @@
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -68321,7 +68321,7 @@
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -68383,7 +68383,7 @@
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -68440,7 +68440,7 @@
         <v>45330</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -68490,14 +68490,14 @@
     <row r="1072" ht="15" customHeight="1">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>A 5851-2024</t>
+          <t>A 5860-2024</t>
         </is>
       </c>
       <c r="B1072" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -68510,7 +68510,7 @@
         </is>
       </c>
       <c r="G1072" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H1072" t="n">
         <v>0</v>
@@ -68547,14 +68547,14 @@
     <row r="1073" ht="15" customHeight="1">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>A 5860-2024</t>
+          <t>A 5851-2024</t>
         </is>
       </c>
       <c r="B1073" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -68567,7 +68567,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -68604,14 +68604,14 @@
     <row r="1074" ht="15" customHeight="1">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>A 6121-2024</t>
+          <t>A 6120-2024</t>
         </is>
       </c>
       <c r="B1074" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -68624,7 +68624,7 @@
         </is>
       </c>
       <c r="G1074" t="n">
-        <v>0.4</v>
+        <v>0.7</v>
       </c>
       <c r="H1074" t="n">
         <v>0</v>
@@ -68661,14 +68661,14 @@
     <row r="1075" ht="15" customHeight="1">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>A 6143-2024</t>
+          <t>A 6121-2024</t>
         </is>
       </c>
       <c r="B1075" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H1075" t="n">
         <v>0</v>
@@ -68725,7 +68725,7 @@
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -68782,7 +68782,7 @@
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -68832,14 +68832,14 @@
     <row r="1078" ht="15" customHeight="1">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>A 6120-2024</t>
+          <t>A 6143-2024</t>
         </is>
       </c>
       <c r="B1078" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -68896,7 +68896,7 @@
         <v>45338</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -68946,14 +68946,14 @@
     <row r="1080" ht="15" customHeight="1">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>A 6656-2024</t>
+          <t>A 6661-2024</t>
         </is>
       </c>
       <c r="B1080" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -68966,7 +68966,7 @@
         </is>
       </c>
       <c r="G1080" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -69003,14 +69003,14 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>A 6661-2024</t>
+          <t>A 6656-2024</t>
         </is>
       </c>
       <c r="B1081" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45347</v>
+        <v>45348</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -69023,7 +69023,7 @@
         </is>
       </c>
       <c r="G1081" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="H1081" t="n">
         <v>0</v>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45098</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>44063</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>45182</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>43689</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44077</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45077</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44698</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44771</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>43647</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44789</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44312</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44335</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44779</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45076</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45303</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>43447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>43538</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44021</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44546</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44572</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>44614</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44662</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44727</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44819</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45006</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45076</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45099</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45201</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45205</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45244</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>43573</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44376</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44684</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>45092</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>43480</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44376</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44474</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44739</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44875</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44984</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44998</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45002</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45016</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45054</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45055</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45190</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45230</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45246</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>43369</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>43508</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43846</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43882</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44235</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44495</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44525</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44555</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44610</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44644</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44729</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44778</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44865</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44874</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44874</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44967</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45063</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45092</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45154</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45205</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45238</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45238</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45253</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43462</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43689</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43742</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>43959</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44007</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44043</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44090</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44455</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44509</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44511</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44606</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44607</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44712</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44728</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44796</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44874</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44874</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44875</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44938</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45013</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45021</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45021</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45048</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45063</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45070</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45070</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45075</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45078</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45107</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45121</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45135</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45238</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45246</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45246</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45246</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45323</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>43320</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>43327</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>43343</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>43343</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43355</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43360</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43376</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43381</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43384</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43398</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43410</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>43423</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43423</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43423</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43431</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43432</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>43432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>43448</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>43468</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>43469</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>43469</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43472</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>43472</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43473</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>43474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>43475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43476</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>43479</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43479</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43479</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>43479</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>43480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>43482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>43482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>43483</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43483</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43484</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43485</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43485</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43485</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43485</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43485</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43486</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43486</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43487</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43489</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43489</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>43489</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>43493</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>43493</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>43493</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>43494</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>43494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>43495</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>43500</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>43500</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>43502</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>43503</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43507</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43507</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>43508</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>43508</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>43509</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>43514</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>43515</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>43517</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>43518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>43518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>43518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>43518</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>43521</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>43522</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>43523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>43524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>43524</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43524</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>43529</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>43530</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>43531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43535</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43535</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43536</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43537</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>43537</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43538</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43545</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43545</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>43550</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>43560</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>43561</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>43562</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>43562</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>43573</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>43580</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>43590</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43590</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43591</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43605</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43607</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>43607</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43607</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>43612</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>43613</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>43613</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>43618</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>43623</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>43635</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>43642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>43642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>43647</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>43651</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>43651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>43651</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>43651</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>43651</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>43686</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>43692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>43699</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43699</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43706</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>43713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>43717</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>43723</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>43723</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>43739</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>43748</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>43755</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>43761</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>43767</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>43773</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>43782</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>43787</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>43790</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>43795</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>43797</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>43802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>43808</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>43810</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>43812</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>43817</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>43821</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>43821</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>43821</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>43838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>43844</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>43844</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>43850</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>43852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>43855</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>43864</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>43865</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>43867</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>43873</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>43882</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>43885</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>43885</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>43895</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>43901</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>43902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>43903</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>43906</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>43909</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>43909</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>43910</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>43920</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>43936</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>43969</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>43986</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44007</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44021</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44038</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44038</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44038</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44040</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44040</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44060</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44061</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44064</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44077</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44092</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44118</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44131</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44133</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44133</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44133</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44140</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44151</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44151</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44155</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44160</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44165</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44173</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44183</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44186</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44196</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44221</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44224</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44238</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44243</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>44257</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44279</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44287</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44295</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44295</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44295</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44298</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44308</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44308</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44308</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44308</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44309</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44327</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44330</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44336</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44337</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44341</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44354</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44354</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44361</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44365</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44365</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44368</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44371</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44376</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44376</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44376</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44376</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44377</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44406</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44420</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44425</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44425</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44425</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44425</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44450</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44460</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44461</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44461</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44462</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44466</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44467</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44476</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44476</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44482</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44488</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44491</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44491</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44496</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44498</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44501</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44501</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44504</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44504</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44511</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44512</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44512</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44512</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>44515</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44515</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44515</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44515</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44519</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44522</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44522</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44523</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>44525</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44531</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44533</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44546</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44546</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44548</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44550</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44552</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44560</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44560</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44560</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44572</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44573</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44576</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44577</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44578</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44578</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44586</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44586</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44587</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44588</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>44588</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44589</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44589</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44591</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44591</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44591</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44591</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44591</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44596</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44597</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44598</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44598</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44598</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44598</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44605</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>44607</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44607</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44608</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44608</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44609</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44610</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44613</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44613</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44613</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44614</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>44614</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44618</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44620</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44622</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44622</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44622</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44622</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44628</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>44631</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44631</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44635</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44635</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44635</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44636</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44643</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44643</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44643</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44644</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44649</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44651</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44651</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44651</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44651</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>44655</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44659</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44659</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44660</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44660</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44660</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44661</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44661</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44664</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44664</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>44664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44665</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>44665</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44667</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44669</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44669</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>44670</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44676</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44676</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44683</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44684</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44687</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44687</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44687</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44687</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44687</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44687</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44691</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44691</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44692</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44694</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>44699</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44706</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>44710</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44710</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44712</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44714</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44715</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44715</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44715</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44718</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44718</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44725</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44725</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44725</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>44726</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44726</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44728</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44729</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44732</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44732</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44734</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>44734</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>44734</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44734</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44739</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44739</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44739</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44746</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44755</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44757</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44768</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44768</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44768</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44770</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44770</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44771</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>44775</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44775</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44775</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>44783</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44783</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44783</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44795</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44796</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44796</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44803</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44805</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44809</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44810</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>44810</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>44813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44813</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44814</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44818</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44824</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44824</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44825</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44826</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44838</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44838</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>44839</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>44839</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44840</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44841</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>44841</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44848</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>44858</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44858</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44860</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>44861</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44872</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44874</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44874</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>44876</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>44890</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44896</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44896</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>44901</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44905</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44915</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>44916</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44923</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>44923</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44923</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44923</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44928</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44928</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44929</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44936</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>44938</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>44938</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44938</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44945</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>44945</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44948</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44949</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44950</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44953</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44953</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>44954</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44957</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44959</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44959</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44960</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>44963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44970</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>44970</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44970</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>44972</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>44972</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>44972</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44973</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>44973</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>44978</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44978</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44979</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44980</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44981</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>44981</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44985</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44987</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>44991</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44991</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44991</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44991</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>44991</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>44991</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44991</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44992</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>44992</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>44993</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44995</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44998</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44998</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44999</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45005</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45005</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45006</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45006</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45006</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45007</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45007</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45007</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45007</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>45007</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45012</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45012</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45014</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45014</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45015</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45015</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45015</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45019</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45027</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45028</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45030</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45033</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45033</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45033</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45034</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45040</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45040</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45040</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45040</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45041</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45042</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45042</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45042</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45042</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45042</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45044</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45044</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45044</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45044</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45045</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45045</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45045</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45045</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45045</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45047</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45047</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45048</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45048</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45048</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45048</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45051</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45051</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45054</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45054</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45054</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45054</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45056</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45057</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45058</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45058</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45058</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45058</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45063</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45063</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45063</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>45068</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45070</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45070</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45070</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45072</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45072</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45072</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45075</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45075</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45075</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45076</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45076</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45079</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45080</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45080</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45082</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45082</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45083</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45084</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45084</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45084</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45086</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45089</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45090</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45090</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45090</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45090</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45090</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45093</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45093</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45093</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>45096</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45096</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45097</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>45097</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45098</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45102</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45102</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45102</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>45102</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45102</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45102</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45102</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45106</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45106</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45107</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45107</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45110</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>45111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45112</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45112</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45112</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45112</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45112</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45114</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45114</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45114</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45114</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45114</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45114</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45114</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45114</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45117</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45119</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45119</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>45119</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45120</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45121</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>45121</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45122</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45123</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45123</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45124</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45135</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>45138</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45139</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45139</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45142</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45142</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45142</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45142</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45146</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45146</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45146</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45146</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45146</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45146</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45146</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45152</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45152</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45154</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45154</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45154</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45154</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45155</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>45156</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -60425,7 +60425,7 @@
         <v>45157</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45157</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>45157</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45160</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45160</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45161</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45161</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45162</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45162</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45162</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>45163</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45169</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45172</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>45173</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45174</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45175</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45176</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45176</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>45187</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>45187</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45189</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>45189</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45191</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45194</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45194</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45194</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45194</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45194</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45194</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45194</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45195</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45196</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
         <v>45196</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -62959,7 +62959,7 @@
         <v>45197</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45198</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45201</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45201</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>45202</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45202</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45202</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45203</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>45204</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>45205</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45208</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45209</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>45210</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45210</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45210</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45210</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45212</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>45212</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45212</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45213</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45213</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45213</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45215</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45215</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45215</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>45218</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>45225</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45225</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45225</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45225</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45225</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45225</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45226</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -64982,7 +64982,7 @@
         <v>45229</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45229</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45230</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>45230</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45230</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45230</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>45230</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45230</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45230</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45232</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>45233</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45233</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45233</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -65753,7 +65753,7 @@
         <v>45237</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>45238</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>45239</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45240</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45243</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45243</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45244</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45244</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45244</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45250</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45250</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45250</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45250</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45250</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -66819,7 +66819,7 @@
         <v>45252</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -66876,7 +66876,7 @@
         <v>45252</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -66933,7 +66933,7 @@
         <v>45252</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -66990,7 +66990,7 @@
         <v>45253</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67047,7 +67047,7 @@
         <v>45253</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45253</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67161,7 +67161,7 @@
         <v>45253</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67218,7 +67218,7 @@
         <v>45253</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45253</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>45257</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45258</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -67565,7 +67565,7 @@
         <v>45259</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>45260</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>45261</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -67736,7 +67736,7 @@
         <v>45264</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>45271</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>45282</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>45313</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45315</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68093,7 +68093,7 @@
         <v>45329</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>45329</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68207,7 +68207,7 @@
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -68257,14 +68257,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5149-2024</t>
+          <t>A 5198-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -68276,8 +68276,13 @@
           <t>ÖSTHAMMAR</t>
         </is>
       </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G1068" t="n">
-        <v>1.1</v>
+        <v>2.4</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -68314,14 +68319,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5198-2024</t>
+          <t>A 5216-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -68333,13 +68338,8 @@
           <t>ÖSTHAMMAR</t>
         </is>
       </c>
-      <c r="F1069" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G1069" t="n">
-        <v>2.4</v>
+        <v>2.6</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -68376,14 +68376,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5216-2024</t>
+          <t>A 5149-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -68396,7 +68396,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -68440,7 +68440,7 @@
         <v>45330</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -68490,14 +68490,14 @@
     <row r="1072" ht="15" customHeight="1">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>A 5860-2024</t>
+          <t>A 5851-2024</t>
         </is>
       </c>
       <c r="B1072" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -68510,7 +68510,7 @@
         </is>
       </c>
       <c r="G1072" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="H1072" t="n">
         <v>0</v>
@@ -68547,14 +68547,14 @@
     <row r="1073" ht="15" customHeight="1">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>A 5851-2024</t>
+          <t>A 5860-2024</t>
         </is>
       </c>
       <c r="B1073" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -68567,7 +68567,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -68611,7 +68611,7 @@
         <v>45337</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -68661,14 +68661,14 @@
     <row r="1075" ht="15" customHeight="1">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>A 6121-2024</t>
+          <t>A 6102-2024</t>
         </is>
       </c>
       <c r="B1075" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="H1075" t="n">
         <v>0</v>
@@ -68718,14 +68718,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6102-2024</t>
+          <t>A 6106-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -68738,7 +68738,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -68775,14 +68775,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 6106-2024</t>
+          <t>A 6121-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -68795,7 +68795,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>0.6</v>
+        <v>0.4</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>
@@ -68839,7 +68839,7 @@
         <v>45337</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -68896,7 +68896,7 @@
         <v>45338</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -68946,14 +68946,14 @@
     <row r="1080" ht="15" customHeight="1">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>A 6661-2024</t>
+          <t>A 6656-2024</t>
         </is>
       </c>
       <c r="B1080" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -68966,7 +68966,7 @@
         </is>
       </c>
       <c r="G1080" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -69003,14 +69003,14 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>A 6656-2024</t>
+          <t>A 6661-2024</t>
         </is>
       </c>
       <c r="B1081" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45348</v>
+        <v>45349</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -69023,7 +69023,7 @@
         </is>
       </c>
       <c r="G1081" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="H1081" t="n">
         <v>0</v>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45098</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>44063</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>45182</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>43689</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44077</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45077</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44698</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44771</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>43647</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44789</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44312</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44335</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44779</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45076</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45303</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>43447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>43538</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44021</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44546</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44572</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>44614</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44662</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44727</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44819</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45006</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45076</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45099</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45201</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45205</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45244</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>43573</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44376</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44684</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>45092</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>43480</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44376</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44474</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44739</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44875</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44984</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44998</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45002</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45016</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45054</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45055</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45190</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45230</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45246</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>43369</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>43508</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43846</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43882</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44235</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44495</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44525</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44555</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44610</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44644</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44729</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44778</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44865</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44874</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44874</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44967</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45063</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45092</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45154</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45205</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45238</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45238</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45253</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43462</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43689</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43742</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>43959</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44007</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44043</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44090</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44455</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44509</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44511</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44606</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44607</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44712</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44728</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44796</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44874</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44874</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44875</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44938</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45013</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45021</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45021</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45048</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45063</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45070</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45070</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45075</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45078</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45107</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45121</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45135</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45238</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45246</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45246</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45246</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45323</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>43320</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>43327</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>43343</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>43343</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43355</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43360</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43376</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43381</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43384</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43398</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43410</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>43423</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43423</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43423</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43431</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43432</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>43432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>43448</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>43468</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>43469</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>43469</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43472</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>43472</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43473</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>43474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>43475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43476</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>43479</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43479</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43479</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>43479</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>43480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>43482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>43482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>43483</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43483</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43484</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43485</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43485</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43485</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43485</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43485</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43486</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43486</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43487</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43489</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43489</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>43489</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>43493</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>43493</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>43493</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>43494</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>43494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>43495</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>43500</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>43500</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>43502</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>43503</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43507</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43507</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>43508</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>43508</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>43509</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>43514</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>43515</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>43517</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>43518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>43518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>43518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>43518</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>43521</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>43522</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>43523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>43524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>43524</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43524</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>43529</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>43530</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>43531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43535</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43535</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43536</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43537</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>43537</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43538</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43545</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43545</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>43550</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>43560</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>43561</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>43562</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>43562</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>43573</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>43580</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>43590</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43590</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43591</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43605</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43607</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>43607</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43607</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>43612</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>43613</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>43613</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>43618</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>43623</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>43635</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>43642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>43642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>43647</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>43651</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>43651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>43651</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>43651</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>43651</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>43686</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>43692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>43699</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43699</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43706</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>43713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>43717</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>43723</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>43723</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>43739</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>43748</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>43755</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>43761</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>43767</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>43773</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>43782</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>43787</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>43790</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>43795</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>43797</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>43802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>43808</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>43810</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>43812</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>43817</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>43821</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>43821</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>43821</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>43838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>43844</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>43844</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>43850</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>43852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>43855</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>43864</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>43865</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>43867</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>43873</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>43882</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>43885</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>43885</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>43895</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>43901</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>43902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>43903</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>43906</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>43909</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>43909</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>43910</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>43920</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>43936</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>43969</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>43986</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44007</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44021</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44038</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44038</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44038</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44040</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44040</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44060</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44061</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44064</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44077</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44092</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44118</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44131</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44133</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44133</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44133</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44140</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44151</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44151</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44155</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44160</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44165</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44173</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44183</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44186</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44196</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44221</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44224</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44238</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44243</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>44257</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44279</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44287</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44295</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44295</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44295</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44298</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44308</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44308</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44308</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44308</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44309</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44327</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44330</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44336</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44337</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44341</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44354</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44354</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44361</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44365</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44365</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44368</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44371</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44376</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44376</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44376</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44376</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44377</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44406</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44420</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44425</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44425</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44425</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44425</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44450</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44460</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44461</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44461</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44462</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44466</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44467</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44476</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44476</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44482</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44488</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44491</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44491</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44496</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44498</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44501</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44501</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44504</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44504</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44511</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44512</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44512</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44512</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>44515</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44515</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44515</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44515</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44519</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44522</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44522</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44523</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>44525</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44531</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44533</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44546</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44546</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44548</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44550</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44552</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44560</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44560</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44560</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44572</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44573</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44576</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44577</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44578</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44578</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44586</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44586</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44587</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44588</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>44588</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44589</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44589</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44591</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44591</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44591</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44591</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44591</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44596</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44597</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44598</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44598</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44598</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44598</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44605</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>44607</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44607</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44608</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44608</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44609</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44610</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44613</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44613</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44613</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44614</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>44614</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44618</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44620</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44622</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44622</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44622</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44622</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44628</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>44631</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44631</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44635</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44635</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44635</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44636</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44643</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44643</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44643</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44644</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44649</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44651</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44651</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44651</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44651</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>44655</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44659</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44659</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44660</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44660</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44660</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44661</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44661</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44664</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44664</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>44664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44665</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>44665</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44667</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44669</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44669</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>44670</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44676</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44676</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44683</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44684</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44687</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44687</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44687</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44687</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44687</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44687</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44691</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44691</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44692</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44694</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>44699</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44706</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>44710</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44710</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44712</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44714</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44715</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44715</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44715</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44718</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44718</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44725</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44725</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44725</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>44726</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44726</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44728</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44729</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44732</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44732</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44734</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>44734</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>44734</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44734</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44739</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44739</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44739</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44746</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44755</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44757</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44768</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44768</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44768</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44770</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44770</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44771</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>44775</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44775</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44775</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>44783</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44783</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44783</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44795</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44796</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44796</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44803</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44805</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44809</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44810</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>44810</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>44813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44813</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44814</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44818</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44824</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44824</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44825</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44826</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44838</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44838</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>44839</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>44839</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44840</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44841</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>44841</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44848</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>44858</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44858</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44860</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>44861</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44872</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44874</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44874</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>44876</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>44890</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44896</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44896</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>44901</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44905</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44915</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>44916</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44923</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>44923</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44923</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44923</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44928</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44928</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44929</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44936</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>44938</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>44938</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44938</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44945</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>44945</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44948</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44949</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44950</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44953</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44953</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>44954</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44957</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44959</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44959</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44960</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>44963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44970</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>44970</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44970</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>44972</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>44972</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>44972</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44973</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>44973</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>44978</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44978</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44979</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44980</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44981</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>44981</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44985</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44987</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>44991</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44991</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44991</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44991</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>44991</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>44991</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44991</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44992</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>44992</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>44993</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44995</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44998</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44998</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44999</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45005</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45005</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45006</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45006</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45006</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45007</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45007</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45007</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45007</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>45007</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45012</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45012</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45014</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45014</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45015</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45015</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45015</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45019</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45027</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45028</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45030</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45033</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45033</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45033</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45034</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45040</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45040</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45040</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45040</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45041</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45042</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45042</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45042</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45042</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45042</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45044</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45044</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45044</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45044</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45045</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45045</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45045</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45045</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45045</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45047</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45047</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45048</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45048</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45048</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45048</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45051</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45051</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45054</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45054</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45054</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45054</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45056</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45057</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45058</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45058</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45058</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45058</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45063</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45063</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45063</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>45068</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45070</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45070</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45070</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45072</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45072</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45072</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45075</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45075</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45075</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45076</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45076</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45079</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45080</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45080</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45082</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45082</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45083</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45084</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45084</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45084</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45086</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45089</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45090</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45090</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45090</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45090</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45090</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45093</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45093</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45093</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>45096</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45096</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45097</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>45097</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45098</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45102</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45102</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45102</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>45102</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45102</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45102</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45102</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45106</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45106</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45107</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45107</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45110</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>45111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45112</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45112</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45112</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45112</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45112</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45114</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45114</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45114</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45114</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45114</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45114</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45114</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45114</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45117</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45119</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45119</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>45119</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45120</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45121</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>45121</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45122</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45123</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45123</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45124</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45135</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>45138</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45139</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45139</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45142</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45142</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45142</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45142</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45146</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45146</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45146</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45146</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45146</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45146</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45146</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45152</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45152</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45154</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45154</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45154</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45154</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45155</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>45156</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -60425,7 +60425,7 @@
         <v>45157</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45157</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>45157</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45160</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45160</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45161</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45161</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45162</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45162</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45162</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>45163</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45169</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45172</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>45173</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45174</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45175</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45176</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45176</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>45187</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>45187</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45189</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>45189</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45191</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45194</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45194</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45194</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45194</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45194</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45194</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45194</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45195</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45196</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
         <v>45196</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -62959,7 +62959,7 @@
         <v>45197</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45198</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45201</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45201</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>45202</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45202</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45202</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45203</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>45204</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>45205</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45208</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45209</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>45210</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45210</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45210</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45210</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45212</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>45212</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45212</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45213</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45213</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45213</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45215</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45215</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45215</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>45218</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>45225</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45225</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45225</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45225</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45225</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45225</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45226</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -64982,7 +64982,7 @@
         <v>45229</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45229</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45230</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>45230</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45230</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45230</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>45230</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45230</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45230</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45232</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>45233</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45233</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45233</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -65753,7 +65753,7 @@
         <v>45237</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>45238</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>45239</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45240</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45243</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45243</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45244</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45244</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45244</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45250</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45250</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45250</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45250</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45250</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -66819,7 +66819,7 @@
         <v>45252</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -66876,7 +66876,7 @@
         <v>45252</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -66933,7 +66933,7 @@
         <v>45252</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -66990,7 +66990,7 @@
         <v>45253</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67047,7 +67047,7 @@
         <v>45253</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45253</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67161,7 +67161,7 @@
         <v>45253</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67218,7 +67218,7 @@
         <v>45253</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45253</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>45257</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45258</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -67565,7 +67565,7 @@
         <v>45259</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>45260</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>45261</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -67736,7 +67736,7 @@
         <v>45264</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>45271</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>45282</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>45313</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45315</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68086,14 +68086,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 4984-2024</t>
+          <t>A 5042-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68106,7 +68106,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -68143,14 +68143,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 5042-2024</t>
+          <t>A 4984-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68163,7 +68163,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -68207,7 +68207,7 @@
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -68264,7 +68264,7 @@
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -68319,14 +68319,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5216-2024</t>
+          <t>A 5149-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -68339,7 +68339,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>2.6</v>
+        <v>1.1</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -68376,14 +68376,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5149-2024</t>
+          <t>A 5216-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -68396,7 +68396,7 @@
         </is>
       </c>
       <c r="G1070" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -68440,7 +68440,7 @@
         <v>45330</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -68490,14 +68490,14 @@
     <row r="1072" ht="15" customHeight="1">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>A 5851-2024</t>
+          <t>A 5860-2024</t>
         </is>
       </c>
       <c r="B1072" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -68510,7 +68510,7 @@
         </is>
       </c>
       <c r="G1072" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H1072" t="n">
         <v>0</v>
@@ -68547,14 +68547,14 @@
     <row r="1073" ht="15" customHeight="1">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>A 5860-2024</t>
+          <t>A 5851-2024</t>
         </is>
       </c>
       <c r="B1073" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -68567,7 +68567,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -68604,14 +68604,14 @@
     <row r="1074" ht="15" customHeight="1">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>A 6120-2024</t>
+          <t>A 6121-2024</t>
         </is>
       </c>
       <c r="B1074" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -68624,7 +68624,7 @@
         </is>
       </c>
       <c r="G1074" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H1074" t="n">
         <v>0</v>
@@ -68661,14 +68661,14 @@
     <row r="1075" ht="15" customHeight="1">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>A 6102-2024</t>
+          <t>A 6120-2024</t>
         </is>
       </c>
       <c r="B1075" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>2.7</v>
+        <v>0.7</v>
       </c>
       <c r="H1075" t="n">
         <v>0</v>
@@ -68718,14 +68718,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6106-2024</t>
+          <t>A 6102-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -68738,7 +68738,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>0.6</v>
+        <v>2.7</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -68775,14 +68775,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 6121-2024</t>
+          <t>A 6106-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -68795,7 +68795,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>
@@ -68839,7 +68839,7 @@
         <v>45337</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -68896,7 +68896,7 @@
         <v>45338</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -68946,14 +68946,14 @@
     <row r="1080" ht="15" customHeight="1">
       <c r="A1080" t="inlineStr">
         <is>
-          <t>A 6656-2024</t>
+          <t>A 6661-2024</t>
         </is>
       </c>
       <c r="B1080" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -68966,7 +68966,7 @@
         </is>
       </c>
       <c r="G1080" t="n">
-        <v>0.9</v>
+        <v>0.2</v>
       </c>
       <c r="H1080" t="n">
         <v>0</v>
@@ -69003,14 +69003,14 @@
     <row r="1081">
       <c r="A1081" t="inlineStr">
         <is>
-          <t>A 6661-2024</t>
+          <t>A 6656-2024</t>
         </is>
       </c>
       <c r="B1081" s="1" t="n">
         <v>45341</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45349</v>
+        <v>45350</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>
@@ -69023,7 +69023,7 @@
         </is>
       </c>
       <c r="G1081" t="n">
-        <v>0.2</v>
+        <v>0.9</v>
       </c>
       <c r="H1081" t="n">
         <v>0</v>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45098</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>44063</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>45182</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>43689</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44077</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45077</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44698</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44771</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>43647</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44789</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44312</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44335</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44779</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45076</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45303</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>43447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>43538</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44021</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44546</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44572</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>44614</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44662</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44727</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44819</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45006</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45076</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45099</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45201</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45205</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45244</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>43573</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44376</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44684</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>45092</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>43480</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44376</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44474</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44739</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44875</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44984</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44998</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45002</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45016</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45054</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45055</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45190</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45230</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45246</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>43369</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>43508</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43846</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43882</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44235</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44495</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44525</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44555</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44610</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44644</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44729</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44778</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44865</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44874</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44874</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44967</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45063</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45092</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45154</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45205</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45238</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45238</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45253</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43462</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43689</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43742</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>43959</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44007</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44043</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44090</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44455</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44509</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44511</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44606</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44607</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44712</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44728</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44796</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44874</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44874</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44875</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44938</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45013</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45021</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45021</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45048</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45063</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45070</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45070</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45075</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45078</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45107</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45121</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45135</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45238</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45246</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45246</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45246</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45323</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>43320</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>43327</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>43343</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>43343</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43355</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43360</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43376</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43381</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43384</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43398</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43410</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>43423</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43423</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43423</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43431</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43432</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>43432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>43448</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>43468</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>43469</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>43469</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43472</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>43472</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43473</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>43474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>43475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43476</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>43479</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43479</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43479</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>43479</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>43480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>43482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>43482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>43483</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43483</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43484</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43485</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43485</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43485</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43485</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43485</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43486</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43486</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43487</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43489</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43489</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>43489</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>43493</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>43493</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>43493</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>43494</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>43494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>43495</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>43500</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>43500</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>43502</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>43503</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43507</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43507</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>43508</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>43508</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>43509</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>43514</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>43515</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>43517</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>43518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>43518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>43518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>43518</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>43521</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>43522</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>43523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>43524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>43524</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43524</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>43529</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>43530</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>43531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43535</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43535</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43536</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43537</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>43537</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43538</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43545</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43545</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>43550</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>43560</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>43561</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>43562</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>43562</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>43573</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>43580</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>43590</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43590</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43591</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43605</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43607</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>43607</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43607</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>43612</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>43613</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>43613</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>43618</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>43623</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>43635</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>43642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>43642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>43647</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>43651</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>43651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>43651</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>43651</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>43651</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>43686</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>43692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>43699</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43699</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43706</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>43713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>43717</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>43723</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>43723</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>43739</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>43748</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>43755</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>43761</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>43767</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>43773</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>43782</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>43787</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>43790</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>43795</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>43797</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>43802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>43808</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>43810</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>43812</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>43817</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>43821</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>43821</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>43821</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>43838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>43844</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>43844</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>43850</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>43852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>43855</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>43864</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>43865</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>43867</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>43873</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>43882</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>43885</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>43885</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>43895</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>43901</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>43902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>43903</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>43906</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>43909</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>43909</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>43910</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>43920</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>43936</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>43969</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>43986</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44007</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44021</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44038</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44038</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44038</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44040</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44040</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44060</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44061</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44064</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44077</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44092</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44118</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44131</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44133</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44133</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44133</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44140</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44151</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44151</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44155</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44160</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44165</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44173</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44183</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44186</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44196</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44221</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44224</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44238</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44243</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>44257</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44279</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44287</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44295</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44295</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44295</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44298</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44308</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44308</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44308</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44308</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44309</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44327</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44330</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44336</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44337</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44341</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44354</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44354</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44361</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44365</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44365</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44368</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44371</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44376</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44376</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44376</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44376</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44377</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44406</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44420</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44425</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44425</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44425</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44425</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44450</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44460</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44461</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44461</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44462</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44466</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44467</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44476</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44476</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44482</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44488</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44491</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44491</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44496</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44498</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44501</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44501</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44504</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44504</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44511</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44512</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44512</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44512</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>44515</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44515</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44515</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44515</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44519</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44522</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44522</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44523</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>44525</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44531</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44533</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44546</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44546</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44548</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44550</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44552</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44560</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44560</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44560</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44572</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44573</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44576</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44577</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44578</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44578</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44586</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44586</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44587</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44588</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>44588</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44589</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44589</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44591</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44591</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44591</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44591</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44591</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44596</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44597</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44598</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44598</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44598</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44598</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44605</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>44607</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44607</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44608</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44608</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44609</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44610</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44613</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44613</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44613</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44614</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>44614</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44618</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44620</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44622</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44622</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44622</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44622</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44628</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>44631</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44631</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44635</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44635</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44635</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44636</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44643</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44643</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44643</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44644</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44649</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44651</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44651</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44651</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44651</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>44655</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44659</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44659</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44660</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44660</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44660</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44661</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44661</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44664</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44664</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>44664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44665</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>44665</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44667</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44669</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44669</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>44670</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44676</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44676</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44683</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44684</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44687</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44687</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44687</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44687</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44687</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44687</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44691</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44691</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44692</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44694</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>44699</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44706</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>44710</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44710</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44712</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44714</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44715</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44715</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44715</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44718</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44718</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44725</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44725</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44725</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>44726</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44726</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44728</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44729</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44732</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44732</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44734</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>44734</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>44734</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44734</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44739</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44739</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44739</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44746</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44755</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44757</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44768</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44768</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44768</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44770</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44770</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44771</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>44775</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44775</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44775</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>44783</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44783</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44783</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44795</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44796</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44796</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44803</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44805</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44809</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44810</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>44810</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>44813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44813</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44814</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44818</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44824</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44824</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44825</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44826</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44838</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44838</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>44839</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>44839</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44840</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44841</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>44841</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44848</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>44858</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44858</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44860</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>44861</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44872</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44874</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44874</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>44876</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>44890</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44896</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44896</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>44901</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44905</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44915</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>44916</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44923</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>44923</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44923</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44923</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44928</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44928</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44929</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44936</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>44938</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>44938</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44938</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44945</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>44945</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44948</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44949</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44950</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44953</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44953</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>44954</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44957</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44959</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44959</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44960</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>44963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44970</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>44970</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44970</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>44972</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>44972</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>44972</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44973</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>44973</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>44978</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44978</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44979</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44980</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44981</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>44981</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44985</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44987</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>44991</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44991</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44991</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44991</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>44991</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>44991</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44991</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44992</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>44992</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>44993</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44995</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44998</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44998</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44999</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45005</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45005</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45006</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45006</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45006</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45007</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45007</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45007</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45007</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>45007</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45012</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45012</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45014</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45014</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45015</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45015</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45015</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45019</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45027</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45028</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45030</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45033</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45033</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45033</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45034</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45040</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45040</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45040</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45040</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45041</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45042</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45042</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45042</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45042</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45042</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45044</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45044</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45044</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45044</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45045</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45045</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45045</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45045</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45045</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45047</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45047</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45048</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45048</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45048</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45048</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45051</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45051</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45054</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45054</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45054</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45054</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45056</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45057</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45058</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45058</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45058</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45058</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45063</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45063</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45063</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>45068</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45070</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45070</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45070</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45072</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45072</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45072</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45075</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45075</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45075</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45076</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45076</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45079</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45080</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45080</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45082</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45082</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45083</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45084</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45084</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45084</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45086</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45089</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45090</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45090</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45090</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45090</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45090</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45093</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45093</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45093</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>45096</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45096</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45097</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>45097</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45098</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45102</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45102</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45102</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>45102</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45102</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45102</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45102</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45106</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45106</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45107</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45107</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45110</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>45111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45112</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45112</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45112</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45112</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45112</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45114</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45114</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45114</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45114</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45114</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45114</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45114</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45114</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45117</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45119</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45119</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>45119</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45120</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45121</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>45121</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45122</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45123</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45123</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45124</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45135</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>45138</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45139</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45139</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45142</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45142</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45142</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45142</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45146</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45146</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45146</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45146</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45146</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45146</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45146</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45152</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45152</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45154</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45154</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45154</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45154</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45155</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>45156</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -60425,7 +60425,7 @@
         <v>45157</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45157</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>45157</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45160</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45160</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45161</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45161</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45162</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45162</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45162</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>45163</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45169</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45172</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>45173</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45174</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45175</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45176</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45176</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>45187</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>45187</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45189</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>45189</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45191</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45194</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45194</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45194</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45194</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45194</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45194</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45194</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45195</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45196</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
         <v>45196</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -62959,7 +62959,7 @@
         <v>45197</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45198</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45201</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45201</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>45202</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45202</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45202</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45203</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>45204</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>45205</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45208</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45209</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>45210</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45210</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45210</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45210</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45212</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>45212</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45212</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45213</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45213</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45213</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45215</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45215</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45215</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>45218</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>45225</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45225</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45225</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45225</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45225</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45225</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45226</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -64982,7 +64982,7 @@
         <v>45229</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45229</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45230</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>45230</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45230</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45230</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>45230</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45230</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45230</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45232</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>45233</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45233</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45233</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -65753,7 +65753,7 @@
         <v>45237</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>45238</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>45239</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45240</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45243</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45243</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45244</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45244</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45244</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45250</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45250</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45250</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45250</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45250</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -66819,7 +66819,7 @@
         <v>45252</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -66876,7 +66876,7 @@
         <v>45252</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -66933,7 +66933,7 @@
         <v>45252</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -66990,7 +66990,7 @@
         <v>45253</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67047,7 +67047,7 @@
         <v>45253</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45253</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67161,7 +67161,7 @@
         <v>45253</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67218,7 +67218,7 @@
         <v>45253</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45253</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>45257</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45258</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -67565,7 +67565,7 @@
         <v>45259</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>45260</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>45261</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -67736,7 +67736,7 @@
         <v>45264</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>45271</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>45282</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>45313</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45315</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68086,14 +68086,14 @@
     <row r="1065" ht="15" customHeight="1">
       <c r="A1065" t="inlineStr">
         <is>
-          <t>A 5042-2024</t>
+          <t>A 4984-2024</t>
         </is>
       </c>
       <c r="B1065" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68106,7 +68106,7 @@
         </is>
       </c>
       <c r="G1065" t="n">
-        <v>1.1</v>
+        <v>2.2</v>
       </c>
       <c r="H1065" t="n">
         <v>0</v>
@@ -68143,14 +68143,14 @@
     <row r="1066" ht="15" customHeight="1">
       <c r="A1066" t="inlineStr">
         <is>
-          <t>A 4984-2024</t>
+          <t>A 5042-2024</t>
         </is>
       </c>
       <c r="B1066" s="1" t="n">
         <v>45329</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68163,7 +68163,7 @@
         </is>
       </c>
       <c r="G1066" t="n">
-        <v>2.2</v>
+        <v>1.1</v>
       </c>
       <c r="H1066" t="n">
         <v>0</v>
@@ -68200,14 +68200,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5161-2024</t>
+          <t>A 5149-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -68220,7 +68220,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>5.5</v>
+        <v>1.1</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -68257,14 +68257,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5198-2024</t>
+          <t>A 5161-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -68276,13 +68276,8 @@
           <t>ÖSTHAMMAR</t>
         </is>
       </c>
-      <c r="F1068" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G1068" t="n">
-        <v>2.4</v>
+        <v>5.5</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -68319,14 +68314,14 @@
     <row r="1069" ht="15" customHeight="1">
       <c r="A1069" t="inlineStr">
         <is>
-          <t>A 5149-2024</t>
+          <t>A 5216-2024</t>
         </is>
       </c>
       <c r="B1069" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -68339,7 +68334,7 @@
         </is>
       </c>
       <c r="G1069" t="n">
-        <v>1.1</v>
+        <v>2.6</v>
       </c>
       <c r="H1069" t="n">
         <v>0</v>
@@ -68376,14 +68371,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5216-2024</t>
+          <t>A 5198-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -68395,8 +68390,13 @@
           <t>ÖSTHAMMAR</t>
         </is>
       </c>
+      <c r="F1070" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G1070" t="n">
-        <v>2.6</v>
+        <v>2.4</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -68440,7 +68440,7 @@
         <v>45330</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -68497,7 +68497,7 @@
         <v>45335</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -68554,7 +68554,7 @@
         <v>45335</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -68611,7 +68611,7 @@
         <v>45337</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -68661,14 +68661,14 @@
     <row r="1075" ht="15" customHeight="1">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>A 6120-2024</t>
+          <t>A 6102-2024</t>
         </is>
       </c>
       <c r="B1075" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>0.7</v>
+        <v>2.7</v>
       </c>
       <c r="H1075" t="n">
         <v>0</v>
@@ -68718,14 +68718,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6102-2024</t>
+          <t>A 6106-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -68738,7 +68738,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -68775,14 +68775,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 6106-2024</t>
+          <t>A 6143-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -68795,7 +68795,7 @@
         </is>
       </c>
       <c r="G1077" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H1077" t="n">
         <v>0</v>
@@ -68832,14 +68832,14 @@
     <row r="1078" ht="15" customHeight="1">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>A 6143-2024</t>
+          <t>A 6120-2024</t>
         </is>
       </c>
       <c r="B1078" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -68896,7 +68896,7 @@
         <v>45338</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -68953,7 +68953,7 @@
         <v>45341</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -69010,7 +69010,7 @@
         <v>45341</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45350</v>
+        <v>45351</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45098</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>44063</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>45182</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>43689</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44077</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45077</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44698</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44771</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>43647</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44789</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44312</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44335</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44779</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45076</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45303</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>43447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>43538</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44021</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44546</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44572</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>44614</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44662</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44727</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44819</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45006</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45076</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45099</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45201</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45205</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45244</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>43573</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44376</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44684</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>45092</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>43480</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44376</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44474</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44739</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44875</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44984</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44998</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45002</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45016</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45054</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45055</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45190</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45230</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45246</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>43369</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>43508</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43846</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43882</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44235</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44495</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44525</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44555</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44610</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44644</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44729</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44778</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44865</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44874</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44874</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44967</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45063</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45092</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45154</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45205</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45238</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45238</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45253</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43462</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43689</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43742</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>43959</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44007</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44043</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44090</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44455</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44509</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44511</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44606</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44607</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44712</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44728</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44796</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44874</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44874</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44875</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44938</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45013</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45021</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45021</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45048</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45063</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45070</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45070</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45075</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45078</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45107</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45121</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45135</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45238</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45246</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45246</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45246</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45323</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>43320</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>43327</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>43343</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>43343</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43355</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43360</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43376</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43381</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43384</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43398</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43410</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>43423</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43423</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43423</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43431</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43432</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>43432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>43448</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>43468</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>43469</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>43469</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43472</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>43472</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43473</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>43474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>43475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43476</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>43479</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43479</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43479</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>43479</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>43480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>43482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>43482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>43483</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43483</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43484</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43485</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43485</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43485</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43485</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43485</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43486</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43486</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43487</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43489</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43489</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>43489</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>43493</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>43493</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>43493</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>43494</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>43494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>43495</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>43500</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>43500</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>43502</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>43503</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43507</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43507</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>43508</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>43508</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>43509</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>43514</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>43515</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>43517</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>43518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>43518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>43518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>43518</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>43521</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>43522</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>43523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>43524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>43524</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43524</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>43529</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>43530</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>43531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43535</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43535</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43536</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43537</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>43537</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43538</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43545</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43545</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>43550</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>43560</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>43561</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>43562</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>43562</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>43573</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>43580</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>43590</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43590</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43591</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43605</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43607</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>43607</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43607</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>43612</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>43613</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>43613</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>43618</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>43623</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>43635</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>43642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>43642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>43647</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>43651</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>43651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>43651</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>43651</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>43651</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>43686</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>43692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>43699</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43699</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43706</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>43713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>43717</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>43723</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>43723</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>43739</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>43748</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>43755</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>43761</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>43767</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>43773</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>43782</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>43787</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>43790</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>43795</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>43797</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>43802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>43808</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>43810</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>43812</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>43817</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>43821</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>43821</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>43821</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>43838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>43844</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>43844</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>43850</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>43852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>43855</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>43864</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>43865</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>43867</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>43873</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>43882</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>43885</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>43885</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>43895</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>43901</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>43902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>43903</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>43906</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>43909</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>43909</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>43910</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>43920</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>43936</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>43969</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>43986</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44007</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44021</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44038</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44038</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44038</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44040</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44040</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44060</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44061</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44064</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44077</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44092</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44118</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44131</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44133</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44133</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44133</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44140</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44151</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44151</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44155</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44160</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44165</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44173</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44183</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44186</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44196</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44221</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44224</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44238</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44243</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>44257</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44279</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44287</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44295</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44295</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44295</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44298</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44308</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44308</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44308</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44308</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44309</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44327</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44330</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44336</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44337</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44341</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44354</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44354</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44361</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44365</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44365</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44368</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44371</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44376</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44376</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44376</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44376</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44377</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44406</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44420</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44425</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44425</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44425</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44425</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44450</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44460</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44461</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44461</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44462</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44466</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44467</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44476</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44476</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44482</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44488</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44491</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44491</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44496</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44498</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44501</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44501</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44504</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44504</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44511</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44512</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44512</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44512</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>44515</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44515</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44515</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44515</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44519</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44522</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44522</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D445" t="inlineStr">
         <is>
@@ -31290,7 +31290,7 @@
         <v>44522</v>
       </c>
       <c r="C446" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D446" t="inlineStr">
         <is>
@@ -31347,7 +31347,7 @@
         <v>44523</v>
       </c>
       <c r="C447" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D447" t="inlineStr">
         <is>
@@ -31404,7 +31404,7 @@
         <v>44523</v>
       </c>
       <c r="C448" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D448" t="inlineStr">
         <is>
@@ -31461,7 +31461,7 @@
         <v>44523</v>
       </c>
       <c r="C449" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D449" t="inlineStr">
         <is>
@@ -31518,7 +31518,7 @@
         <v>44525</v>
       </c>
       <c r="C450" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D450" t="inlineStr">
         <is>
@@ -31575,7 +31575,7 @@
         <v>44525</v>
       </c>
       <c r="C451" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D451" t="inlineStr">
         <is>
@@ -31632,7 +31632,7 @@
         <v>44531</v>
       </c>
       <c r="C452" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D452" t="inlineStr">
         <is>
@@ -31694,7 +31694,7 @@
         <v>44531</v>
       </c>
       <c r="C453" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D453" t="inlineStr">
         <is>
@@ -31756,7 +31756,7 @@
         <v>44531</v>
       </c>
       <c r="C454" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D454" t="inlineStr">
         <is>
@@ -31813,7 +31813,7 @@
         <v>44533</v>
       </c>
       <c r="C455" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D455" t="inlineStr">
         <is>
@@ -31875,7 +31875,7 @@
         <v>44536</v>
       </c>
       <c r="C456" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D456" t="inlineStr">
         <is>
@@ -31932,7 +31932,7 @@
         <v>44546</v>
       </c>
       <c r="C457" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D457" t="inlineStr">
         <is>
@@ -31994,7 +31994,7 @@
         <v>44546</v>
       </c>
       <c r="C458" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D458" t="inlineStr">
         <is>
@@ -32051,7 +32051,7 @@
         <v>44548</v>
       </c>
       <c r="C459" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D459" t="inlineStr">
         <is>
@@ -32113,7 +32113,7 @@
         <v>44550</v>
       </c>
       <c r="C460" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D460" t="inlineStr">
         <is>
@@ -32170,7 +32170,7 @@
         <v>44552</v>
       </c>
       <c r="C461" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D461" t="inlineStr">
         <is>
@@ -32227,7 +32227,7 @@
         <v>44553</v>
       </c>
       <c r="C462" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D462" t="inlineStr">
         <is>
@@ -32289,7 +32289,7 @@
         <v>44555</v>
       </c>
       <c r="C463" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D463" t="inlineStr">
         <is>
@@ -32346,7 +32346,7 @@
         <v>44555</v>
       </c>
       <c r="C464" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D464" t="inlineStr">
         <is>
@@ -32403,7 +32403,7 @@
         <v>44560</v>
       </c>
       <c r="C465" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D465" t="inlineStr">
         <is>
@@ -32465,7 +32465,7 @@
         <v>44560</v>
       </c>
       <c r="C466" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D466" t="inlineStr">
         <is>
@@ -32527,7 +32527,7 @@
         <v>44560</v>
       </c>
       <c r="C467" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D467" t="inlineStr">
         <is>
@@ -32589,7 +32589,7 @@
         <v>44560</v>
       </c>
       <c r="C468" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D468" t="inlineStr">
         <is>
@@ -32651,7 +32651,7 @@
         <v>44572</v>
       </c>
       <c r="C469" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D469" t="inlineStr">
         <is>
@@ -32708,7 +32708,7 @@
         <v>44573</v>
       </c>
       <c r="C470" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D470" t="inlineStr">
         <is>
@@ -32765,7 +32765,7 @@
         <v>44576</v>
       </c>
       <c r="C471" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D471" t="inlineStr">
         <is>
@@ -32827,7 +32827,7 @@
         <v>44577</v>
       </c>
       <c r="C472" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D472" t="inlineStr">
         <is>
@@ -32889,7 +32889,7 @@
         <v>44578</v>
       </c>
       <c r="C473" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D473" t="inlineStr">
         <is>
@@ -32946,7 +32946,7 @@
         <v>44578</v>
       </c>
       <c r="C474" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D474" t="inlineStr">
         <is>
@@ -33003,7 +33003,7 @@
         <v>44586</v>
       </c>
       <c r="C475" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D475" t="inlineStr">
         <is>
@@ -33060,7 +33060,7 @@
         <v>44586</v>
       </c>
       <c r="C476" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D476" t="inlineStr">
         <is>
@@ -33122,7 +33122,7 @@
         <v>44586</v>
       </c>
       <c r="C477" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D477" t="inlineStr">
         <is>
@@ -33184,7 +33184,7 @@
         <v>44587</v>
       </c>
       <c r="C478" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D478" t="inlineStr">
         <is>
@@ -33246,7 +33246,7 @@
         <v>44588</v>
       </c>
       <c r="C479" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D479" t="inlineStr">
         <is>
@@ -33303,7 +33303,7 @@
         <v>44588</v>
       </c>
       <c r="C480" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D480" t="inlineStr">
         <is>
@@ -33365,7 +33365,7 @@
         <v>44588</v>
       </c>
       <c r="C481" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D481" t="inlineStr">
         <is>
@@ -33427,7 +33427,7 @@
         <v>44589</v>
       </c>
       <c r="C482" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D482" t="inlineStr">
         <is>
@@ -33484,7 +33484,7 @@
         <v>44589</v>
       </c>
       <c r="C483" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D483" t="inlineStr">
         <is>
@@ -33541,7 +33541,7 @@
         <v>44591</v>
       </c>
       <c r="C484" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D484" t="inlineStr">
         <is>
@@ -33603,7 +33603,7 @@
         <v>44591</v>
       </c>
       <c r="C485" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D485" t="inlineStr">
         <is>
@@ -33660,7 +33660,7 @@
         <v>44591</v>
       </c>
       <c r="C486" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D486" t="inlineStr">
         <is>
@@ -33722,7 +33722,7 @@
         <v>44591</v>
       </c>
       <c r="C487" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D487" t="inlineStr">
         <is>
@@ -33784,7 +33784,7 @@
         <v>44591</v>
       </c>
       <c r="C488" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D488" t="inlineStr">
         <is>
@@ -33846,7 +33846,7 @@
         <v>44596</v>
       </c>
       <c r="C489" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D489" t="inlineStr">
         <is>
@@ -33903,7 +33903,7 @@
         <v>44597</v>
       </c>
       <c r="C490" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D490" t="inlineStr">
         <is>
@@ -33960,7 +33960,7 @@
         <v>44598</v>
       </c>
       <c r="C491" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D491" t="inlineStr">
         <is>
@@ -34022,7 +34022,7 @@
         <v>44598</v>
       </c>
       <c r="C492" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D492" t="inlineStr">
         <is>
@@ -34084,7 +34084,7 @@
         <v>44598</v>
       </c>
       <c r="C493" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D493" t="inlineStr">
         <is>
@@ -34146,7 +34146,7 @@
         <v>44598</v>
       </c>
       <c r="C494" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D494" t="inlineStr">
         <is>
@@ -34208,7 +34208,7 @@
         <v>44599</v>
       </c>
       <c r="C495" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D495" t="inlineStr">
         <is>
@@ -34265,7 +34265,7 @@
         <v>44599</v>
       </c>
       <c r="C496" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D496" t="inlineStr">
         <is>
@@ -34322,7 +34322,7 @@
         <v>44600</v>
       </c>
       <c r="C497" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D497" t="inlineStr">
         <is>
@@ -34379,7 +34379,7 @@
         <v>44600</v>
       </c>
       <c r="C498" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D498" t="inlineStr">
         <is>
@@ -34436,7 +34436,7 @@
         <v>44602</v>
       </c>
       <c r="C499" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D499" t="inlineStr">
         <is>
@@ -34498,7 +34498,7 @@
         <v>44605</v>
       </c>
       <c r="C500" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D500" t="inlineStr">
         <is>
@@ -34560,7 +34560,7 @@
         <v>44606</v>
       </c>
       <c r="C501" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D501" t="inlineStr">
         <is>
@@ -34617,7 +34617,7 @@
         <v>44607</v>
       </c>
       <c r="C502" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D502" t="inlineStr">
         <is>
@@ -34674,7 +34674,7 @@
         <v>44607</v>
       </c>
       <c r="C503" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D503" t="inlineStr">
         <is>
@@ -34731,7 +34731,7 @@
         <v>44608</v>
       </c>
       <c r="C504" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D504" t="inlineStr">
         <is>
@@ -34788,7 +34788,7 @@
         <v>44608</v>
       </c>
       <c r="C505" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D505" t="inlineStr">
         <is>
@@ -34845,7 +34845,7 @@
         <v>44609</v>
       </c>
       <c r="C506" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D506" t="inlineStr">
         <is>
@@ -34902,7 +34902,7 @@
         <v>44610</v>
       </c>
       <c r="C507" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D507" t="inlineStr">
         <is>
@@ -34964,7 +34964,7 @@
         <v>44613</v>
       </c>
       <c r="C508" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D508" t="inlineStr">
         <is>
@@ -35021,7 +35021,7 @@
         <v>44613</v>
       </c>
       <c r="C509" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D509" t="inlineStr">
         <is>
@@ -35078,7 +35078,7 @@
         <v>44613</v>
       </c>
       <c r="C510" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D510" t="inlineStr">
         <is>
@@ -35135,7 +35135,7 @@
         <v>44613</v>
       </c>
       <c r="C511" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D511" t="inlineStr">
         <is>
@@ -35192,7 +35192,7 @@
         <v>44613</v>
       </c>
       <c r="C512" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D512" t="inlineStr">
         <is>
@@ -35249,7 +35249,7 @@
         <v>44613</v>
       </c>
       <c r="C513" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D513" t="inlineStr">
         <is>
@@ -35306,7 +35306,7 @@
         <v>44614</v>
       </c>
       <c r="C514" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D514" t="inlineStr">
         <is>
@@ -35363,7 +35363,7 @@
         <v>44614</v>
       </c>
       <c r="C515" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D515" t="inlineStr">
         <is>
@@ -35420,7 +35420,7 @@
         <v>44618</v>
       </c>
       <c r="C516" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D516" t="inlineStr">
         <is>
@@ -35482,7 +35482,7 @@
         <v>44620</v>
       </c>
       <c r="C517" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D517" t="inlineStr">
         <is>
@@ -35539,7 +35539,7 @@
         <v>44620</v>
       </c>
       <c r="C518" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D518" t="inlineStr">
         <is>
@@ -35596,7 +35596,7 @@
         <v>44622</v>
       </c>
       <c r="C519" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D519" t="inlineStr">
         <is>
@@ -35658,7 +35658,7 @@
         <v>44622</v>
       </c>
       <c r="C520" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D520" t="inlineStr">
         <is>
@@ -35720,7 +35720,7 @@
         <v>44622</v>
       </c>
       <c r="C521" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D521" t="inlineStr">
         <is>
@@ -35782,7 +35782,7 @@
         <v>44622</v>
       </c>
       <c r="C522" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D522" t="inlineStr">
         <is>
@@ -35844,7 +35844,7 @@
         <v>44628</v>
       </c>
       <c r="C523" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D523" t="inlineStr">
         <is>
@@ -35901,7 +35901,7 @@
         <v>44631</v>
       </c>
       <c r="C524" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D524" t="inlineStr">
         <is>
@@ -35958,7 +35958,7 @@
         <v>44631</v>
       </c>
       <c r="C525" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D525" t="inlineStr">
         <is>
@@ -36020,7 +36020,7 @@
         <v>44635</v>
       </c>
       <c r="C526" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D526" t="inlineStr">
         <is>
@@ -36077,7 +36077,7 @@
         <v>44635</v>
       </c>
       <c r="C527" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D527" t="inlineStr">
         <is>
@@ -36139,7 +36139,7 @@
         <v>44635</v>
       </c>
       <c r="C528" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D528" t="inlineStr">
         <is>
@@ -36201,7 +36201,7 @@
         <v>44636</v>
       </c>
       <c r="C529" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D529" t="inlineStr">
         <is>
@@ -36258,7 +36258,7 @@
         <v>44643</v>
       </c>
       <c r="C530" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D530" t="inlineStr">
         <is>
@@ -36315,7 +36315,7 @@
         <v>44643</v>
       </c>
       <c r="C531" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D531" t="inlineStr">
         <is>
@@ -36372,7 +36372,7 @@
         <v>44643</v>
       </c>
       <c r="C532" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D532" t="inlineStr">
         <is>
@@ -36434,7 +36434,7 @@
         <v>44644</v>
       </c>
       <c r="C533" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D533" t="inlineStr">
         <is>
@@ -36491,7 +36491,7 @@
         <v>44644</v>
       </c>
       <c r="C534" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D534" t="inlineStr">
         <is>
@@ -36548,7 +36548,7 @@
         <v>44649</v>
       </c>
       <c r="C535" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D535" t="inlineStr">
         <is>
@@ -36610,7 +36610,7 @@
         <v>44651</v>
       </c>
       <c r="C536" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D536" t="inlineStr">
         <is>
@@ -36672,7 +36672,7 @@
         <v>44651</v>
       </c>
       <c r="C537" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D537" t="inlineStr">
         <is>
@@ -36734,7 +36734,7 @@
         <v>44651</v>
       </c>
       <c r="C538" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D538" t="inlineStr">
         <is>
@@ -36796,7 +36796,7 @@
         <v>44651</v>
       </c>
       <c r="C539" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D539" t="inlineStr">
         <is>
@@ -36858,7 +36858,7 @@
         <v>44655</v>
       </c>
       <c r="C540" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D540" t="inlineStr">
         <is>
@@ -36915,7 +36915,7 @@
         <v>44657</v>
       </c>
       <c r="C541" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D541" t="inlineStr">
         <is>
@@ -36972,7 +36972,7 @@
         <v>44659</v>
       </c>
       <c r="C542" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D542" t="inlineStr">
         <is>
@@ -37029,7 +37029,7 @@
         <v>44659</v>
       </c>
       <c r="C543" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D543" t="inlineStr">
         <is>
@@ -37086,7 +37086,7 @@
         <v>44660</v>
       </c>
       <c r="C544" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D544" t="inlineStr">
         <is>
@@ -37148,7 +37148,7 @@
         <v>44660</v>
       </c>
       <c r="C545" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D545" t="inlineStr">
         <is>
@@ -37210,7 +37210,7 @@
         <v>44660</v>
       </c>
       <c r="C546" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D546" t="inlineStr">
         <is>
@@ -37272,7 +37272,7 @@
         <v>44661</v>
       </c>
       <c r="C547" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D547" t="inlineStr">
         <is>
@@ -37334,7 +37334,7 @@
         <v>44661</v>
       </c>
       <c r="C548" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D548" t="inlineStr">
         <is>
@@ -37396,7 +37396,7 @@
         <v>44664</v>
       </c>
       <c r="C549" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D549" t="inlineStr">
         <is>
@@ -37453,7 +37453,7 @@
         <v>44664</v>
       </c>
       <c r="C550" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D550" t="inlineStr">
         <is>
@@ -37510,7 +37510,7 @@
         <v>44664</v>
       </c>
       <c r="C551" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D551" t="inlineStr">
         <is>
@@ -37567,7 +37567,7 @@
         <v>44665</v>
       </c>
       <c r="C552" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D552" t="inlineStr">
         <is>
@@ -37629,7 +37629,7 @@
         <v>44665</v>
       </c>
       <c r="C553" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D553" t="inlineStr">
         <is>
@@ -37691,7 +37691,7 @@
         <v>44667</v>
       </c>
       <c r="C554" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D554" t="inlineStr">
         <is>
@@ -37753,7 +37753,7 @@
         <v>44669</v>
       </c>
       <c r="C555" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D555" t="inlineStr">
         <is>
@@ -37815,7 +37815,7 @@
         <v>44669</v>
       </c>
       <c r="C556" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D556" t="inlineStr">
         <is>
@@ -37877,7 +37877,7 @@
         <v>44670</v>
       </c>
       <c r="C557" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D557" t="inlineStr">
         <is>
@@ -37934,7 +37934,7 @@
         <v>44676</v>
       </c>
       <c r="C558" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D558" t="inlineStr">
         <is>
@@ -37991,7 +37991,7 @@
         <v>44676</v>
       </c>
       <c r="C559" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D559" t="inlineStr">
         <is>
@@ -38053,7 +38053,7 @@
         <v>44683</v>
       </c>
       <c r="C560" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D560" t="inlineStr">
         <is>
@@ -38110,7 +38110,7 @@
         <v>44684</v>
       </c>
       <c r="C561" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D561" t="inlineStr">
         <is>
@@ -38167,7 +38167,7 @@
         <v>44687</v>
       </c>
       <c r="C562" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D562" t="inlineStr">
         <is>
@@ -38224,7 +38224,7 @@
         <v>44687</v>
       </c>
       <c r="C563" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D563" t="inlineStr">
         <is>
@@ -38281,7 +38281,7 @@
         <v>44687</v>
       </c>
       <c r="C564" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D564" t="inlineStr">
         <is>
@@ -38338,7 +38338,7 @@
         <v>44687</v>
       </c>
       <c r="C565" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D565" t="inlineStr">
         <is>
@@ -38400,7 +38400,7 @@
         <v>44687</v>
       </c>
       <c r="C566" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D566" t="inlineStr">
         <is>
@@ -38457,7 +38457,7 @@
         <v>44687</v>
       </c>
       <c r="C567" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D567" t="inlineStr">
         <is>
@@ -38519,7 +38519,7 @@
         <v>44691</v>
       </c>
       <c r="C568" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D568" t="inlineStr">
         <is>
@@ -38576,7 +38576,7 @@
         <v>44691</v>
       </c>
       <c r="C569" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D569" t="inlineStr">
         <is>
@@ -38633,7 +38633,7 @@
         <v>44692</v>
       </c>
       <c r="C570" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D570" t="inlineStr">
         <is>
@@ -38695,7 +38695,7 @@
         <v>44694</v>
       </c>
       <c r="C571" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D571" t="inlineStr">
         <is>
@@ -38757,7 +38757,7 @@
         <v>44699</v>
       </c>
       <c r="C572" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D572" t="inlineStr">
         <is>
@@ -38814,7 +38814,7 @@
         <v>44706</v>
       </c>
       <c r="C573" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D573" t="inlineStr">
         <is>
@@ -38871,7 +38871,7 @@
         <v>44710</v>
       </c>
       <c r="C574" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D574" t="inlineStr">
         <is>
@@ -38933,7 +38933,7 @@
         <v>44710</v>
       </c>
       <c r="C575" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D575" t="inlineStr">
         <is>
@@ -38995,7 +38995,7 @@
         <v>44712</v>
       </c>
       <c r="C576" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D576" t="inlineStr">
         <is>
@@ -39057,7 +39057,7 @@
         <v>44714</v>
       </c>
       <c r="C577" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D577" t="inlineStr">
         <is>
@@ -39114,7 +39114,7 @@
         <v>44715</v>
       </c>
       <c r="C578" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D578" t="inlineStr">
         <is>
@@ -39171,7 +39171,7 @@
         <v>44715</v>
       </c>
       <c r="C579" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D579" t="inlineStr">
         <is>
@@ -39228,7 +39228,7 @@
         <v>44715</v>
       </c>
       <c r="C580" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D580" t="inlineStr">
         <is>
@@ -39290,7 +39290,7 @@
         <v>44718</v>
       </c>
       <c r="C581" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D581" t="inlineStr">
         <is>
@@ -39352,7 +39352,7 @@
         <v>44718</v>
       </c>
       <c r="C582" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D582" t="inlineStr">
         <is>
@@ -39414,7 +39414,7 @@
         <v>44721</v>
       </c>
       <c r="C583" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D583" t="inlineStr">
         <is>
@@ -39476,7 +39476,7 @@
         <v>44725</v>
       </c>
       <c r="C584" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D584" t="inlineStr">
         <is>
@@ -39533,7 +39533,7 @@
         <v>44725</v>
       </c>
       <c r="C585" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D585" t="inlineStr">
         <is>
@@ -39590,7 +39590,7 @@
         <v>44725</v>
       </c>
       <c r="C586" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D586" t="inlineStr">
         <is>
@@ -39647,7 +39647,7 @@
         <v>44725</v>
       </c>
       <c r="C587" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D587" t="inlineStr">
         <is>
@@ -39704,7 +39704,7 @@
         <v>44726</v>
       </c>
       <c r="C588" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D588" t="inlineStr">
         <is>
@@ -39761,7 +39761,7 @@
         <v>44726</v>
       </c>
       <c r="C589" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D589" t="inlineStr">
         <is>
@@ -39818,7 +39818,7 @@
         <v>44728</v>
       </c>
       <c r="C590" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D590" t="inlineStr">
         <is>
@@ -39880,7 +39880,7 @@
         <v>44729</v>
       </c>
       <c r="C591" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D591" t="inlineStr">
         <is>
@@ -39942,7 +39942,7 @@
         <v>44732</v>
       </c>
       <c r="C592" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D592" t="inlineStr">
         <is>
@@ -39999,7 +39999,7 @@
         <v>44732</v>
       </c>
       <c r="C593" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D593" t="inlineStr">
         <is>
@@ -40056,7 +40056,7 @@
         <v>44734</v>
       </c>
       <c r="C594" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D594" t="inlineStr">
         <is>
@@ -40118,7 +40118,7 @@
         <v>44734</v>
       </c>
       <c r="C595" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D595" t="inlineStr">
         <is>
@@ -40175,7 +40175,7 @@
         <v>44734</v>
       </c>
       <c r="C596" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D596" t="inlineStr">
         <is>
@@ -40232,7 +40232,7 @@
         <v>44734</v>
       </c>
       <c r="C597" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D597" t="inlineStr">
         <is>
@@ -40294,7 +40294,7 @@
         <v>44739</v>
       </c>
       <c r="C598" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D598" t="inlineStr">
         <is>
@@ -40356,7 +40356,7 @@
         <v>44739</v>
       </c>
       <c r="C599" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D599" t="inlineStr">
         <is>
@@ -40413,7 +40413,7 @@
         <v>44739</v>
       </c>
       <c r="C600" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D600" t="inlineStr">
         <is>
@@ -40470,7 +40470,7 @@
         <v>44746</v>
       </c>
       <c r="C601" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D601" t="inlineStr">
         <is>
@@ -40527,7 +40527,7 @@
         <v>44755</v>
       </c>
       <c r="C602" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D602" t="inlineStr">
         <is>
@@ -40584,7 +40584,7 @@
         <v>44757</v>
       </c>
       <c r="C603" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D603" t="inlineStr">
         <is>
@@ -40646,7 +40646,7 @@
         <v>44757</v>
       </c>
       <c r="C604" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D604" t="inlineStr">
         <is>
@@ -40708,7 +40708,7 @@
         <v>44762</v>
       </c>
       <c r="C605" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D605" t="inlineStr">
         <is>
@@ -40770,7 +40770,7 @@
         <v>44768</v>
       </c>
       <c r="C606" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D606" t="inlineStr">
         <is>
@@ -40832,7 +40832,7 @@
         <v>44768</v>
       </c>
       <c r="C607" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D607" t="inlineStr">
         <is>
@@ -40894,7 +40894,7 @@
         <v>44768</v>
       </c>
       <c r="C608" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D608" t="inlineStr">
         <is>
@@ -40956,7 +40956,7 @@
         <v>44770</v>
       </c>
       <c r="C609" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D609" t="inlineStr">
         <is>
@@ -41018,7 +41018,7 @@
         <v>44770</v>
       </c>
       <c r="C610" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D610" t="inlineStr">
         <is>
@@ -41080,7 +41080,7 @@
         <v>44770</v>
       </c>
       <c r="C611" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D611" t="inlineStr">
         <is>
@@ -41142,7 +41142,7 @@
         <v>44771</v>
       </c>
       <c r="C612" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D612" t="inlineStr">
         <is>
@@ -41204,7 +41204,7 @@
         <v>44775</v>
       </c>
       <c r="C613" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D613" t="inlineStr">
         <is>
@@ -41261,7 +41261,7 @@
         <v>44775</v>
       </c>
       <c r="C614" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D614" t="inlineStr">
         <is>
@@ -41318,7 +41318,7 @@
         <v>44775</v>
       </c>
       <c r="C615" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D615" t="inlineStr">
         <is>
@@ -41375,7 +41375,7 @@
         <v>44783</v>
       </c>
       <c r="C616" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D616" t="inlineStr">
         <is>
@@ -41432,7 +41432,7 @@
         <v>44783</v>
       </c>
       <c r="C617" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D617" t="inlineStr">
         <is>
@@ -41494,7 +41494,7 @@
         <v>44783</v>
       </c>
       <c r="C618" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D618" t="inlineStr">
         <is>
@@ -41556,7 +41556,7 @@
         <v>44792</v>
       </c>
       <c r="C619" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D619" t="inlineStr">
         <is>
@@ -41613,7 +41613,7 @@
         <v>44795</v>
       </c>
       <c r="C620" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D620" t="inlineStr">
         <is>
@@ -41675,7 +41675,7 @@
         <v>44796</v>
       </c>
       <c r="C621" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D621" t="inlineStr">
         <is>
@@ -41737,7 +41737,7 @@
         <v>44796</v>
       </c>
       <c r="C622" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D622" t="inlineStr">
         <is>
@@ -41799,7 +41799,7 @@
         <v>44803</v>
       </c>
       <c r="C623" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D623" t="inlineStr">
         <is>
@@ -41861,7 +41861,7 @@
         <v>44805</v>
       </c>
       <c r="C624" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D624" t="inlineStr">
         <is>
@@ -41918,7 +41918,7 @@
         <v>44809</v>
       </c>
       <c r="C625" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D625" t="inlineStr">
         <is>
@@ -41975,7 +41975,7 @@
         <v>44809</v>
       </c>
       <c r="C626" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D626" t="inlineStr">
         <is>
@@ -42032,7 +42032,7 @@
         <v>44810</v>
       </c>
       <c r="C627" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D627" t="inlineStr">
         <is>
@@ -42089,7 +42089,7 @@
         <v>44810</v>
       </c>
       <c r="C628" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D628" t="inlineStr">
         <is>
@@ -42146,7 +42146,7 @@
         <v>44813</v>
       </c>
       <c r="C629" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D629" t="inlineStr">
         <is>
@@ -42208,7 +42208,7 @@
         <v>44813</v>
       </c>
       <c r="C630" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D630" t="inlineStr">
         <is>
@@ -42270,7 +42270,7 @@
         <v>44814</v>
       </c>
       <c r="C631" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D631" t="inlineStr">
         <is>
@@ -42327,7 +42327,7 @@
         <v>44818</v>
       </c>
       <c r="C632" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D632" t="inlineStr">
         <is>
@@ -42389,7 +42389,7 @@
         <v>44823</v>
       </c>
       <c r="C633" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D633" t="inlineStr">
         <is>
@@ -42451,7 +42451,7 @@
         <v>44824</v>
       </c>
       <c r="C634" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D634" t="inlineStr">
         <is>
@@ -42513,7 +42513,7 @@
         <v>44824</v>
       </c>
       <c r="C635" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D635" t="inlineStr">
         <is>
@@ -42570,7 +42570,7 @@
         <v>44825</v>
       </c>
       <c r="C636" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D636" t="inlineStr">
         <is>
@@ -42632,7 +42632,7 @@
         <v>44826</v>
       </c>
       <c r="C637" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D637" t="inlineStr">
         <is>
@@ -42694,7 +42694,7 @@
         <v>44838</v>
       </c>
       <c r="C638" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D638" t="inlineStr">
         <is>
@@ -42756,7 +42756,7 @@
         <v>44838</v>
       </c>
       <c r="C639" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D639" t="inlineStr">
         <is>
@@ -42818,7 +42818,7 @@
         <v>44839</v>
       </c>
       <c r="C640" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D640" t="inlineStr">
         <is>
@@ -42875,7 +42875,7 @@
         <v>44839</v>
       </c>
       <c r="C641" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D641" t="inlineStr">
         <is>
@@ -42932,7 +42932,7 @@
         <v>44839</v>
       </c>
       <c r="C642" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D642" t="inlineStr">
         <is>
@@ -42989,7 +42989,7 @@
         <v>44840</v>
       </c>
       <c r="C643" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D643" t="inlineStr">
         <is>
@@ -43046,7 +43046,7 @@
         <v>44841</v>
       </c>
       <c r="C644" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D644" t="inlineStr">
         <is>
@@ -43103,7 +43103,7 @@
         <v>44841</v>
       </c>
       <c r="C645" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D645" t="inlineStr">
         <is>
@@ -43160,7 +43160,7 @@
         <v>44846</v>
       </c>
       <c r="C646" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D646" t="inlineStr">
         <is>
@@ -43222,7 +43222,7 @@
         <v>44848</v>
       </c>
       <c r="C647" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D647" t="inlineStr">
         <is>
@@ -43279,7 +43279,7 @@
         <v>44851</v>
       </c>
       <c r="C648" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D648" t="inlineStr">
         <is>
@@ -43341,7 +43341,7 @@
         <v>44852</v>
       </c>
       <c r="C649" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D649" t="inlineStr">
         <is>
@@ -43398,7 +43398,7 @@
         <v>44858</v>
       </c>
       <c r="C650" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D650" t="inlineStr">
         <is>
@@ -43455,7 +43455,7 @@
         <v>44858</v>
       </c>
       <c r="C651" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D651" t="inlineStr">
         <is>
@@ -43512,7 +43512,7 @@
         <v>44860</v>
       </c>
       <c r="C652" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D652" t="inlineStr">
         <is>
@@ -43569,7 +43569,7 @@
         <v>44861</v>
       </c>
       <c r="C653" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D653" t="inlineStr">
         <is>
@@ -43626,7 +43626,7 @@
         <v>44865</v>
       </c>
       <c r="C654" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D654" t="inlineStr">
         <is>
@@ -43688,7 +43688,7 @@
         <v>44866</v>
       </c>
       <c r="C655" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D655" t="inlineStr">
         <is>
@@ -43745,7 +43745,7 @@
         <v>44868</v>
       </c>
       <c r="C656" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D656" t="inlineStr">
         <is>
@@ -43802,7 +43802,7 @@
         <v>44872</v>
       </c>
       <c r="C657" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D657" t="inlineStr">
         <is>
@@ -43859,7 +43859,7 @@
         <v>44872</v>
       </c>
       <c r="C658" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D658" t="inlineStr">
         <is>
@@ -43916,7 +43916,7 @@
         <v>44873</v>
       </c>
       <c r="C659" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D659" t="inlineStr">
         <is>
@@ -43973,7 +43973,7 @@
         <v>44873</v>
       </c>
       <c r="C660" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D660" t="inlineStr">
         <is>
@@ -44030,7 +44030,7 @@
         <v>44873</v>
       </c>
       <c r="C661" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D661" t="inlineStr">
         <is>
@@ -44087,7 +44087,7 @@
         <v>44874</v>
       </c>
       <c r="C662" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D662" t="inlineStr">
         <is>
@@ -44149,7 +44149,7 @@
         <v>44874</v>
       </c>
       <c r="C663" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D663" t="inlineStr">
         <is>
@@ -44206,7 +44206,7 @@
         <v>44874</v>
       </c>
       <c r="C664" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D664" t="inlineStr">
         <is>
@@ -44268,7 +44268,7 @@
         <v>44874</v>
       </c>
       <c r="C665" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D665" t="inlineStr">
         <is>
@@ -44330,7 +44330,7 @@
         <v>44874</v>
       </c>
       <c r="C666" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D666" t="inlineStr">
         <is>
@@ -44392,7 +44392,7 @@
         <v>44876</v>
       </c>
       <c r="C667" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D667" t="inlineStr">
         <is>
@@ -44449,7 +44449,7 @@
         <v>44883</v>
       </c>
       <c r="C668" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D668" t="inlineStr">
         <is>
@@ -44506,7 +44506,7 @@
         <v>44890</v>
       </c>
       <c r="C669" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D669" t="inlineStr">
         <is>
@@ -44568,7 +44568,7 @@
         <v>44894</v>
       </c>
       <c r="C670" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D670" t="inlineStr">
         <is>
@@ -44625,7 +44625,7 @@
         <v>44896</v>
       </c>
       <c r="C671" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D671" t="inlineStr">
         <is>
@@ -44682,7 +44682,7 @@
         <v>44896</v>
       </c>
       <c r="C672" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D672" t="inlineStr">
         <is>
@@ -44739,7 +44739,7 @@
         <v>44900</v>
       </c>
       <c r="C673" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D673" t="inlineStr">
         <is>
@@ -44801,7 +44801,7 @@
         <v>44901</v>
       </c>
       <c r="C674" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D674" t="inlineStr">
         <is>
@@ -44863,7 +44863,7 @@
         <v>44903</v>
       </c>
       <c r="C675" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D675" t="inlineStr">
         <is>
@@ -44920,7 +44920,7 @@
         <v>44903</v>
       </c>
       <c r="C676" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D676" t="inlineStr">
         <is>
@@ -44977,7 +44977,7 @@
         <v>44905</v>
       </c>
       <c r="C677" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D677" t="inlineStr">
         <is>
@@ -45034,7 +45034,7 @@
         <v>44907</v>
       </c>
       <c r="C678" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D678" t="inlineStr">
         <is>
@@ -45091,7 +45091,7 @@
         <v>44908</v>
       </c>
       <c r="C679" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D679" t="inlineStr">
         <is>
@@ -45148,7 +45148,7 @@
         <v>44909</v>
       </c>
       <c r="C680" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D680" t="inlineStr">
         <is>
@@ -45205,7 +45205,7 @@
         <v>44911</v>
       </c>
       <c r="C681" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D681" t="inlineStr">
         <is>
@@ -45262,7 +45262,7 @@
         <v>44915</v>
       </c>
       <c r="C682" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D682" t="inlineStr">
         <is>
@@ -45319,7 +45319,7 @@
         <v>44915</v>
       </c>
       <c r="C683" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D683" t="inlineStr">
         <is>
@@ -45376,7 +45376,7 @@
         <v>44915</v>
       </c>
       <c r="C684" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D684" t="inlineStr">
         <is>
@@ -45433,7 +45433,7 @@
         <v>44916</v>
       </c>
       <c r="C685" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D685" t="inlineStr">
         <is>
@@ -45490,7 +45490,7 @@
         <v>44923</v>
       </c>
       <c r="C686" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D686" t="inlineStr">
         <is>
@@ -45552,7 +45552,7 @@
         <v>44923</v>
       </c>
       <c r="C687" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D687" t="inlineStr">
         <is>
@@ -45614,7 +45614,7 @@
         <v>44923</v>
       </c>
       <c r="C688" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D688" t="inlineStr">
         <is>
@@ -45676,7 +45676,7 @@
         <v>44923</v>
       </c>
       <c r="C689" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D689" t="inlineStr">
         <is>
@@ -45738,7 +45738,7 @@
         <v>44928</v>
       </c>
       <c r="C690" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D690" t="inlineStr">
         <is>
@@ -45795,7 +45795,7 @@
         <v>44928</v>
       </c>
       <c r="C691" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D691" t="inlineStr">
         <is>
@@ -45852,7 +45852,7 @@
         <v>44929</v>
       </c>
       <c r="C692" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D692" t="inlineStr">
         <is>
@@ -45914,7 +45914,7 @@
         <v>44936</v>
       </c>
       <c r="C693" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D693" t="inlineStr">
         <is>
@@ -45971,7 +45971,7 @@
         <v>44938</v>
       </c>
       <c r="C694" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D694" t="inlineStr">
         <is>
@@ -46028,7 +46028,7 @@
         <v>44938</v>
       </c>
       <c r="C695" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D695" t="inlineStr">
         <is>
@@ -46085,7 +46085,7 @@
         <v>44938</v>
       </c>
       <c r="C696" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D696" t="inlineStr">
         <is>
@@ -46142,7 +46142,7 @@
         <v>44943</v>
       </c>
       <c r="C697" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D697" t="inlineStr">
         <is>
@@ -46199,7 +46199,7 @@
         <v>44945</v>
       </c>
       <c r="C698" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D698" t="inlineStr">
         <is>
@@ -46261,7 +46261,7 @@
         <v>44945</v>
       </c>
       <c r="C699" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D699" t="inlineStr">
         <is>
@@ -46323,7 +46323,7 @@
         <v>44948</v>
       </c>
       <c r="C700" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D700" t="inlineStr">
         <is>
@@ -46380,7 +46380,7 @@
         <v>44949</v>
       </c>
       <c r="C701" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D701" t="inlineStr">
         <is>
@@ -46437,7 +46437,7 @@
         <v>44950</v>
       </c>
       <c r="C702" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D702" t="inlineStr">
         <is>
@@ -46499,7 +46499,7 @@
         <v>44952</v>
       </c>
       <c r="C703" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D703" t="inlineStr">
         <is>
@@ -46556,7 +46556,7 @@
         <v>44952</v>
       </c>
       <c r="C704" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D704" t="inlineStr">
         <is>
@@ -46618,7 +46618,7 @@
         <v>44953</v>
       </c>
       <c r="C705" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D705" t="inlineStr">
         <is>
@@ -46675,7 +46675,7 @@
         <v>44953</v>
       </c>
       <c r="C706" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D706" t="inlineStr">
         <is>
@@ -46732,7 +46732,7 @@
         <v>44954</v>
       </c>
       <c r="C707" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D707" t="inlineStr">
         <is>
@@ -46794,7 +46794,7 @@
         <v>44957</v>
       </c>
       <c r="C708" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D708" t="inlineStr">
         <is>
@@ -46851,7 +46851,7 @@
         <v>44959</v>
       </c>
       <c r="C709" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D709" t="inlineStr">
         <is>
@@ -46913,7 +46913,7 @@
         <v>44959</v>
       </c>
       <c r="C710" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D710" t="inlineStr">
         <is>
@@ -46975,7 +46975,7 @@
         <v>44960</v>
       </c>
       <c r="C711" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D711" t="inlineStr">
         <is>
@@ -47032,7 +47032,7 @@
         <v>44960</v>
       </c>
       <c r="C712" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D712" t="inlineStr">
         <is>
@@ -47089,7 +47089,7 @@
         <v>44960</v>
       </c>
       <c r="C713" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D713" t="inlineStr">
         <is>
@@ -47146,7 +47146,7 @@
         <v>44963</v>
       </c>
       <c r="C714" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D714" t="inlineStr">
         <is>
@@ -47203,7 +47203,7 @@
         <v>44963</v>
       </c>
       <c r="C715" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D715" t="inlineStr">
         <is>
@@ -47260,7 +47260,7 @@
         <v>44963</v>
       </c>
       <c r="C716" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D716" t="inlineStr">
         <is>
@@ -47317,7 +47317,7 @@
         <v>44963</v>
       </c>
       <c r="C717" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D717" t="inlineStr">
         <is>
@@ -47374,7 +47374,7 @@
         <v>44963</v>
       </c>
       <c r="C718" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D718" t="inlineStr">
         <is>
@@ -47431,7 +47431,7 @@
         <v>44963</v>
       </c>
       <c r="C719" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D719" t="inlineStr">
         <is>
@@ -47488,7 +47488,7 @@
         <v>44970</v>
       </c>
       <c r="C720" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D720" t="inlineStr">
         <is>
@@ -47545,7 +47545,7 @@
         <v>44970</v>
       </c>
       <c r="C721" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D721" t="inlineStr">
         <is>
@@ -47602,7 +47602,7 @@
         <v>44970</v>
       </c>
       <c r="C722" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D722" t="inlineStr">
         <is>
@@ -47659,7 +47659,7 @@
         <v>44972</v>
       </c>
       <c r="C723" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D723" t="inlineStr">
         <is>
@@ -47721,7 +47721,7 @@
         <v>44972</v>
       </c>
       <c r="C724" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D724" t="inlineStr">
         <is>
@@ -47783,7 +47783,7 @@
         <v>44972</v>
       </c>
       <c r="C725" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D725" t="inlineStr">
         <is>
@@ -47845,7 +47845,7 @@
         <v>44973</v>
       </c>
       <c r="C726" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D726" t="inlineStr">
         <is>
@@ -47902,7 +47902,7 @@
         <v>44973</v>
       </c>
       <c r="C727" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D727" t="inlineStr">
         <is>
@@ -47959,7 +47959,7 @@
         <v>44973</v>
       </c>
       <c r="C728" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D728" t="inlineStr">
         <is>
@@ -48021,7 +48021,7 @@
         <v>44973</v>
       </c>
       <c r="C729" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D729" t="inlineStr">
         <is>
@@ -48083,7 +48083,7 @@
         <v>44977</v>
       </c>
       <c r="C730" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D730" t="inlineStr">
         <is>
@@ -48145,7 +48145,7 @@
         <v>44978</v>
       </c>
       <c r="C731" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D731" t="inlineStr">
         <is>
@@ -48207,7 +48207,7 @@
         <v>44978</v>
       </c>
       <c r="C732" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D732" t="inlineStr">
         <is>
@@ -48269,7 +48269,7 @@
         <v>44979</v>
       </c>
       <c r="C733" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D733" t="inlineStr">
         <is>
@@ -48331,7 +48331,7 @@
         <v>44980</v>
       </c>
       <c r="C734" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D734" t="inlineStr">
         <is>
@@ -48393,7 +48393,7 @@
         <v>44981</v>
       </c>
       <c r="C735" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D735" t="inlineStr">
         <is>
@@ -48455,7 +48455,7 @@
         <v>44981</v>
       </c>
       <c r="C736" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D736" t="inlineStr">
         <is>
@@ -48517,7 +48517,7 @@
         <v>44985</v>
       </c>
       <c r="C737" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D737" t="inlineStr">
         <is>
@@ -48574,7 +48574,7 @@
         <v>44987</v>
       </c>
       <c r="C738" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D738" t="inlineStr">
         <is>
@@ -48631,7 +48631,7 @@
         <v>44991</v>
       </c>
       <c r="C739" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D739" t="inlineStr">
         <is>
@@ -48688,7 +48688,7 @@
         <v>44991</v>
       </c>
       <c r="C740" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D740" t="inlineStr">
         <is>
@@ -48745,7 +48745,7 @@
         <v>44991</v>
       </c>
       <c r="C741" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D741" t="inlineStr">
         <is>
@@ -48807,7 +48807,7 @@
         <v>44991</v>
       </c>
       <c r="C742" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D742" t="inlineStr">
         <is>
@@ -48869,7 +48869,7 @@
         <v>44991</v>
       </c>
       <c r="C743" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D743" t="inlineStr">
         <is>
@@ -48931,7 +48931,7 @@
         <v>44991</v>
       </c>
       <c r="C744" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D744" t="inlineStr">
         <is>
@@ -48993,7 +48993,7 @@
         <v>44991</v>
       </c>
       <c r="C745" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D745" t="inlineStr">
         <is>
@@ -49055,7 +49055,7 @@
         <v>44992</v>
       </c>
       <c r="C746" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D746" t="inlineStr">
         <is>
@@ -49117,7 +49117,7 @@
         <v>44992</v>
       </c>
       <c r="C747" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D747" t="inlineStr">
         <is>
@@ -49179,7 +49179,7 @@
         <v>44993</v>
       </c>
       <c r="C748" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D748" t="inlineStr">
         <is>
@@ -49241,7 +49241,7 @@
         <v>44995</v>
       </c>
       <c r="C749" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D749" t="inlineStr">
         <is>
@@ -49298,7 +49298,7 @@
         <v>44995</v>
       </c>
       <c r="C750" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D750" t="inlineStr">
         <is>
@@ -49355,7 +49355,7 @@
         <v>44998</v>
       </c>
       <c r="C751" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D751" t="inlineStr">
         <is>
@@ -49412,7 +49412,7 @@
         <v>44998</v>
       </c>
       <c r="C752" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D752" t="inlineStr">
         <is>
@@ -49469,7 +49469,7 @@
         <v>44999</v>
       </c>
       <c r="C753" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D753" t="inlineStr">
         <is>
@@ -49531,7 +49531,7 @@
         <v>45005</v>
       </c>
       <c r="C754" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D754" t="inlineStr">
         <is>
@@ -49588,7 +49588,7 @@
         <v>45005</v>
       </c>
       <c r="C755" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D755" t="inlineStr">
         <is>
@@ -49645,7 +49645,7 @@
         <v>45006</v>
       </c>
       <c r="C756" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D756" t="inlineStr">
         <is>
@@ -49702,7 +49702,7 @@
         <v>45006</v>
       </c>
       <c r="C757" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D757" t="inlineStr">
         <is>
@@ -49764,7 +49764,7 @@
         <v>45006</v>
       </c>
       <c r="C758" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D758" t="inlineStr">
         <is>
@@ -49826,7 +49826,7 @@
         <v>45007</v>
       </c>
       <c r="C759" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D759" t="inlineStr">
         <is>
@@ -49883,7 +49883,7 @@
         <v>45007</v>
       </c>
       <c r="C760" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D760" t="inlineStr">
         <is>
@@ -49940,7 +49940,7 @@
         <v>45007</v>
       </c>
       <c r="C761" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D761" t="inlineStr">
         <is>
@@ -49997,7 +49997,7 @@
         <v>45007</v>
       </c>
       <c r="C762" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D762" t="inlineStr">
         <is>
@@ -50054,7 +50054,7 @@
         <v>45007</v>
       </c>
       <c r="C763" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D763" t="inlineStr">
         <is>
@@ -50111,7 +50111,7 @@
         <v>45012</v>
       </c>
       <c r="C764" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D764" t="inlineStr">
         <is>
@@ -50173,7 +50173,7 @@
         <v>45012</v>
       </c>
       <c r="C765" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D765" t="inlineStr">
         <is>
@@ -50235,7 +50235,7 @@
         <v>45013</v>
       </c>
       <c r="C766" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D766" t="inlineStr">
         <is>
@@ -50292,7 +50292,7 @@
         <v>45014</v>
       </c>
       <c r="C767" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D767" t="inlineStr">
         <is>
@@ -50349,7 +50349,7 @@
         <v>45014</v>
       </c>
       <c r="C768" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D768" t="inlineStr">
         <is>
@@ -50406,7 +50406,7 @@
         <v>45015</v>
       </c>
       <c r="C769" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D769" t="inlineStr">
         <is>
@@ -50468,7 +50468,7 @@
         <v>45015</v>
       </c>
       <c r="C770" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D770" t="inlineStr">
         <is>
@@ -50530,7 +50530,7 @@
         <v>45015</v>
       </c>
       <c r="C771" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D771" t="inlineStr">
         <is>
@@ -50587,7 +50587,7 @@
         <v>45019</v>
       </c>
       <c r="C772" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D772" t="inlineStr">
         <is>
@@ -50644,7 +50644,7 @@
         <v>45027</v>
       </c>
       <c r="C773" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D773" t="inlineStr">
         <is>
@@ -50701,7 +50701,7 @@
         <v>45028</v>
       </c>
       <c r="C774" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D774" t="inlineStr">
         <is>
@@ -50763,7 +50763,7 @@
         <v>45030</v>
       </c>
       <c r="C775" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D775" t="inlineStr">
         <is>
@@ -50820,7 +50820,7 @@
         <v>45033</v>
       </c>
       <c r="C776" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D776" t="inlineStr">
         <is>
@@ -50877,7 +50877,7 @@
         <v>45033</v>
       </c>
       <c r="C777" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D777" t="inlineStr">
         <is>
@@ -50934,7 +50934,7 @@
         <v>45033</v>
       </c>
       <c r="C778" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D778" t="inlineStr">
         <is>
@@ -50991,7 +50991,7 @@
         <v>45034</v>
       </c>
       <c r="C779" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D779" t="inlineStr">
         <is>
@@ -51053,7 +51053,7 @@
         <v>45036</v>
       </c>
       <c r="C780" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D780" t="inlineStr">
         <is>
@@ -51110,7 +51110,7 @@
         <v>45037</v>
       </c>
       <c r="C781" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D781" t="inlineStr">
         <is>
@@ -51167,7 +51167,7 @@
         <v>45037</v>
       </c>
       <c r="C782" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D782" t="inlineStr">
         <is>
@@ -51224,7 +51224,7 @@
         <v>45037</v>
       </c>
       <c r="C783" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D783" t="inlineStr">
         <is>
@@ -51281,7 +51281,7 @@
         <v>45040</v>
       </c>
       <c r="C784" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D784" t="inlineStr">
         <is>
@@ -51338,7 +51338,7 @@
         <v>45040</v>
       </c>
       <c r="C785" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D785" t="inlineStr">
         <is>
@@ -51395,7 +51395,7 @@
         <v>45040</v>
       </c>
       <c r="C786" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D786" t="inlineStr">
         <is>
@@ -51452,7 +51452,7 @@
         <v>45040</v>
       </c>
       <c r="C787" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D787" t="inlineStr">
         <is>
@@ -51509,7 +51509,7 @@
         <v>45040</v>
       </c>
       <c r="C788" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D788" t="inlineStr">
         <is>
@@ -51566,7 +51566,7 @@
         <v>45041</v>
       </c>
       <c r="C789" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D789" t="inlineStr">
         <is>
@@ -51623,7 +51623,7 @@
         <v>45042</v>
       </c>
       <c r="C790" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D790" t="inlineStr">
         <is>
@@ -51685,7 +51685,7 @@
         <v>45042</v>
       </c>
       <c r="C791" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D791" t="inlineStr">
         <is>
@@ -51747,7 +51747,7 @@
         <v>45042</v>
       </c>
       <c r="C792" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D792" t="inlineStr">
         <is>
@@ -51809,7 +51809,7 @@
         <v>45042</v>
       </c>
       <c r="C793" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D793" t="inlineStr">
         <is>
@@ -51871,7 +51871,7 @@
         <v>45042</v>
       </c>
       <c r="C794" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D794" t="inlineStr">
         <is>
@@ -51933,7 +51933,7 @@
         <v>45044</v>
       </c>
       <c r="C795" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D795" t="inlineStr">
         <is>
@@ -51990,7 +51990,7 @@
         <v>45044</v>
       </c>
       <c r="C796" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D796" t="inlineStr">
         <is>
@@ -52047,7 +52047,7 @@
         <v>45044</v>
       </c>
       <c r="C797" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D797" t="inlineStr">
         <is>
@@ -52104,7 +52104,7 @@
         <v>45044</v>
       </c>
       <c r="C798" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D798" t="inlineStr">
         <is>
@@ -52161,7 +52161,7 @@
         <v>45044</v>
       </c>
       <c r="C799" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D799" t="inlineStr">
         <is>
@@ -52218,7 +52218,7 @@
         <v>45045</v>
       </c>
       <c r="C800" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D800" t="inlineStr">
         <is>
@@ -52280,7 +52280,7 @@
         <v>45045</v>
       </c>
       <c r="C801" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D801" t="inlineStr">
         <is>
@@ -52342,7 +52342,7 @@
         <v>45045</v>
       </c>
       <c r="C802" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D802" t="inlineStr">
         <is>
@@ -52404,7 +52404,7 @@
         <v>45045</v>
       </c>
       <c r="C803" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D803" t="inlineStr">
         <is>
@@ -52466,7 +52466,7 @@
         <v>45045</v>
       </c>
       <c r="C804" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D804" t="inlineStr">
         <is>
@@ -52528,7 +52528,7 @@
         <v>45047</v>
       </c>
       <c r="C805" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D805" t="inlineStr">
         <is>
@@ -52590,7 +52590,7 @@
         <v>45047</v>
       </c>
       <c r="C806" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D806" t="inlineStr">
         <is>
@@ -52652,7 +52652,7 @@
         <v>45048</v>
       </c>
       <c r="C807" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D807" t="inlineStr">
         <is>
@@ -52714,7 +52714,7 @@
         <v>45048</v>
       </c>
       <c r="C808" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D808" t="inlineStr">
         <is>
@@ -52776,7 +52776,7 @@
         <v>45048</v>
       </c>
       <c r="C809" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D809" t="inlineStr">
         <is>
@@ -52838,7 +52838,7 @@
         <v>45048</v>
       </c>
       <c r="C810" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D810" t="inlineStr">
         <is>
@@ -52895,7 +52895,7 @@
         <v>45048</v>
       </c>
       <c r="C811" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D811" t="inlineStr">
         <is>
@@ -52952,7 +52952,7 @@
         <v>45051</v>
       </c>
       <c r="C812" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D812" t="inlineStr">
         <is>
@@ -53009,7 +53009,7 @@
         <v>45051</v>
       </c>
       <c r="C813" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D813" t="inlineStr">
         <is>
@@ -53066,7 +53066,7 @@
         <v>45054</v>
       </c>
       <c r="C814" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D814" t="inlineStr">
         <is>
@@ -53123,7 +53123,7 @@
         <v>45054</v>
       </c>
       <c r="C815" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D815" t="inlineStr">
         <is>
@@ -53180,7 +53180,7 @@
         <v>45054</v>
       </c>
       <c r="C816" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D816" t="inlineStr">
         <is>
@@ -53237,7 +53237,7 @@
         <v>45054</v>
       </c>
       <c r="C817" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D817" t="inlineStr">
         <is>
@@ -53294,7 +53294,7 @@
         <v>45056</v>
       </c>
       <c r="C818" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D818" t="inlineStr">
         <is>
@@ -53351,7 +53351,7 @@
         <v>45057</v>
       </c>
       <c r="C819" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D819" t="inlineStr">
         <is>
@@ -53408,7 +53408,7 @@
         <v>45058</v>
       </c>
       <c r="C820" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D820" t="inlineStr">
         <is>
@@ -53465,7 +53465,7 @@
         <v>45058</v>
       </c>
       <c r="C821" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D821" t="inlineStr">
         <is>
@@ -53522,7 +53522,7 @@
         <v>45058</v>
       </c>
       <c r="C822" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D822" t="inlineStr">
         <is>
@@ -53584,7 +53584,7 @@
         <v>45058</v>
       </c>
       <c r="C823" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D823" t="inlineStr">
         <is>
@@ -53646,7 +53646,7 @@
         <v>45063</v>
       </c>
       <c r="C824" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D824" t="inlineStr">
         <is>
@@ -53703,7 +53703,7 @@
         <v>45063</v>
       </c>
       <c r="C825" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D825" t="inlineStr">
         <is>
@@ -53760,7 +53760,7 @@
         <v>45063</v>
       </c>
       <c r="C826" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D826" t="inlineStr">
         <is>
@@ -53822,7 +53822,7 @@
         <v>45068</v>
       </c>
       <c r="C827" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D827" t="inlineStr">
         <is>
@@ -53879,7 +53879,7 @@
         <v>45070</v>
       </c>
       <c r="C828" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D828" t="inlineStr">
         <is>
@@ -53941,7 +53941,7 @@
         <v>45070</v>
       </c>
       <c r="C829" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D829" t="inlineStr">
         <is>
@@ -54003,7 +54003,7 @@
         <v>45070</v>
       </c>
       <c r="C830" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D830" t="inlineStr">
         <is>
@@ -54065,7 +54065,7 @@
         <v>45071</v>
       </c>
       <c r="C831" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D831" t="inlineStr">
         <is>
@@ -54122,7 +54122,7 @@
         <v>45072</v>
       </c>
       <c r="C832" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D832" t="inlineStr">
         <is>
@@ -54179,7 +54179,7 @@
         <v>45072</v>
       </c>
       <c r="C833" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D833" t="inlineStr">
         <is>
@@ -54236,7 +54236,7 @@
         <v>45072</v>
       </c>
       <c r="C834" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D834" t="inlineStr">
         <is>
@@ -54293,7 +54293,7 @@
         <v>45075</v>
       </c>
       <c r="C835" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D835" t="inlineStr">
         <is>
@@ -54355,7 +54355,7 @@
         <v>45075</v>
       </c>
       <c r="C836" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D836" t="inlineStr">
         <is>
@@ -54417,7 +54417,7 @@
         <v>45075</v>
       </c>
       <c r="C837" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D837" t="inlineStr">
         <is>
@@ -54474,7 +54474,7 @@
         <v>45075</v>
       </c>
       <c r="C838" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D838" t="inlineStr">
         <is>
@@ -54531,7 +54531,7 @@
         <v>45075</v>
       </c>
       <c r="C839" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D839" t="inlineStr">
         <is>
@@ -54588,7 +54588,7 @@
         <v>45076</v>
       </c>
       <c r="C840" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D840" t="inlineStr">
         <is>
@@ -54645,7 +54645,7 @@
         <v>45076</v>
       </c>
       <c r="C841" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D841" t="inlineStr">
         <is>
@@ -54707,7 +54707,7 @@
         <v>45078</v>
       </c>
       <c r="C842" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D842" t="inlineStr">
         <is>
@@ -54769,7 +54769,7 @@
         <v>45079</v>
       </c>
       <c r="C843" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D843" t="inlineStr">
         <is>
@@ -54826,7 +54826,7 @@
         <v>45080</v>
       </c>
       <c r="C844" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D844" t="inlineStr">
         <is>
@@ -54888,7 +54888,7 @@
         <v>45080</v>
       </c>
       <c r="C845" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D845" t="inlineStr">
         <is>
@@ -54950,7 +54950,7 @@
         <v>45082</v>
       </c>
       <c r="C846" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D846" t="inlineStr">
         <is>
@@ -55007,7 +55007,7 @@
         <v>45082</v>
       </c>
       <c r="C847" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D847" t="inlineStr">
         <is>
@@ -55064,7 +55064,7 @@
         <v>45082</v>
       </c>
       <c r="C848" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D848" t="inlineStr">
         <is>
@@ -55121,7 +55121,7 @@
         <v>45083</v>
       </c>
       <c r="C849" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D849" t="inlineStr">
         <is>
@@ -55183,7 +55183,7 @@
         <v>45084</v>
       </c>
       <c r="C850" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D850" t="inlineStr">
         <is>
@@ -55245,7 +55245,7 @@
         <v>45084</v>
       </c>
       <c r="C851" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D851" t="inlineStr">
         <is>
@@ -55307,7 +55307,7 @@
         <v>45084</v>
       </c>
       <c r="C852" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D852" t="inlineStr">
         <is>
@@ -55369,7 +55369,7 @@
         <v>45086</v>
       </c>
       <c r="C853" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D853" t="inlineStr">
         <is>
@@ -55426,7 +55426,7 @@
         <v>45089</v>
       </c>
       <c r="C854" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D854" t="inlineStr">
         <is>
@@ -55483,7 +55483,7 @@
         <v>45089</v>
       </c>
       <c r="C855" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D855" t="inlineStr">
         <is>
@@ -55540,7 +55540,7 @@
         <v>45090</v>
       </c>
       <c r="C856" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D856" t="inlineStr">
         <is>
@@ -55602,7 +55602,7 @@
         <v>45090</v>
       </c>
       <c r="C857" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D857" t="inlineStr">
         <is>
@@ -55664,7 +55664,7 @@
         <v>45090</v>
       </c>
       <c r="C858" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D858" t="inlineStr">
         <is>
@@ -55726,7 +55726,7 @@
         <v>45090</v>
       </c>
       <c r="C859" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D859" t="inlineStr">
         <is>
@@ -55788,7 +55788,7 @@
         <v>45090</v>
       </c>
       <c r="C860" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D860" t="inlineStr">
         <is>
@@ -55850,7 +55850,7 @@
         <v>45093</v>
       </c>
       <c r="C861" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D861" t="inlineStr">
         <is>
@@ -55912,7 +55912,7 @@
         <v>45093</v>
       </c>
       <c r="C862" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D862" t="inlineStr">
         <is>
@@ -55974,7 +55974,7 @@
         <v>45093</v>
       </c>
       <c r="C863" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D863" t="inlineStr">
         <is>
@@ -56031,7 +56031,7 @@
         <v>45096</v>
       </c>
       <c r="C864" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D864" t="inlineStr">
         <is>
@@ -56093,7 +56093,7 @@
         <v>45096</v>
       </c>
       <c r="C865" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D865" t="inlineStr">
         <is>
@@ -56155,7 +56155,7 @@
         <v>45096</v>
       </c>
       <c r="C866" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D866" t="inlineStr">
         <is>
@@ -56217,7 +56217,7 @@
         <v>45097</v>
       </c>
       <c r="C867" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D867" t="inlineStr">
         <is>
@@ -56274,7 +56274,7 @@
         <v>45097</v>
       </c>
       <c r="C868" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D868" t="inlineStr">
         <is>
@@ -56331,7 +56331,7 @@
         <v>45098</v>
       </c>
       <c r="C869" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D869" t="inlineStr">
         <is>
@@ -56393,7 +56393,7 @@
         <v>45102</v>
       </c>
       <c r="C870" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D870" t="inlineStr">
         <is>
@@ -56455,7 +56455,7 @@
         <v>45102</v>
       </c>
       <c r="C871" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D871" t="inlineStr">
         <is>
@@ -56517,7 +56517,7 @@
         <v>45102</v>
       </c>
       <c r="C872" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D872" t="inlineStr">
         <is>
@@ -56579,7 +56579,7 @@
         <v>45102</v>
       </c>
       <c r="C873" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D873" t="inlineStr">
         <is>
@@ -56641,7 +56641,7 @@
         <v>45102</v>
       </c>
       <c r="C874" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D874" t="inlineStr">
         <is>
@@ -56703,7 +56703,7 @@
         <v>45102</v>
       </c>
       <c r="C875" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D875" t="inlineStr">
         <is>
@@ -56765,7 +56765,7 @@
         <v>45102</v>
       </c>
       <c r="C876" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D876" t="inlineStr">
         <is>
@@ -56827,7 +56827,7 @@
         <v>45103</v>
       </c>
       <c r="C877" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D877" t="inlineStr">
         <is>
@@ -56889,7 +56889,7 @@
         <v>45106</v>
       </c>
       <c r="C878" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D878" t="inlineStr">
         <is>
@@ -56951,7 +56951,7 @@
         <v>45106</v>
       </c>
       <c r="C879" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D879" t="inlineStr">
         <is>
@@ -57013,7 +57013,7 @@
         <v>45107</v>
       </c>
       <c r="C880" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D880" t="inlineStr">
         <is>
@@ -57075,7 +57075,7 @@
         <v>45107</v>
       </c>
       <c r="C881" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D881" t="inlineStr">
         <is>
@@ -57137,7 +57137,7 @@
         <v>45110</v>
       </c>
       <c r="C882" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D882" t="inlineStr">
         <is>
@@ -57194,7 +57194,7 @@
         <v>45111</v>
       </c>
       <c r="C883" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D883" t="inlineStr">
         <is>
@@ -57251,7 +57251,7 @@
         <v>45111</v>
       </c>
       <c r="C884" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D884" t="inlineStr">
         <is>
@@ -57308,7 +57308,7 @@
         <v>45112</v>
       </c>
       <c r="C885" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D885" t="inlineStr">
         <is>
@@ -57370,7 +57370,7 @@
         <v>45112</v>
       </c>
       <c r="C886" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D886" t="inlineStr">
         <is>
@@ -57432,7 +57432,7 @@
         <v>45112</v>
       </c>
       <c r="C887" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D887" t="inlineStr">
         <is>
@@ -57494,7 +57494,7 @@
         <v>45112</v>
       </c>
       <c r="C888" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D888" t="inlineStr">
         <is>
@@ -57556,7 +57556,7 @@
         <v>45112</v>
       </c>
       <c r="C889" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D889" t="inlineStr">
         <is>
@@ -57618,7 +57618,7 @@
         <v>45114</v>
       </c>
       <c r="C890" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D890" t="inlineStr">
         <is>
@@ -57680,7 +57680,7 @@
         <v>45114</v>
       </c>
       <c r="C891" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D891" t="inlineStr">
         <is>
@@ -57742,7 +57742,7 @@
         <v>45114</v>
       </c>
       <c r="C892" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D892" t="inlineStr">
         <is>
@@ -57804,7 +57804,7 @@
         <v>45114</v>
       </c>
       <c r="C893" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D893" t="inlineStr">
         <is>
@@ -57866,7 +57866,7 @@
         <v>45114</v>
       </c>
       <c r="C894" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D894" t="inlineStr">
         <is>
@@ -57928,7 +57928,7 @@
         <v>45114</v>
       </c>
       <c r="C895" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D895" t="inlineStr">
         <is>
@@ -57990,7 +57990,7 @@
         <v>45114</v>
       </c>
       <c r="C896" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D896" t="inlineStr">
         <is>
@@ -58052,7 +58052,7 @@
         <v>45114</v>
       </c>
       <c r="C897" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D897" t="inlineStr">
         <is>
@@ -58114,7 +58114,7 @@
         <v>45117</v>
       </c>
       <c r="C898" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D898" t="inlineStr">
         <is>
@@ -58176,7 +58176,7 @@
         <v>45119</v>
       </c>
       <c r="C899" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D899" t="inlineStr">
         <is>
@@ -58238,7 +58238,7 @@
         <v>45119</v>
       </c>
       <c r="C900" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D900" t="inlineStr">
         <is>
@@ -58300,7 +58300,7 @@
         <v>45119</v>
       </c>
       <c r="C901" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D901" t="inlineStr">
         <is>
@@ -58362,7 +58362,7 @@
         <v>45119</v>
       </c>
       <c r="C902" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D902" t="inlineStr">
         <is>
@@ -58424,7 +58424,7 @@
         <v>45120</v>
       </c>
       <c r="C903" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D903" t="inlineStr">
         <is>
@@ -58486,7 +58486,7 @@
         <v>45121</v>
       </c>
       <c r="C904" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D904" t="inlineStr">
         <is>
@@ -58548,7 +58548,7 @@
         <v>45121</v>
       </c>
       <c r="C905" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D905" t="inlineStr">
         <is>
@@ -58610,7 +58610,7 @@
         <v>45122</v>
       </c>
       <c r="C906" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D906" t="inlineStr">
         <is>
@@ -58672,7 +58672,7 @@
         <v>45123</v>
       </c>
       <c r="C907" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D907" t="inlineStr">
         <is>
@@ -58734,7 +58734,7 @@
         <v>45123</v>
       </c>
       <c r="C908" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D908" t="inlineStr">
         <is>
@@ -58796,7 +58796,7 @@
         <v>45124</v>
       </c>
       <c r="C909" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D909" t="inlineStr">
         <is>
@@ -58858,7 +58858,7 @@
         <v>45135</v>
       </c>
       <c r="C910" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D910" t="inlineStr">
         <is>
@@ -58920,7 +58920,7 @@
         <v>45138</v>
       </c>
       <c r="C911" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D911" t="inlineStr">
         <is>
@@ -58977,7 +58977,7 @@
         <v>45139</v>
       </c>
       <c r="C912" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D912" t="inlineStr">
         <is>
@@ -59039,7 +59039,7 @@
         <v>45139</v>
       </c>
       <c r="C913" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D913" t="inlineStr">
         <is>
@@ -59101,7 +59101,7 @@
         <v>45142</v>
       </c>
       <c r="C914" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D914" t="inlineStr">
         <is>
@@ -59163,7 +59163,7 @@
         <v>45142</v>
       </c>
       <c r="C915" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D915" t="inlineStr">
         <is>
@@ -59225,7 +59225,7 @@
         <v>45142</v>
       </c>
       <c r="C916" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D916" t="inlineStr">
         <is>
@@ -59287,7 +59287,7 @@
         <v>45142</v>
       </c>
       <c r="C917" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D917" t="inlineStr">
         <is>
@@ -59349,7 +59349,7 @@
         <v>45146</v>
       </c>
       <c r="C918" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D918" t="inlineStr">
         <is>
@@ -59411,7 +59411,7 @@
         <v>45146</v>
       </c>
       <c r="C919" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D919" t="inlineStr">
         <is>
@@ -59468,7 +59468,7 @@
         <v>45146</v>
       </c>
       <c r="C920" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D920" t="inlineStr">
         <is>
@@ -59530,7 +59530,7 @@
         <v>45146</v>
       </c>
       <c r="C921" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D921" t="inlineStr">
         <is>
@@ -59592,7 +59592,7 @@
         <v>45146</v>
       </c>
       <c r="C922" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D922" t="inlineStr">
         <is>
@@ -59654,7 +59654,7 @@
         <v>45146</v>
       </c>
       <c r="C923" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D923" t="inlineStr">
         <is>
@@ -59716,7 +59716,7 @@
         <v>45146</v>
       </c>
       <c r="C924" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D924" t="inlineStr">
         <is>
@@ -59773,7 +59773,7 @@
         <v>45147</v>
       </c>
       <c r="C925" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D925" t="inlineStr">
         <is>
@@ -59830,7 +59830,7 @@
         <v>45148</v>
       </c>
       <c r="C926" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D926" t="inlineStr">
         <is>
@@ -59892,7 +59892,7 @@
         <v>45149</v>
       </c>
       <c r="C927" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D927" t="inlineStr">
         <is>
@@ -59954,7 +59954,7 @@
         <v>45152</v>
       </c>
       <c r="C928" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D928" t="inlineStr">
         <is>
@@ -60011,7 +60011,7 @@
         <v>45152</v>
       </c>
       <c r="C929" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D929" t="inlineStr">
         <is>
@@ -60073,7 +60073,7 @@
         <v>45154</v>
       </c>
       <c r="C930" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D930" t="inlineStr">
         <is>
@@ -60130,7 +60130,7 @@
         <v>45154</v>
       </c>
       <c r="C931" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D931" t="inlineStr">
         <is>
@@ -60187,7 +60187,7 @@
         <v>45154</v>
       </c>
       <c r="C932" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D932" t="inlineStr">
         <is>
@@ -60244,7 +60244,7 @@
         <v>45154</v>
       </c>
       <c r="C933" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D933" t="inlineStr">
         <is>
@@ -60306,7 +60306,7 @@
         <v>45155</v>
       </c>
       <c r="C934" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D934" t="inlineStr">
         <is>
@@ -60368,7 +60368,7 @@
         <v>45156</v>
       </c>
       <c r="C935" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D935" t="inlineStr">
         <is>
@@ -60425,7 +60425,7 @@
         <v>45157</v>
       </c>
       <c r="C936" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D936" t="inlineStr">
         <is>
@@ -60487,7 +60487,7 @@
         <v>45157</v>
       </c>
       <c r="C937" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D937" t="inlineStr">
         <is>
@@ -60549,7 +60549,7 @@
         <v>45157</v>
       </c>
       <c r="C938" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D938" t="inlineStr">
         <is>
@@ -60611,7 +60611,7 @@
         <v>45160</v>
       </c>
       <c r="C939" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D939" t="inlineStr">
         <is>
@@ -60668,7 +60668,7 @@
         <v>45160</v>
       </c>
       <c r="C940" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D940" t="inlineStr">
         <is>
@@ -60725,7 +60725,7 @@
         <v>45160</v>
       </c>
       <c r="C941" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D941" t="inlineStr">
         <is>
@@ -60787,7 +60787,7 @@
         <v>45160</v>
       </c>
       <c r="C942" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D942" t="inlineStr">
         <is>
@@ -60844,7 +60844,7 @@
         <v>45161</v>
       </c>
       <c r="C943" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D943" t="inlineStr">
         <is>
@@ -60901,7 +60901,7 @@
         <v>45161</v>
       </c>
       <c r="C944" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D944" t="inlineStr">
         <is>
@@ -60963,7 +60963,7 @@
         <v>45161</v>
       </c>
       <c r="C945" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D945" t="inlineStr">
         <is>
@@ -61025,7 +61025,7 @@
         <v>45162</v>
       </c>
       <c r="C946" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D946" t="inlineStr">
         <is>
@@ -61087,7 +61087,7 @@
         <v>45162</v>
       </c>
       <c r="C947" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D947" t="inlineStr">
         <is>
@@ -61149,7 +61149,7 @@
         <v>45162</v>
       </c>
       <c r="C948" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D948" t="inlineStr">
         <is>
@@ -61211,7 +61211,7 @@
         <v>45163</v>
       </c>
       <c r="C949" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D949" t="inlineStr">
         <is>
@@ -61268,7 +61268,7 @@
         <v>45169</v>
       </c>
       <c r="C950" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D950" t="inlineStr">
         <is>
@@ -61330,7 +61330,7 @@
         <v>45170</v>
       </c>
       <c r="C951" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D951" t="inlineStr">
         <is>
@@ -61387,7 +61387,7 @@
         <v>45172</v>
       </c>
       <c r="C952" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D952" t="inlineStr">
         <is>
@@ -61444,7 +61444,7 @@
         <v>45173</v>
       </c>
       <c r="C953" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D953" t="inlineStr">
         <is>
@@ -61506,7 +61506,7 @@
         <v>45173</v>
       </c>
       <c r="C954" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D954" t="inlineStr">
         <is>
@@ -61568,7 +61568,7 @@
         <v>45173</v>
       </c>
       <c r="C955" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D955" t="inlineStr">
         <is>
@@ -61630,7 +61630,7 @@
         <v>45174</v>
       </c>
       <c r="C956" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D956" t="inlineStr">
         <is>
@@ -61692,7 +61692,7 @@
         <v>45175</v>
       </c>
       <c r="C957" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D957" t="inlineStr">
         <is>
@@ -61754,7 +61754,7 @@
         <v>45176</v>
       </c>
       <c r="C958" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D958" t="inlineStr">
         <is>
@@ -61811,7 +61811,7 @@
         <v>45176</v>
       </c>
       <c r="C959" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D959" t="inlineStr">
         <is>
@@ -61868,7 +61868,7 @@
         <v>45187</v>
       </c>
       <c r="C960" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D960" t="inlineStr">
         <is>
@@ -61930,7 +61930,7 @@
         <v>45187</v>
       </c>
       <c r="C961" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D961" t="inlineStr">
         <is>
@@ -61992,7 +61992,7 @@
         <v>45187</v>
       </c>
       <c r="C962" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D962" t="inlineStr">
         <is>
@@ -62054,7 +62054,7 @@
         <v>45187</v>
       </c>
       <c r="C963" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D963" t="inlineStr">
         <is>
@@ -62111,7 +62111,7 @@
         <v>45189</v>
       </c>
       <c r="C964" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D964" t="inlineStr">
         <is>
@@ -62168,7 +62168,7 @@
         <v>45189</v>
       </c>
       <c r="C965" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D965" t="inlineStr">
         <is>
@@ -62230,7 +62230,7 @@
         <v>45191</v>
       </c>
       <c r="C966" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D966" t="inlineStr">
         <is>
@@ -62292,7 +62292,7 @@
         <v>45194</v>
       </c>
       <c r="C967" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D967" t="inlineStr">
         <is>
@@ -62354,7 +62354,7 @@
         <v>45194</v>
       </c>
       <c r="C968" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D968" t="inlineStr">
         <is>
@@ -62416,7 +62416,7 @@
         <v>45194</v>
       </c>
       <c r="C969" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D969" t="inlineStr">
         <is>
@@ -62478,7 +62478,7 @@
         <v>45194</v>
       </c>
       <c r="C970" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D970" t="inlineStr">
         <is>
@@ -62540,7 +62540,7 @@
         <v>45194</v>
       </c>
       <c r="C971" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D971" t="inlineStr">
         <is>
@@ -62602,7 +62602,7 @@
         <v>45194</v>
       </c>
       <c r="C972" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D972" t="inlineStr">
         <is>
@@ -62664,7 +62664,7 @@
         <v>45194</v>
       </c>
       <c r="C973" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D973" t="inlineStr">
         <is>
@@ -62726,7 +62726,7 @@
         <v>45194</v>
       </c>
       <c r="C974" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D974" t="inlineStr">
         <is>
@@ -62783,7 +62783,7 @@
         <v>45195</v>
       </c>
       <c r="C975" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D975" t="inlineStr">
         <is>
@@ -62840,7 +62840,7 @@
         <v>45196</v>
       </c>
       <c r="C976" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D976" t="inlineStr">
         <is>
@@ -62897,7 +62897,7 @@
         <v>45196</v>
       </c>
       <c r="C977" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D977" t="inlineStr">
         <is>
@@ -62959,7 +62959,7 @@
         <v>45197</v>
       </c>
       <c r="C978" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D978" t="inlineStr">
         <is>
@@ -63016,7 +63016,7 @@
         <v>45198</v>
       </c>
       <c r="C979" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D979" t="inlineStr">
         <is>
@@ -63073,7 +63073,7 @@
         <v>45201</v>
       </c>
       <c r="C980" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D980" t="inlineStr">
         <is>
@@ -63135,7 +63135,7 @@
         <v>45201</v>
       </c>
       <c r="C981" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D981" t="inlineStr">
         <is>
@@ -63192,7 +63192,7 @@
         <v>45202</v>
       </c>
       <c r="C982" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D982" t="inlineStr">
         <is>
@@ -63249,7 +63249,7 @@
         <v>45202</v>
       </c>
       <c r="C983" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D983" t="inlineStr">
         <is>
@@ -63311,7 +63311,7 @@
         <v>45202</v>
       </c>
       <c r="C984" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D984" t="inlineStr">
         <is>
@@ -63368,7 +63368,7 @@
         <v>45203</v>
       </c>
       <c r="C985" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D985" t="inlineStr">
         <is>
@@ -63430,7 +63430,7 @@
         <v>45204</v>
       </c>
       <c r="C986" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D986" t="inlineStr">
         <is>
@@ -63487,7 +63487,7 @@
         <v>45205</v>
       </c>
       <c r="C987" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D987" t="inlineStr">
         <is>
@@ -63549,7 +63549,7 @@
         <v>45208</v>
       </c>
       <c r="C988" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D988" t="inlineStr">
         <is>
@@ -63606,7 +63606,7 @@
         <v>45209</v>
       </c>
       <c r="C989" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D989" t="inlineStr">
         <is>
@@ -63668,7 +63668,7 @@
         <v>45210</v>
       </c>
       <c r="C990" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D990" t="inlineStr">
         <is>
@@ -63725,7 +63725,7 @@
         <v>45210</v>
       </c>
       <c r="C991" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D991" t="inlineStr">
         <is>
@@ -63787,7 +63787,7 @@
         <v>45210</v>
       </c>
       <c r="C992" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D992" t="inlineStr">
         <is>
@@ -63849,7 +63849,7 @@
         <v>45210</v>
       </c>
       <c r="C993" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D993" t="inlineStr">
         <is>
@@ -63906,7 +63906,7 @@
         <v>45212</v>
       </c>
       <c r="C994" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D994" t="inlineStr">
         <is>
@@ -63968,7 +63968,7 @@
         <v>45212</v>
       </c>
       <c r="C995" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D995" t="inlineStr">
         <is>
@@ -64030,7 +64030,7 @@
         <v>45212</v>
       </c>
       <c r="C996" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D996" t="inlineStr">
         <is>
@@ -64092,7 +64092,7 @@
         <v>45213</v>
       </c>
       <c r="C997" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D997" t="inlineStr">
         <is>
@@ -64149,7 +64149,7 @@
         <v>45213</v>
       </c>
       <c r="C998" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D998" t="inlineStr">
         <is>
@@ -64206,7 +64206,7 @@
         <v>45213</v>
       </c>
       <c r="C999" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D999" t="inlineStr">
         <is>
@@ -64268,7 +64268,7 @@
         <v>45215</v>
       </c>
       <c r="C1000" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1000" t="inlineStr">
         <is>
@@ -64325,7 +64325,7 @@
         <v>45215</v>
       </c>
       <c r="C1001" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1001" t="inlineStr">
         <is>
@@ -64387,7 +64387,7 @@
         <v>45215</v>
       </c>
       <c r="C1002" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1002" t="inlineStr">
         <is>
@@ -64449,7 +64449,7 @@
         <v>45215</v>
       </c>
       <c r="C1003" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1003" t="inlineStr">
         <is>
@@ -64511,7 +64511,7 @@
         <v>45218</v>
       </c>
       <c r="C1004" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1004" t="inlineStr">
         <is>
@@ -64568,7 +64568,7 @@
         <v>45225</v>
       </c>
       <c r="C1005" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1005" t="inlineStr">
         <is>
@@ -64625,7 +64625,7 @@
         <v>45225</v>
       </c>
       <c r="C1006" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1006" t="inlineStr">
         <is>
@@ -64682,7 +64682,7 @@
         <v>45225</v>
       </c>
       <c r="C1007" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1007" t="inlineStr">
         <is>
@@ -64744,7 +64744,7 @@
         <v>45225</v>
       </c>
       <c r="C1008" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1008" t="inlineStr">
         <is>
@@ -64801,7 +64801,7 @@
         <v>45225</v>
       </c>
       <c r="C1009" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1009" t="inlineStr">
         <is>
@@ -64863,7 +64863,7 @@
         <v>45225</v>
       </c>
       <c r="C1010" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1010" t="inlineStr">
         <is>
@@ -64920,7 +64920,7 @@
         <v>45226</v>
       </c>
       <c r="C1011" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1011" t="inlineStr">
         <is>
@@ -64982,7 +64982,7 @@
         <v>45229</v>
       </c>
       <c r="C1012" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1012" t="inlineStr">
         <is>
@@ -65039,7 +65039,7 @@
         <v>45229</v>
       </c>
       <c r="C1013" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1013" t="inlineStr">
         <is>
@@ -65096,7 +65096,7 @@
         <v>45230</v>
       </c>
       <c r="C1014" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1014" t="inlineStr">
         <is>
@@ -65153,7 +65153,7 @@
         <v>45230</v>
       </c>
       <c r="C1015" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1015" t="inlineStr">
         <is>
@@ -65210,7 +65210,7 @@
         <v>45230</v>
       </c>
       <c r="C1016" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1016" t="inlineStr">
         <is>
@@ -65272,7 +65272,7 @@
         <v>45230</v>
       </c>
       <c r="C1017" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1017" t="inlineStr">
         <is>
@@ -65329,7 +65329,7 @@
         <v>45230</v>
       </c>
       <c r="C1018" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1018" t="inlineStr">
         <is>
@@ -65386,7 +65386,7 @@
         <v>45230</v>
       </c>
       <c r="C1019" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1019" t="inlineStr">
         <is>
@@ -65448,7 +65448,7 @@
         <v>45230</v>
       </c>
       <c r="C1020" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1020" t="inlineStr">
         <is>
@@ -65510,7 +65510,7 @@
         <v>45232</v>
       </c>
       <c r="C1021" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1021" t="inlineStr">
         <is>
@@ -65567,7 +65567,7 @@
         <v>45233</v>
       </c>
       <c r="C1022" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1022" t="inlineStr">
         <is>
@@ -65629,7 +65629,7 @@
         <v>45233</v>
       </c>
       <c r="C1023" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1023" t="inlineStr">
         <is>
@@ -65691,7 +65691,7 @@
         <v>45233</v>
       </c>
       <c r="C1024" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1024" t="inlineStr">
         <is>
@@ -65753,7 +65753,7 @@
         <v>45237</v>
       </c>
       <c r="C1025" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1025" t="inlineStr">
         <is>
@@ -65815,7 +65815,7 @@
         <v>45238</v>
       </c>
       <c r="C1026" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1026" t="inlineStr">
         <is>
@@ -65877,7 +65877,7 @@
         <v>45238</v>
       </c>
       <c r="C1027" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1027" t="inlineStr">
         <is>
@@ -65939,7 +65939,7 @@
         <v>45239</v>
       </c>
       <c r="C1028" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1028" t="inlineStr">
         <is>
@@ -65996,7 +65996,7 @@
         <v>45240</v>
       </c>
       <c r="C1029" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1029" t="inlineStr">
         <is>
@@ -66058,7 +66058,7 @@
         <v>45243</v>
       </c>
       <c r="C1030" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1030" t="inlineStr">
         <is>
@@ -66120,7 +66120,7 @@
         <v>45243</v>
       </c>
       <c r="C1031" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1031" t="inlineStr">
         <is>
@@ -66182,7 +66182,7 @@
         <v>45244</v>
       </c>
       <c r="C1032" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1032" t="inlineStr">
         <is>
@@ -66239,7 +66239,7 @@
         <v>45244</v>
       </c>
       <c r="C1033" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1033" t="inlineStr">
         <is>
@@ -66296,7 +66296,7 @@
         <v>45244</v>
       </c>
       <c r="C1034" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1034" t="inlineStr">
         <is>
@@ -66353,7 +66353,7 @@
         <v>45244</v>
       </c>
       <c r="C1035" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1035" t="inlineStr">
         <is>
@@ -66410,7 +66410,7 @@
         <v>45244</v>
       </c>
       <c r="C1036" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1036" t="inlineStr">
         <is>
@@ -66467,7 +66467,7 @@
         <v>45250</v>
       </c>
       <c r="C1037" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1037" t="inlineStr">
         <is>
@@ -66529,7 +66529,7 @@
         <v>45250</v>
       </c>
       <c r="C1038" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1038" t="inlineStr">
         <is>
@@ -66586,7 +66586,7 @@
         <v>45250</v>
       </c>
       <c r="C1039" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1039" t="inlineStr">
         <is>
@@ -66643,7 +66643,7 @@
         <v>45250</v>
       </c>
       <c r="C1040" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1040" t="inlineStr">
         <is>
@@ -66700,7 +66700,7 @@
         <v>45250</v>
       </c>
       <c r="C1041" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1041" t="inlineStr">
         <is>
@@ -66757,7 +66757,7 @@
         <v>45250</v>
       </c>
       <c r="C1042" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1042" t="inlineStr">
         <is>
@@ -66819,7 +66819,7 @@
         <v>45252</v>
       </c>
       <c r="C1043" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1043" t="inlineStr">
         <is>
@@ -66876,7 +66876,7 @@
         <v>45252</v>
       </c>
       <c r="C1044" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1044" t="inlineStr">
         <is>
@@ -66933,7 +66933,7 @@
         <v>45252</v>
       </c>
       <c r="C1045" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1045" t="inlineStr">
         <is>
@@ -66990,7 +66990,7 @@
         <v>45253</v>
       </c>
       <c r="C1046" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1046" t="inlineStr">
         <is>
@@ -67047,7 +67047,7 @@
         <v>45253</v>
       </c>
       <c r="C1047" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1047" t="inlineStr">
         <is>
@@ -67104,7 +67104,7 @@
         <v>45253</v>
       </c>
       <c r="C1048" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1048" t="inlineStr">
         <is>
@@ -67161,7 +67161,7 @@
         <v>45253</v>
       </c>
       <c r="C1049" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1049" t="inlineStr">
         <is>
@@ -67218,7 +67218,7 @@
         <v>45253</v>
       </c>
       <c r="C1050" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1050" t="inlineStr">
         <is>
@@ -67275,7 +67275,7 @@
         <v>45253</v>
       </c>
       <c r="C1051" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1051" t="inlineStr">
         <is>
@@ -67332,7 +67332,7 @@
         <v>45257</v>
       </c>
       <c r="C1052" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1052" t="inlineStr">
         <is>
@@ -67389,7 +67389,7 @@
         <v>45258</v>
       </c>
       <c r="C1053" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1053" t="inlineStr">
         <is>
@@ -67451,7 +67451,7 @@
         <v>45259</v>
       </c>
       <c r="C1054" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1054" t="inlineStr">
         <is>
@@ -67508,7 +67508,7 @@
         <v>45259</v>
       </c>
       <c r="C1055" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1055" t="inlineStr">
         <is>
@@ -67565,7 +67565,7 @@
         <v>45259</v>
       </c>
       <c r="C1056" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1056" t="inlineStr">
         <is>
@@ -67622,7 +67622,7 @@
         <v>45260</v>
       </c>
       <c r="C1057" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1057" t="inlineStr">
         <is>
@@ -67679,7 +67679,7 @@
         <v>45261</v>
       </c>
       <c r="C1058" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1058" t="inlineStr">
         <is>
@@ -67736,7 +67736,7 @@
         <v>45264</v>
       </c>
       <c r="C1059" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1059" t="inlineStr">
         <is>
@@ -67798,7 +67798,7 @@
         <v>45264</v>
       </c>
       <c r="C1060" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1060" t="inlineStr">
         <is>
@@ -67860,7 +67860,7 @@
         <v>45271</v>
       </c>
       <c r="C1061" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1061" t="inlineStr">
         <is>
@@ -67917,7 +67917,7 @@
         <v>45282</v>
       </c>
       <c r="C1062" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1062" t="inlineStr">
         <is>
@@ -67979,7 +67979,7 @@
         <v>45313</v>
       </c>
       <c r="C1063" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1063" t="inlineStr">
         <is>
@@ -68036,7 +68036,7 @@
         <v>45315</v>
       </c>
       <c r="C1064" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1064" t="inlineStr">
         <is>
@@ -68093,7 +68093,7 @@
         <v>45329</v>
       </c>
       <c r="C1065" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1065" t="inlineStr">
         <is>
@@ -68150,7 +68150,7 @@
         <v>45329</v>
       </c>
       <c r="C1066" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1066" t="inlineStr">
         <is>
@@ -68200,14 +68200,14 @@
     <row r="1067" ht="15" customHeight="1">
       <c r="A1067" t="inlineStr">
         <is>
-          <t>A 5149-2024</t>
+          <t>A 5161-2024</t>
         </is>
       </c>
       <c r="B1067" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1067" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1067" t="inlineStr">
         <is>
@@ -68220,7 +68220,7 @@
         </is>
       </c>
       <c r="G1067" t="n">
-        <v>1.1</v>
+        <v>5.5</v>
       </c>
       <c r="H1067" t="n">
         <v>0</v>
@@ -68257,14 +68257,14 @@
     <row r="1068" ht="15" customHeight="1">
       <c r="A1068" t="inlineStr">
         <is>
-          <t>A 5161-2024</t>
+          <t>A 5198-2024</t>
         </is>
       </c>
       <c r="B1068" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1068" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1068" t="inlineStr">
         <is>
@@ -68276,8 +68276,13 @@
           <t>ÖSTHAMMAR</t>
         </is>
       </c>
+      <c r="F1068" t="inlineStr">
+        <is>
+          <t>Övriga Aktiebolag</t>
+        </is>
+      </c>
       <c r="G1068" t="n">
-        <v>5.5</v>
+        <v>2.4</v>
       </c>
       <c r="H1068" t="n">
         <v>0</v>
@@ -68321,7 +68326,7 @@
         <v>45330</v>
       </c>
       <c r="C1069" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1069" t="inlineStr">
         <is>
@@ -68371,14 +68376,14 @@
     <row r="1070" ht="15" customHeight="1">
       <c r="A1070" t="inlineStr">
         <is>
-          <t>A 5198-2024</t>
+          <t>A 5149-2024</t>
         </is>
       </c>
       <c r="B1070" s="1" t="n">
         <v>45330</v>
       </c>
       <c r="C1070" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1070" t="inlineStr">
         <is>
@@ -68390,13 +68395,8 @@
           <t>ÖSTHAMMAR</t>
         </is>
       </c>
-      <c r="F1070" t="inlineStr">
-        <is>
-          <t>Övriga Aktiebolag</t>
-        </is>
-      </c>
       <c r="G1070" t="n">
-        <v>2.4</v>
+        <v>1.1</v>
       </c>
       <c r="H1070" t="n">
         <v>0</v>
@@ -68440,7 +68440,7 @@
         <v>45330</v>
       </c>
       <c r="C1071" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1071" t="inlineStr">
         <is>
@@ -68490,14 +68490,14 @@
     <row r="1072" ht="15" customHeight="1">
       <c r="A1072" t="inlineStr">
         <is>
-          <t>A 5860-2024</t>
+          <t>A 5851-2024</t>
         </is>
       </c>
       <c r="B1072" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C1072" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1072" t="inlineStr">
         <is>
@@ -68510,7 +68510,7 @@
         </is>
       </c>
       <c r="G1072" t="n">
-        <v>2.1</v>
+        <v>1.1</v>
       </c>
       <c r="H1072" t="n">
         <v>0</v>
@@ -68547,14 +68547,14 @@
     <row r="1073" ht="15" customHeight="1">
       <c r="A1073" t="inlineStr">
         <is>
-          <t>A 5851-2024</t>
+          <t>A 5860-2024</t>
         </is>
       </c>
       <c r="B1073" s="1" t="n">
         <v>45335</v>
       </c>
       <c r="C1073" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1073" t="inlineStr">
         <is>
@@ -68567,7 +68567,7 @@
         </is>
       </c>
       <c r="G1073" t="n">
-        <v>1.1</v>
+        <v>2.1</v>
       </c>
       <c r="H1073" t="n">
         <v>0</v>
@@ -68604,14 +68604,14 @@
     <row r="1074" ht="15" customHeight="1">
       <c r="A1074" t="inlineStr">
         <is>
-          <t>A 6121-2024</t>
+          <t>A 6102-2024</t>
         </is>
       </c>
       <c r="B1074" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1074" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1074" t="inlineStr">
         <is>
@@ -68624,7 +68624,7 @@
         </is>
       </c>
       <c r="G1074" t="n">
-        <v>0.4</v>
+        <v>2.7</v>
       </c>
       <c r="H1074" t="n">
         <v>0</v>
@@ -68661,14 +68661,14 @@
     <row r="1075" ht="15" customHeight="1">
       <c r="A1075" t="inlineStr">
         <is>
-          <t>A 6102-2024</t>
+          <t>A 6106-2024</t>
         </is>
       </c>
       <c r="B1075" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1075" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1075" t="inlineStr">
         <is>
@@ -68681,7 +68681,7 @@
         </is>
       </c>
       <c r="G1075" t="n">
-        <v>2.7</v>
+        <v>0.6</v>
       </c>
       <c r="H1075" t="n">
         <v>0</v>
@@ -68718,14 +68718,14 @@
     <row r="1076" ht="15" customHeight="1">
       <c r="A1076" t="inlineStr">
         <is>
-          <t>A 6106-2024</t>
+          <t>A 6143-2024</t>
         </is>
       </c>
       <c r="B1076" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1076" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1076" t="inlineStr">
         <is>
@@ -68738,7 +68738,7 @@
         </is>
       </c>
       <c r="G1076" t="n">
-        <v>0.6</v>
+        <v>0.7</v>
       </c>
       <c r="H1076" t="n">
         <v>0</v>
@@ -68775,14 +68775,14 @@
     <row r="1077" ht="15" customHeight="1">
       <c r="A1077" t="inlineStr">
         <is>
-          <t>A 6143-2024</t>
+          <t>A 6120-2024</t>
         </is>
       </c>
       <c r="B1077" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1077" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1077" t="inlineStr">
         <is>
@@ -68832,14 +68832,14 @@
     <row r="1078" ht="15" customHeight="1">
       <c r="A1078" t="inlineStr">
         <is>
-          <t>A 6120-2024</t>
+          <t>A 6121-2024</t>
         </is>
       </c>
       <c r="B1078" s="1" t="n">
         <v>45337</v>
       </c>
       <c r="C1078" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1078" t="inlineStr">
         <is>
@@ -68852,7 +68852,7 @@
         </is>
       </c>
       <c r="G1078" t="n">
-        <v>0.7</v>
+        <v>0.4</v>
       </c>
       <c r="H1078" t="n">
         <v>0</v>
@@ -68896,7 +68896,7 @@
         <v>45338</v>
       </c>
       <c r="C1079" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1079" t="inlineStr">
         <is>
@@ -68953,7 +68953,7 @@
         <v>45341</v>
       </c>
       <c r="C1080" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1080" t="inlineStr">
         <is>
@@ -69010,7 +69010,7 @@
         <v>45341</v>
       </c>
       <c r="C1081" s="1" t="n">
-        <v>45351</v>
+        <v>45352</v>
       </c>
       <c r="D1081" t="inlineStr">
         <is>

--- a/Översikt ÖSTHAMMAR.xlsx
+++ b/Översikt ÖSTHAMMAR.xlsx
@@ -569,7 +569,7 @@
         <v>45098</v>
       </c>
       <c r="C2" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -698,7 +698,7 @@
         <v>44063</v>
       </c>
       <c r="C3" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -819,7 +819,7 @@
         <v>45182</v>
       </c>
       <c r="C4" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -938,7 +938,7 @@
         <v>43689</v>
       </c>
       <c r="C5" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1047,7 +1047,7 @@
         <v>44077</v>
       </c>
       <c r="C6" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1151,7 +1151,7 @@
         <v>45077</v>
       </c>
       <c r="C7" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1262,7 +1262,7 @@
         <v>44439</v>
       </c>
       <c r="C8" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1356,7 +1356,7 @@
         <v>44482</v>
       </c>
       <c r="C9" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>44698</v>
       </c>
       <c r="C10" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D10" t="inlineStr">
         <is>
@@ -1544,7 +1544,7 @@
         <v>44771</v>
       </c>
       <c r="C11" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D11" t="inlineStr">
         <is>
@@ -1637,7 +1637,7 @@
         <v>43647</v>
       </c>
       <c r="C12" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D12" t="inlineStr">
         <is>
@@ -1729,7 +1729,7 @@
         <v>44789</v>
       </c>
       <c r="C13" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D13" t="inlineStr">
         <is>
@@ -1825,7 +1825,7 @@
         <v>44312</v>
       </c>
       <c r="C14" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -1916,7 +1916,7 @@
         <v>44335</v>
       </c>
       <c r="C15" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D15" t="inlineStr">
         <is>
@@ -2011,7 +2011,7 @@
         <v>45246</v>
       </c>
       <c r="C16" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D16" t="inlineStr">
         <is>
@@ -2107,7 +2107,7 @@
         <v>44021</v>
       </c>
       <c r="C17" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D17" t="inlineStr">
         <is>
@@ -2201,7 +2201,7 @@
         <v>44387</v>
       </c>
       <c r="C18" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D18" t="inlineStr">
         <is>
@@ -2300,7 +2300,7 @@
         <v>44779</v>
       </c>
       <c r="C19" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D19" t="inlineStr">
         <is>
@@ -2398,7 +2398,7 @@
         <v>45076</v>
       </c>
       <c r="C20" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D20" t="inlineStr">
         <is>
@@ -2497,7 +2497,7 @@
         <v>45303</v>
       </c>
       <c r="C21" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D21" t="inlineStr">
         <is>
@@ -2592,7 +2592,7 @@
         <v>43447</v>
       </c>
       <c r="C22" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D22" t="inlineStr">
         <is>
@@ -2685,7 +2685,7 @@
         <v>43538</v>
       </c>
       <c r="C23" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -2774,7 +2774,7 @@
         <v>43635</v>
       </c>
       <c r="C24" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -2868,7 +2868,7 @@
         <v>44021</v>
       </c>
       <c r="C25" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -2961,7 +2961,7 @@
         <v>44546</v>
       </c>
       <c r="C26" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3050,7 +3050,7 @@
         <v>44559</v>
       </c>
       <c r="C27" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -3139,7 +3139,7 @@
         <v>44572</v>
       </c>
       <c r="C28" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D28" t="inlineStr">
         <is>
@@ -3228,7 +3228,7 @@
         <v>44614</v>
       </c>
       <c r="C29" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D29" t="inlineStr">
         <is>
@@ -3317,7 +3317,7 @@
         <v>44662</v>
       </c>
       <c r="C30" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D30" t="inlineStr">
         <is>
@@ -3406,7 +3406,7 @@
         <v>44727</v>
       </c>
       <c r="C31" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D31" t="inlineStr">
         <is>
@@ -3495,7 +3495,7 @@
         <v>44819</v>
       </c>
       <c r="C32" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D32" t="inlineStr">
         <is>
@@ -3588,7 +3588,7 @@
         <v>44837</v>
       </c>
       <c r="C33" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D33" t="inlineStr">
         <is>
@@ -3682,7 +3682,7 @@
         <v>45006</v>
       </c>
       <c r="C34" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D34" t="inlineStr">
         <is>
@@ -3771,7 +3771,7 @@
         <v>45076</v>
       </c>
       <c r="C35" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D35" t="inlineStr">
         <is>
@@ -3869,7 +3869,7 @@
         <v>45099</v>
       </c>
       <c r="C36" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D36" t="inlineStr">
         <is>
@@ -3958,7 +3958,7 @@
         <v>45201</v>
       </c>
       <c r="C37" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D37" t="inlineStr">
         <is>
@@ -4047,7 +4047,7 @@
         <v>45205</v>
       </c>
       <c r="C38" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D38" t="inlineStr">
         <is>
@@ -4136,7 +4136,7 @@
         <v>45244</v>
       </c>
       <c r="C39" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D39" t="inlineStr">
         <is>
@@ -4233,7 +4233,7 @@
         <v>43573</v>
       </c>
       <c r="C40" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D40" t="inlineStr">
         <is>
@@ -4321,7 +4321,7 @@
         <v>44376</v>
       </c>
       <c r="C41" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -4409,7 +4409,7 @@
         <v>44684</v>
       </c>
       <c r="C42" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D42" t="inlineStr">
         <is>
@@ -4505,7 +4505,7 @@
         <v>44858</v>
       </c>
       <c r="C43" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D43" t="inlineStr">
         <is>
@@ -4593,7 +4593,7 @@
         <v>44874</v>
       </c>
       <c r="C44" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D44" t="inlineStr">
         <is>
@@ -4686,7 +4686,7 @@
         <v>45092</v>
       </c>
       <c r="C45" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D45" t="inlineStr">
         <is>
@@ -4779,7 +4779,7 @@
         <v>43480</v>
       </c>
       <c r="C46" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D46" t="inlineStr">
         <is>
@@ -4870,7 +4870,7 @@
         <v>43875</v>
       </c>
       <c r="C47" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D47" t="inlineStr">
         <is>
@@ -4962,7 +4962,7 @@
         <v>44376</v>
       </c>
       <c r="C48" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D48" t="inlineStr">
         <is>
@@ -5049,7 +5049,7 @@
         <v>44474</v>
       </c>
       <c r="C49" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D49" t="inlineStr">
         <is>
@@ -5141,7 +5141,7 @@
         <v>44531</v>
       </c>
       <c r="C50" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -5228,7 +5228,7 @@
         <v>44739</v>
       </c>
       <c r="C51" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -5324,7 +5324,7 @@
         <v>44875</v>
       </c>
       <c r="C52" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -5411,7 +5411,7 @@
         <v>44984</v>
       </c>
       <c r="C53" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -5498,7 +5498,7 @@
         <v>44998</v>
       </c>
       <c r="C54" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D54" t="inlineStr">
         <is>
@@ -5585,7 +5585,7 @@
         <v>45002</v>
       </c>
       <c r="C55" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -5672,7 +5672,7 @@
         <v>45016</v>
       </c>
       <c r="C56" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -5759,7 +5759,7 @@
         <v>45054</v>
       </c>
       <c r="C57" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -5846,7 +5846,7 @@
         <v>45055</v>
       </c>
       <c r="C58" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -5937,7 +5937,7 @@
         <v>45190</v>
       </c>
       <c r="C59" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
@@ -6029,7 +6029,7 @@
         <v>45230</v>
       </c>
       <c r="C60" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
@@ -6116,7 +6116,7 @@
         <v>45246</v>
       </c>
       <c r="C61" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
@@ -6208,7 +6208,7 @@
         <v>45246</v>
       </c>
       <c r="C62" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D62" t="inlineStr">
         <is>
@@ -6300,7 +6300,7 @@
         <v>43369</v>
       </c>
       <c r="C63" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D63" t="inlineStr">
         <is>
@@ -6395,7 +6395,7 @@
         <v>43508</v>
       </c>
       <c r="C64" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D64" t="inlineStr">
         <is>
@@ -6481,7 +6481,7 @@
         <v>43846</v>
       </c>
       <c r="C65" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -6567,7 +6567,7 @@
         <v>43882</v>
       </c>
       <c r="C66" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D66" t="inlineStr">
         <is>
@@ -6658,7 +6658,7 @@
         <v>44077</v>
       </c>
       <c r="C67" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D67" t="inlineStr">
         <is>
@@ -6744,7 +6744,7 @@
         <v>44148</v>
       </c>
       <c r="C68" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -6835,7 +6835,7 @@
         <v>44235</v>
       </c>
       <c r="C69" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
@@ -6921,7 +6921,7 @@
         <v>44495</v>
       </c>
       <c r="C70" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -7007,7 +7007,7 @@
         <v>44525</v>
       </c>
       <c r="C71" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
@@ -7093,7 +7093,7 @@
         <v>44529</v>
       </c>
       <c r="C72" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -7179,7 +7179,7 @@
         <v>44555</v>
       </c>
       <c r="C73" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D73" t="inlineStr">
         <is>
@@ -7265,7 +7265,7 @@
         <v>44610</v>
       </c>
       <c r="C74" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D74" t="inlineStr">
         <is>
@@ -7351,7 +7351,7 @@
         <v>44644</v>
       </c>
       <c r="C75" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D75" t="inlineStr">
         <is>
@@ -7437,7 +7437,7 @@
         <v>44729</v>
       </c>
       <c r="C76" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D76" t="inlineStr">
         <is>
@@ -7523,7 +7523,7 @@
         <v>44778</v>
       </c>
       <c r="C77" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D77" t="inlineStr">
         <is>
@@ -7609,7 +7609,7 @@
         <v>44865</v>
       </c>
       <c r="C78" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
@@ -7700,7 +7700,7 @@
         <v>44874</v>
       </c>
       <c r="C79" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D79" t="inlineStr">
         <is>
@@ -7791,7 +7791,7 @@
         <v>44874</v>
       </c>
       <c r="C80" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
@@ -7882,7 +7882,7 @@
         <v>44967</v>
       </c>
       <c r="C81" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -7968,7 +7968,7 @@
         <v>45063</v>
       </c>
       <c r="C82" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D82" t="inlineStr">
         <is>
@@ -8059,7 +8059,7 @@
         <v>45063</v>
       </c>
       <c r="C83" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D83" t="inlineStr">
         <is>
@@ -8150,7 +8150,7 @@
         <v>45092</v>
       </c>
       <c r="C84" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D84" t="inlineStr">
         <is>
@@ -8241,7 +8241,7 @@
         <v>45154</v>
       </c>
       <c r="C85" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D85" t="inlineStr">
         <is>
@@ -8336,7 +8336,7 @@
         <v>45205</v>
       </c>
       <c r="C86" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D86" t="inlineStr">
         <is>
@@ -8422,7 +8422,7 @@
         <v>45208</v>
       </c>
       <c r="C87" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
@@ -8508,7 +8508,7 @@
         <v>45238</v>
       </c>
       <c r="C88" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -8594,7 +8594,7 @@
         <v>45238</v>
       </c>
       <c r="C89" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -8680,7 +8680,7 @@
         <v>45253</v>
       </c>
       <c r="C90" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
@@ -8766,7 +8766,7 @@
         <v>43462</v>
       </c>
       <c r="C91" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D91" t="inlineStr">
         <is>
@@ -8851,7 +8851,7 @@
         <v>43468</v>
       </c>
       <c r="C92" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D92" t="inlineStr">
         <is>
@@ -8936,7 +8936,7 @@
         <v>43538</v>
       </c>
       <c r="C93" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D93" t="inlineStr">
         <is>
@@ -9021,7 +9021,7 @@
         <v>43689</v>
       </c>
       <c r="C94" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -9106,7 +9106,7 @@
         <v>43742</v>
       </c>
       <c r="C95" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
@@ -9191,7 +9191,7 @@
         <v>43959</v>
       </c>
       <c r="C96" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -9276,7 +9276,7 @@
         <v>44007</v>
       </c>
       <c r="C97" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -9361,7 +9361,7 @@
         <v>44043</v>
       </c>
       <c r="C98" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -9455,7 +9455,7 @@
         <v>44090</v>
       </c>
       <c r="C99" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
@@ -9545,7 +9545,7 @@
         <v>44154</v>
       </c>
       <c r="C100" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -9630,7 +9630,7 @@
         <v>44369</v>
       </c>
       <c r="C101" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D101" t="inlineStr">
         <is>
@@ -9715,7 +9715,7 @@
         <v>44445</v>
       </c>
       <c r="C102" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D102" t="inlineStr">
         <is>
@@ -9805,7 +9805,7 @@
         <v>44455</v>
       </c>
       <c r="C103" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -9890,7 +9890,7 @@
         <v>44455</v>
       </c>
       <c r="C104" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
@@ -9975,7 +9975,7 @@
         <v>44501</v>
       </c>
       <c r="C105" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
@@ -10065,7 +10065,7 @@
         <v>44501</v>
       </c>
       <c r="C106" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
@@ -10155,7 +10155,7 @@
         <v>44509</v>
       </c>
       <c r="C107" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -10240,7 +10240,7 @@
         <v>44511</v>
       </c>
       <c r="C108" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
@@ -10325,7 +10325,7 @@
         <v>44517</v>
       </c>
       <c r="C109" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
@@ -10410,7 +10410,7 @@
         <v>44536</v>
       </c>
       <c r="C110" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -10499,7 +10499,7 @@
         <v>44571</v>
       </c>
       <c r="C111" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -10584,7 +10584,7 @@
         <v>44572</v>
       </c>
       <c r="C112" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -10669,7 +10669,7 @@
         <v>44606</v>
       </c>
       <c r="C113" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -10754,7 +10754,7 @@
         <v>44607</v>
       </c>
       <c r="C114" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -10839,7 +10839,7 @@
         <v>44712</v>
       </c>
       <c r="C115" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
@@ -10929,7 +10929,7 @@
         <v>44728</v>
       </c>
       <c r="C116" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
@@ -11019,7 +11019,7 @@
         <v>44742</v>
       </c>
       <c r="C117" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -11104,7 +11104,7 @@
         <v>44796</v>
       </c>
       <c r="C118" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -11194,7 +11194,7 @@
         <v>44874</v>
       </c>
       <c r="C119" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -11284,7 +11284,7 @@
         <v>44874</v>
       </c>
       <c r="C120" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
@@ -11374,7 +11374,7 @@
         <v>44875</v>
       </c>
       <c r="C121" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
@@ -11459,7 +11459,7 @@
         <v>44938</v>
       </c>
       <c r="C122" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
@@ -11544,7 +11544,7 @@
         <v>45013</v>
       </c>
       <c r="C123" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -11629,7 +11629,7 @@
         <v>45021</v>
       </c>
       <c r="C124" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -11719,7 +11719,7 @@
         <v>45021</v>
       </c>
       <c r="C125" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -11813,7 +11813,7 @@
         <v>45048</v>
       </c>
       <c r="C126" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -11903,7 +11903,7 @@
         <v>45063</v>
       </c>
       <c r="C127" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
@@ -11997,7 +11997,7 @@
         <v>45070</v>
       </c>
       <c r="C128" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
@@ -12087,7 +12087,7 @@
         <v>45070</v>
       </c>
       <c r="C129" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -12172,7 +12172,7 @@
         <v>45071</v>
       </c>
       <c r="C130" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -12257,7 +12257,7 @@
         <v>45075</v>
       </c>
       <c r="C131" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -12342,7 +12342,7 @@
         <v>45078</v>
       </c>
       <c r="C132" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -12427,7 +12427,7 @@
         <v>45093</v>
       </c>
       <c r="C133" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -12512,7 +12512,7 @@
         <v>45107</v>
       </c>
       <c r="C134" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -12602,7 +12602,7 @@
         <v>45121</v>
       </c>
       <c r="C135" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -12687,7 +12687,7 @@
         <v>45135</v>
       </c>
       <c r="C136" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -12781,7 +12781,7 @@
         <v>45230</v>
       </c>
       <c r="C137" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -12866,7 +12866,7 @@
         <v>45230</v>
       </c>
       <c r="C138" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -12951,7 +12951,7 @@
         <v>45238</v>
       </c>
       <c r="C139" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -13036,7 +13036,7 @@
         <v>45246</v>
       </c>
       <c r="C140" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -13126,7 +13126,7 @@
         <v>45246</v>
       </c>
       <c r="C141" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -13216,7 +13216,7 @@
         <v>45246</v>
       </c>
       <c r="C142" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
@@ -13306,7 +13306,7 @@
         <v>45323</v>
       </c>
       <c r="C143" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -13396,7 +13396,7 @@
         <v>43320</v>
       </c>
       <c r="C144" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -13453,7 +13453,7 @@
         <v>43327</v>
       </c>
       <c r="C145" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -13510,7 +13510,7 @@
         <v>43343</v>
       </c>
       <c r="C146" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -13572,7 +13572,7 @@
         <v>43343</v>
       </c>
       <c r="C147" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -13634,7 +13634,7 @@
         <v>43355</v>
       </c>
       <c r="C148" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -13691,7 +13691,7 @@
         <v>43360</v>
       </c>
       <c r="C149" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -13753,7 +13753,7 @@
         <v>43376</v>
       </c>
       <c r="C150" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -13810,7 +13810,7 @@
         <v>43376</v>
       </c>
       <c r="C151" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -13867,7 +13867,7 @@
         <v>43381</v>
       </c>
       <c r="C152" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -13924,7 +13924,7 @@
         <v>43384</v>
       </c>
       <c r="C153" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -13986,7 +13986,7 @@
         <v>43398</v>
       </c>
       <c r="C154" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -14043,7 +14043,7 @@
         <v>43410</v>
       </c>
       <c r="C155" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -14105,7 +14105,7 @@
         <v>43423</v>
       </c>
       <c r="C156" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -14162,7 +14162,7 @@
         <v>43423</v>
       </c>
       <c r="C157" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -14219,7 +14219,7 @@
         <v>43423</v>
       </c>
       <c r="C158" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
@@ -14276,7 +14276,7 @@
         <v>43423</v>
       </c>
       <c r="C159" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -14333,7 +14333,7 @@
         <v>43430</v>
       </c>
       <c r="C160" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -14395,7 +14395,7 @@
         <v>43431</v>
       </c>
       <c r="C161" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
@@ -14452,7 +14452,7 @@
         <v>43432</v>
       </c>
       <c r="C162" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -14514,7 +14514,7 @@
         <v>43432</v>
       </c>
       <c r="C163" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -14576,7 +14576,7 @@
         <v>43448</v>
       </c>
       <c r="C164" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -14638,7 +14638,7 @@
         <v>43453</v>
       </c>
       <c r="C165" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -14695,7 +14695,7 @@
         <v>43468</v>
       </c>
       <c r="C166" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -14752,7 +14752,7 @@
         <v>43468</v>
       </c>
       <c r="C167" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
@@ -14809,7 +14809,7 @@
         <v>43469</v>
       </c>
       <c r="C168" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -14866,7 +14866,7 @@
         <v>43469</v>
       </c>
       <c r="C169" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
@@ -14923,7 +14923,7 @@
         <v>43472</v>
       </c>
       <c r="C170" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -14985,7 +14985,7 @@
         <v>43472</v>
       </c>
       <c r="C171" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -15042,7 +15042,7 @@
         <v>43472</v>
       </c>
       <c r="C172" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -15099,7 +15099,7 @@
         <v>43472</v>
       </c>
       <c r="C173" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -15161,7 +15161,7 @@
         <v>43473</v>
       </c>
       <c r="C174" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D174" t="inlineStr">
         <is>
@@ -15218,7 +15218,7 @@
         <v>43474</v>
       </c>
       <c r="C175" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D175" t="inlineStr">
         <is>
@@ -15275,7 +15275,7 @@
         <v>43475</v>
       </c>
       <c r="C176" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D176" t="inlineStr">
         <is>
@@ -15337,7 +15337,7 @@
         <v>43476</v>
       </c>
       <c r="C177" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D177" t="inlineStr">
         <is>
@@ -15399,7 +15399,7 @@
         <v>43479</v>
       </c>
       <c r="C178" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D178" t="inlineStr">
         <is>
@@ -15456,7 +15456,7 @@
         <v>43479</v>
       </c>
       <c r="C179" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D179" t="inlineStr">
         <is>
@@ -15513,7 +15513,7 @@
         <v>43479</v>
       </c>
       <c r="C180" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D180" t="inlineStr">
         <is>
@@ -15570,7 +15570,7 @@
         <v>43479</v>
       </c>
       <c r="C181" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D181" t="inlineStr">
         <is>
@@ -15627,7 +15627,7 @@
         <v>43480</v>
       </c>
       <c r="C182" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D182" t="inlineStr">
         <is>
@@ -15684,7 +15684,7 @@
         <v>43482</v>
       </c>
       <c r="C183" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D183" t="inlineStr">
         <is>
@@ -15741,7 +15741,7 @@
         <v>43482</v>
       </c>
       <c r="C184" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D184" t="inlineStr">
         <is>
@@ -15798,7 +15798,7 @@
         <v>43482</v>
       </c>
       <c r="C185" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D185" t="inlineStr">
         <is>
@@ -15855,7 +15855,7 @@
         <v>43483</v>
       </c>
       <c r="C186" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D186" t="inlineStr">
         <is>
@@ -15917,7 +15917,7 @@
         <v>43483</v>
       </c>
       <c r="C187" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D187" t="inlineStr">
         <is>
@@ -15974,7 +15974,7 @@
         <v>43484</v>
       </c>
       <c r="C188" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D188" t="inlineStr">
         <is>
@@ -16031,7 +16031,7 @@
         <v>43485</v>
       </c>
       <c r="C189" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D189" t="inlineStr">
         <is>
@@ -16088,7 +16088,7 @@
         <v>43485</v>
       </c>
       <c r="C190" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D190" t="inlineStr">
         <is>
@@ -16145,7 +16145,7 @@
         <v>43485</v>
       </c>
       <c r="C191" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D191" t="inlineStr">
         <is>
@@ -16202,7 +16202,7 @@
         <v>43485</v>
       </c>
       <c r="C192" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D192" t="inlineStr">
         <is>
@@ -16259,7 +16259,7 @@
         <v>43485</v>
       </c>
       <c r="C193" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D193" t="inlineStr">
         <is>
@@ -16316,7 +16316,7 @@
         <v>43486</v>
       </c>
       <c r="C194" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D194" t="inlineStr">
         <is>
@@ -16373,7 +16373,7 @@
         <v>43486</v>
       </c>
       <c r="C195" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D195" t="inlineStr">
         <is>
@@ -16430,7 +16430,7 @@
         <v>43487</v>
       </c>
       <c r="C196" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D196" t="inlineStr">
         <is>
@@ -16487,7 +16487,7 @@
         <v>43489</v>
       </c>
       <c r="C197" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D197" t="inlineStr">
         <is>
@@ -16544,7 +16544,7 @@
         <v>43489</v>
       </c>
       <c r="C198" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D198" t="inlineStr">
         <is>
@@ -16601,7 +16601,7 @@
         <v>43489</v>
       </c>
       <c r="C199" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D199" t="inlineStr">
         <is>
@@ -16658,7 +16658,7 @@
         <v>43493</v>
       </c>
       <c r="C200" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D200" t="inlineStr">
         <is>
@@ -16715,7 +16715,7 @@
         <v>43493</v>
       </c>
       <c r="C201" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D201" t="inlineStr">
         <is>
@@ -16772,7 +16772,7 @@
         <v>43493</v>
       </c>
       <c r="C202" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D202" t="inlineStr">
         <is>
@@ -16829,7 +16829,7 @@
         <v>43494</v>
       </c>
       <c r="C203" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D203" t="inlineStr">
         <is>
@@ -16886,7 +16886,7 @@
         <v>43494</v>
       </c>
       <c r="C204" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D204" t="inlineStr">
         <is>
@@ -16943,7 +16943,7 @@
         <v>43495</v>
       </c>
       <c r="C205" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D205" t="inlineStr">
         <is>
@@ -17000,7 +17000,7 @@
         <v>43500</v>
       </c>
       <c r="C206" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D206" t="inlineStr">
         <is>
@@ -17057,7 +17057,7 @@
         <v>43500</v>
       </c>
       <c r="C207" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D207" t="inlineStr">
         <is>
@@ -17114,7 +17114,7 @@
         <v>43502</v>
       </c>
       <c r="C208" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D208" t="inlineStr">
         <is>
@@ -17171,7 +17171,7 @@
         <v>43503</v>
       </c>
       <c r="C209" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D209" t="inlineStr">
         <is>
@@ -17233,7 +17233,7 @@
         <v>43507</v>
       </c>
       <c r="C210" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D210" t="inlineStr">
         <is>
@@ -17290,7 +17290,7 @@
         <v>43507</v>
       </c>
       <c r="C211" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D211" t="inlineStr">
         <is>
@@ -17352,7 +17352,7 @@
         <v>43508</v>
       </c>
       <c r="C212" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D212" t="inlineStr">
         <is>
@@ -17414,7 +17414,7 @@
         <v>43508</v>
       </c>
       <c r="C213" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D213" t="inlineStr">
         <is>
@@ -17476,7 +17476,7 @@
         <v>43509</v>
       </c>
       <c r="C214" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D214" t="inlineStr">
         <is>
@@ -17538,7 +17538,7 @@
         <v>43514</v>
       </c>
       <c r="C215" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D215" t="inlineStr">
         <is>
@@ -17595,7 +17595,7 @@
         <v>43515</v>
       </c>
       <c r="C216" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D216" t="inlineStr">
         <is>
@@ -17652,7 +17652,7 @@
         <v>43517</v>
       </c>
       <c r="C217" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D217" t="inlineStr">
         <is>
@@ -17714,7 +17714,7 @@
         <v>43518</v>
       </c>
       <c r="C218" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D218" t="inlineStr">
         <is>
@@ -17771,7 +17771,7 @@
         <v>43518</v>
       </c>
       <c r="C219" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D219" t="inlineStr">
         <is>
@@ -17828,7 +17828,7 @@
         <v>43518</v>
       </c>
       <c r="C220" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D220" t="inlineStr">
         <is>
@@ -17885,7 +17885,7 @@
         <v>43518</v>
       </c>
       <c r="C221" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D221" t="inlineStr">
         <is>
@@ -17942,7 +17942,7 @@
         <v>43518</v>
       </c>
       <c r="C222" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D222" t="inlineStr">
         <is>
@@ -17999,7 +17999,7 @@
         <v>43521</v>
       </c>
       <c r="C223" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D223" t="inlineStr">
         <is>
@@ -18056,7 +18056,7 @@
         <v>43522</v>
       </c>
       <c r="C224" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D224" t="inlineStr">
         <is>
@@ -18113,7 +18113,7 @@
         <v>43523</v>
       </c>
       <c r="C225" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D225" t="inlineStr">
         <is>
@@ -18170,7 +18170,7 @@
         <v>43524</v>
       </c>
       <c r="C226" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D226" t="inlineStr">
         <is>
@@ -18227,7 +18227,7 @@
         <v>43524</v>
       </c>
       <c r="C227" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D227" t="inlineStr">
         <is>
@@ -18284,7 +18284,7 @@
         <v>43524</v>
       </c>
       <c r="C228" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D228" t="inlineStr">
         <is>
@@ -18341,7 +18341,7 @@
         <v>43529</v>
       </c>
       <c r="C229" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D229" t="inlineStr">
         <is>
@@ -18403,7 +18403,7 @@
         <v>43530</v>
       </c>
       <c r="C230" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D230" t="inlineStr">
         <is>
@@ -18460,7 +18460,7 @@
         <v>43531</v>
       </c>
       <c r="C231" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D231" t="inlineStr">
         <is>
@@ -18522,7 +18522,7 @@
         <v>43535</v>
       </c>
       <c r="C232" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D232" t="inlineStr">
         <is>
@@ -18579,7 +18579,7 @@
         <v>43535</v>
       </c>
       <c r="C233" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D233" t="inlineStr">
         <is>
@@ -18636,7 +18636,7 @@
         <v>43536</v>
       </c>
       <c r="C234" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D234" t="inlineStr">
         <is>
@@ -18693,7 +18693,7 @@
         <v>43537</v>
       </c>
       <c r="C235" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D235" t="inlineStr">
         <is>
@@ -18755,7 +18755,7 @@
         <v>43537</v>
       </c>
       <c r="C236" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D236" t="inlineStr">
         <is>
@@ -18817,7 +18817,7 @@
         <v>43538</v>
       </c>
       <c r="C237" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D237" t="inlineStr">
         <is>
@@ -18874,7 +18874,7 @@
         <v>43545</v>
       </c>
       <c r="C238" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D238" t="inlineStr">
         <is>
@@ -18936,7 +18936,7 @@
         <v>43545</v>
       </c>
       <c r="C239" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D239" t="inlineStr">
         <is>
@@ -18998,7 +18998,7 @@
         <v>43550</v>
       </c>
       <c r="C240" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D240" t="inlineStr">
         <is>
@@ -19060,7 +19060,7 @@
         <v>43560</v>
       </c>
       <c r="C241" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D241" t="inlineStr">
         <is>
@@ -19117,7 +19117,7 @@
         <v>43561</v>
       </c>
       <c r="C242" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D242" t="inlineStr">
         <is>
@@ -19179,7 +19179,7 @@
         <v>43562</v>
       </c>
       <c r="C243" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D243" t="inlineStr">
         <is>
@@ -19236,7 +19236,7 @@
         <v>43562</v>
       </c>
       <c r="C244" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D244" t="inlineStr">
         <is>
@@ -19298,7 +19298,7 @@
         <v>43573</v>
       </c>
       <c r="C245" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D245" t="inlineStr">
         <is>
@@ -19355,7 +19355,7 @@
         <v>43580</v>
       </c>
       <c r="C246" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D246" t="inlineStr">
         <is>
@@ -19417,7 +19417,7 @@
         <v>43590</v>
       </c>
       <c r="C247" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D247" t="inlineStr">
         <is>
@@ -19494,7 +19494,7 @@
         <v>43590</v>
       </c>
       <c r="C248" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D248" t="inlineStr">
         <is>
@@ -19551,7 +19551,7 @@
         <v>43591</v>
       </c>
       <c r="C249" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D249" t="inlineStr">
         <is>
@@ -19608,7 +19608,7 @@
         <v>43605</v>
       </c>
       <c r="C250" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D250" t="inlineStr">
         <is>
@@ -19665,7 +19665,7 @@
         <v>43607</v>
       </c>
       <c r="C251" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D251" t="inlineStr">
         <is>
@@ -19727,7 +19727,7 @@
         <v>43607</v>
       </c>
       <c r="C252" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D252" t="inlineStr">
         <is>
@@ -19789,7 +19789,7 @@
         <v>43607</v>
       </c>
       <c r="C253" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D253" t="inlineStr">
         <is>
@@ -19851,7 +19851,7 @@
         <v>43612</v>
       </c>
       <c r="C254" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D254" t="inlineStr">
         <is>
@@ -19908,7 +19908,7 @@
         <v>43613</v>
       </c>
       <c r="C255" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D255" t="inlineStr">
         <is>
@@ -19970,7 +19970,7 @@
         <v>43613</v>
       </c>
       <c r="C256" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D256" t="inlineStr">
         <is>
@@ -20032,7 +20032,7 @@
         <v>43618</v>
       </c>
       <c r="C257" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D257" t="inlineStr">
         <is>
@@ -20094,7 +20094,7 @@
         <v>43623</v>
       </c>
       <c r="C258" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D258" t="inlineStr">
         <is>
@@ -20151,7 +20151,7 @@
         <v>43635</v>
       </c>
       <c r="C259" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D259" t="inlineStr">
         <is>
@@ -20213,7 +20213,7 @@
         <v>43642</v>
       </c>
       <c r="C260" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D260" t="inlineStr">
         <is>
@@ -20270,7 +20270,7 @@
         <v>43642</v>
       </c>
       <c r="C261" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D261" t="inlineStr">
         <is>
@@ -20327,7 +20327,7 @@
         <v>43647</v>
       </c>
       <c r="C262" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D262" t="inlineStr">
         <is>
@@ -20384,7 +20384,7 @@
         <v>43651</v>
       </c>
       <c r="C263" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D263" t="inlineStr">
         <is>
@@ -20441,7 +20441,7 @@
         <v>43651</v>
       </c>
       <c r="C264" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D264" t="inlineStr">
         <is>
@@ -20498,7 +20498,7 @@
         <v>43651</v>
       </c>
       <c r="C265" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D265" t="inlineStr">
         <is>
@@ -20555,7 +20555,7 @@
         <v>43651</v>
       </c>
       <c r="C266" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D266" t="inlineStr">
         <is>
@@ -20612,7 +20612,7 @@
         <v>43651</v>
       </c>
       <c r="C267" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D267" t="inlineStr">
         <is>
@@ -20669,7 +20669,7 @@
         <v>43686</v>
       </c>
       <c r="C268" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D268" t="inlineStr">
         <is>
@@ -20726,7 +20726,7 @@
         <v>43692</v>
       </c>
       <c r="C269" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D269" t="inlineStr">
         <is>
@@ -20783,7 +20783,7 @@
         <v>43699</v>
       </c>
       <c r="C270" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D270" t="inlineStr">
         <is>
@@ -20845,7 +20845,7 @@
         <v>43699</v>
       </c>
       <c r="C271" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D271" t="inlineStr">
         <is>
@@ -20902,7 +20902,7 @@
         <v>43706</v>
       </c>
       <c r="C272" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D272" t="inlineStr">
         <is>
@@ -20964,7 +20964,7 @@
         <v>43713</v>
       </c>
       <c r="C273" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D273" t="inlineStr">
         <is>
@@ -21021,7 +21021,7 @@
         <v>43717</v>
       </c>
       <c r="C274" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D274" t="inlineStr">
         <is>
@@ -21083,7 +21083,7 @@
         <v>43723</v>
       </c>
       <c r="C275" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D275" t="inlineStr">
         <is>
@@ -21140,7 +21140,7 @@
         <v>43723</v>
       </c>
       <c r="C276" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D276" t="inlineStr">
         <is>
@@ -21197,7 +21197,7 @@
         <v>43739</v>
       </c>
       <c r="C277" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D277" t="inlineStr">
         <is>
@@ -21259,7 +21259,7 @@
         <v>43748</v>
       </c>
       <c r="C278" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D278" t="inlineStr">
         <is>
@@ -21321,7 +21321,7 @@
         <v>43755</v>
       </c>
       <c r="C279" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D279" t="inlineStr">
         <is>
@@ -21378,7 +21378,7 @@
         <v>43761</v>
       </c>
       <c r="C280" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D280" t="inlineStr">
         <is>
@@ -21435,7 +21435,7 @@
         <v>43767</v>
       </c>
       <c r="C281" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D281" t="inlineStr">
         <is>
@@ -21497,7 +21497,7 @@
         <v>43773</v>
       </c>
       <c r="C282" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D282" t="inlineStr">
         <is>
@@ -21554,7 +21554,7 @@
         <v>43782</v>
       </c>
       <c r="C283" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D283" t="inlineStr">
         <is>
@@ -21616,7 +21616,7 @@
         <v>43787</v>
       </c>
       <c r="C284" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D284" t="inlineStr">
         <is>
@@ -21678,7 +21678,7 @@
         <v>43790</v>
       </c>
       <c r="C285" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D285" t="inlineStr">
         <is>
@@ -21735,7 +21735,7 @@
         <v>43795</v>
       </c>
       <c r="C286" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D286" t="inlineStr">
         <is>
@@ -21797,7 +21797,7 @@
         <v>43797</v>
       </c>
       <c r="C287" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D287" t="inlineStr">
         <is>
@@ -21854,7 +21854,7 @@
         <v>43802</v>
       </c>
       <c r="C288" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D288" t="inlineStr">
         <is>
@@ -21911,7 +21911,7 @@
         <v>43808</v>
       </c>
       <c r="C289" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D289" t="inlineStr">
         <is>
@@ -21968,7 +21968,7 @@
         <v>43810</v>
       </c>
       <c r="C290" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D290" t="inlineStr">
         <is>
@@ -22030,7 +22030,7 @@
         <v>43812</v>
       </c>
       <c r="C291" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D291" t="inlineStr">
         <is>
@@ -22092,7 +22092,7 @@
         <v>43817</v>
       </c>
       <c r="C292" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D292" t="inlineStr">
         <is>
@@ -22149,7 +22149,7 @@
         <v>43821</v>
       </c>
       <c r="C293" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D293" t="inlineStr">
         <is>
@@ -22211,7 +22211,7 @@
         <v>43821</v>
       </c>
       <c r="C294" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D294" t="inlineStr">
         <is>
@@ -22273,7 +22273,7 @@
         <v>43821</v>
       </c>
       <c r="C295" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D295" t="inlineStr">
         <is>
@@ -22335,7 +22335,7 @@
         <v>43838</v>
       </c>
       <c r="C296" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D296" t="inlineStr">
         <is>
@@ -22397,7 +22397,7 @@
         <v>43844</v>
       </c>
       <c r="C297" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D297" t="inlineStr">
         <is>
@@ -22459,7 +22459,7 @@
         <v>43844</v>
       </c>
       <c r="C298" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D298" t="inlineStr">
         <is>
@@ -22521,7 +22521,7 @@
         <v>43850</v>
       </c>
       <c r="C299" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D299" t="inlineStr">
         <is>
@@ -22578,7 +22578,7 @@
         <v>43852</v>
       </c>
       <c r="C300" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D300" t="inlineStr">
         <is>
@@ -22635,7 +22635,7 @@
         <v>43855</v>
       </c>
       <c r="C301" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D301" t="inlineStr">
         <is>
@@ -22697,7 +22697,7 @@
         <v>43864</v>
       </c>
       <c r="C302" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D302" t="inlineStr">
         <is>
@@ -22754,7 +22754,7 @@
         <v>43865</v>
       </c>
       <c r="C303" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D303" t="inlineStr">
         <is>
@@ -22816,7 +22816,7 @@
         <v>43867</v>
       </c>
       <c r="C304" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D304" t="inlineStr">
         <is>
@@ -22873,7 +22873,7 @@
         <v>43873</v>
       </c>
       <c r="C305" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D305" t="inlineStr">
         <is>
@@ -22935,7 +22935,7 @@
         <v>43882</v>
       </c>
       <c r="C306" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D306" t="inlineStr">
         <is>
@@ -22992,7 +22992,7 @@
         <v>43885</v>
       </c>
       <c r="C307" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D307" t="inlineStr">
         <is>
@@ -23054,7 +23054,7 @@
         <v>43885</v>
       </c>
       <c r="C308" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D308" t="inlineStr">
         <is>
@@ -23116,7 +23116,7 @@
         <v>43895</v>
       </c>
       <c r="C309" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D309" t="inlineStr">
         <is>
@@ -23178,7 +23178,7 @@
         <v>43901</v>
       </c>
       <c r="C310" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D310" t="inlineStr">
         <is>
@@ -23240,7 +23240,7 @@
         <v>43902</v>
       </c>
       <c r="C311" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D311" t="inlineStr">
         <is>
@@ -23302,7 +23302,7 @@
         <v>43903</v>
       </c>
       <c r="C312" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D312" t="inlineStr">
         <is>
@@ -23364,7 +23364,7 @@
         <v>43906</v>
       </c>
       <c r="C313" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D313" t="inlineStr">
         <is>
@@ -23421,7 +23421,7 @@
         <v>43909</v>
       </c>
       <c r="C314" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D314" t="inlineStr">
         <is>
@@ -23483,7 +23483,7 @@
         <v>43909</v>
       </c>
       <c r="C315" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D315" t="inlineStr">
         <is>
@@ -23545,7 +23545,7 @@
         <v>43910</v>
       </c>
       <c r="C316" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D316" t="inlineStr">
         <is>
@@ -23607,7 +23607,7 @@
         <v>43920</v>
       </c>
       <c r="C317" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D317" t="inlineStr">
         <is>
@@ -23664,7 +23664,7 @@
         <v>43936</v>
       </c>
       <c r="C318" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D318" t="inlineStr">
         <is>
@@ -23721,7 +23721,7 @@
         <v>43969</v>
       </c>
       <c r="C319" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D319" t="inlineStr">
         <is>
@@ -23783,7 +23783,7 @@
         <v>43986</v>
       </c>
       <c r="C320" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D320" t="inlineStr">
         <is>
@@ -23845,7 +23845,7 @@
         <v>44007</v>
       </c>
       <c r="C321" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D321" t="inlineStr">
         <is>
@@ -23902,7 +23902,7 @@
         <v>44007</v>
       </c>
       <c r="C322" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D322" t="inlineStr">
         <is>
@@ -23959,7 +23959,7 @@
         <v>44015</v>
       </c>
       <c r="C323" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D323" t="inlineStr">
         <is>
@@ -24016,7 +24016,7 @@
         <v>44021</v>
       </c>
       <c r="C324" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D324" t="inlineStr">
         <is>
@@ -24073,7 +24073,7 @@
         <v>44038</v>
       </c>
       <c r="C325" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D325" t="inlineStr">
         <is>
@@ -24135,7 +24135,7 @@
         <v>44038</v>
       </c>
       <c r="C326" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D326" t="inlineStr">
         <is>
@@ -24197,7 +24197,7 @@
         <v>44038</v>
       </c>
       <c r="C327" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D327" t="inlineStr">
         <is>
@@ -24259,7 +24259,7 @@
         <v>44040</v>
       </c>
       <c r="C328" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D328" t="inlineStr">
         <is>
@@ -24321,7 +24321,7 @@
         <v>44040</v>
       </c>
       <c r="C329" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D329" t="inlineStr">
         <is>
@@ -24383,7 +24383,7 @@
         <v>44060</v>
       </c>
       <c r="C330" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D330" t="inlineStr">
         <is>
@@ -24440,7 +24440,7 @@
         <v>44061</v>
       </c>
       <c r="C331" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D331" t="inlineStr">
         <is>
@@ -24502,7 +24502,7 @@
         <v>44064</v>
       </c>
       <c r="C332" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D332" t="inlineStr">
         <is>
@@ -24564,7 +24564,7 @@
         <v>44074</v>
       </c>
       <c r="C333" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D333" t="inlineStr">
         <is>
@@ -24626,7 +24626,7 @@
         <v>44077</v>
       </c>
       <c r="C334" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D334" t="inlineStr">
         <is>
@@ -24683,7 +24683,7 @@
         <v>44092</v>
       </c>
       <c r="C335" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D335" t="inlineStr">
         <is>
@@ -24745,7 +24745,7 @@
         <v>44095</v>
       </c>
       <c r="C336" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D336" t="inlineStr">
         <is>
@@ -24802,7 +24802,7 @@
         <v>44098</v>
       </c>
       <c r="C337" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D337" t="inlineStr">
         <is>
@@ -24859,7 +24859,7 @@
         <v>44105</v>
       </c>
       <c r="C338" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D338" t="inlineStr">
         <is>
@@ -24921,7 +24921,7 @@
         <v>44105</v>
       </c>
       <c r="C339" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D339" t="inlineStr">
         <is>
@@ -24983,7 +24983,7 @@
         <v>44118</v>
       </c>
       <c r="C340" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D340" t="inlineStr">
         <is>
@@ -25040,7 +25040,7 @@
         <v>44118</v>
       </c>
       <c r="C341" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D341" t="inlineStr">
         <is>
@@ -25097,7 +25097,7 @@
         <v>44120</v>
       </c>
       <c r="C342" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D342" t="inlineStr">
         <is>
@@ -25154,7 +25154,7 @@
         <v>44131</v>
       </c>
       <c r="C343" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D343" t="inlineStr">
         <is>
@@ -25211,7 +25211,7 @@
         <v>44133</v>
       </c>
       <c r="C344" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D344" t="inlineStr">
         <is>
@@ -25273,7 +25273,7 @@
         <v>44133</v>
       </c>
       <c r="C345" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D345" t="inlineStr">
         <is>
@@ -25335,7 +25335,7 @@
         <v>44133</v>
       </c>
       <c r="C346" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D346" t="inlineStr">
         <is>
@@ -25397,7 +25397,7 @@
         <v>44140</v>
       </c>
       <c r="C347" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D347" t="inlineStr">
         <is>
@@ -25459,7 +25459,7 @@
         <v>44148</v>
       </c>
       <c r="C348" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D348" t="inlineStr">
         <is>
@@ -25521,7 +25521,7 @@
         <v>44148</v>
       </c>
       <c r="C349" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D349" t="inlineStr">
         <is>
@@ -25583,7 +25583,7 @@
         <v>44148</v>
       </c>
       <c r="C350" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D350" t="inlineStr">
         <is>
@@ -25645,7 +25645,7 @@
         <v>44151</v>
       </c>
       <c r="C351" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D351" t="inlineStr">
         <is>
@@ -25707,7 +25707,7 @@
         <v>44151</v>
       </c>
       <c r="C352" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D352" t="inlineStr">
         <is>
@@ -25764,7 +25764,7 @@
         <v>44155</v>
       </c>
       <c r="C353" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D353" t="inlineStr">
         <is>
@@ -25826,7 +25826,7 @@
         <v>44160</v>
       </c>
       <c r="C354" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D354" t="inlineStr">
         <is>
@@ -25883,7 +25883,7 @@
         <v>44162</v>
       </c>
       <c r="C355" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D355" t="inlineStr">
         <is>
@@ -25940,7 +25940,7 @@
         <v>44165</v>
       </c>
       <c r="C356" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D356" t="inlineStr">
         <is>
@@ -25997,7 +25997,7 @@
         <v>44167</v>
       </c>
       <c r="C357" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D357" t="inlineStr">
         <is>
@@ -26054,7 +26054,7 @@
         <v>44173</v>
       </c>
       <c r="C358" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D358" t="inlineStr">
         <is>
@@ -26111,7 +26111,7 @@
         <v>44183</v>
       </c>
       <c r="C359" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D359" t="inlineStr">
         <is>
@@ -26168,7 +26168,7 @@
         <v>44186</v>
       </c>
       <c r="C360" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D360" t="inlineStr">
         <is>
@@ -26225,7 +26225,7 @@
         <v>44196</v>
       </c>
       <c r="C361" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D361" t="inlineStr">
         <is>
@@ -26287,7 +26287,7 @@
         <v>44221</v>
       </c>
       <c r="C362" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D362" t="inlineStr">
         <is>
@@ -26344,7 +26344,7 @@
         <v>44221</v>
       </c>
       <c r="C363" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D363" t="inlineStr">
         <is>
@@ -26401,7 +26401,7 @@
         <v>44224</v>
       </c>
       <c r="C364" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D364" t="inlineStr">
         <is>
@@ -26463,7 +26463,7 @@
         <v>44235</v>
       </c>
       <c r="C365" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D365" t="inlineStr">
         <is>
@@ -26520,7 +26520,7 @@
         <v>44238</v>
       </c>
       <c r="C366" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D366" t="inlineStr">
         <is>
@@ -26582,7 +26582,7 @@
         <v>44243</v>
       </c>
       <c r="C367" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D367" t="inlineStr">
         <is>
@@ -26639,7 +26639,7 @@
         <v>44257</v>
       </c>
       <c r="C368" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D368" t="inlineStr">
         <is>
@@ -26701,7 +26701,7 @@
         <v>44258</v>
       </c>
       <c r="C369" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D369" t="inlineStr">
         <is>
@@ -26763,7 +26763,7 @@
         <v>44278</v>
       </c>
       <c r="C370" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D370" t="inlineStr">
         <is>
@@ -26825,7 +26825,7 @@
         <v>44279</v>
       </c>
       <c r="C371" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D371" t="inlineStr">
         <is>
@@ -26887,7 +26887,7 @@
         <v>44287</v>
       </c>
       <c r="C372" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D372" t="inlineStr">
         <is>
@@ -26944,7 +26944,7 @@
         <v>44287</v>
       </c>
       <c r="C373" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D373" t="inlineStr">
         <is>
@@ -27001,7 +27001,7 @@
         <v>44295</v>
       </c>
       <c r="C374" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D374" t="inlineStr">
         <is>
@@ -27063,7 +27063,7 @@
         <v>44295</v>
       </c>
       <c r="C375" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D375" t="inlineStr">
         <is>
@@ -27125,7 +27125,7 @@
         <v>44295</v>
       </c>
       <c r="C376" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D376" t="inlineStr">
         <is>
@@ -27187,7 +27187,7 @@
         <v>44298</v>
       </c>
       <c r="C377" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D377" t="inlineStr">
         <is>
@@ -27249,7 +27249,7 @@
         <v>44308</v>
       </c>
       <c r="C378" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D378" t="inlineStr">
         <is>
@@ -27311,7 +27311,7 @@
         <v>44308</v>
       </c>
       <c r="C379" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D379" t="inlineStr">
         <is>
@@ -27368,7 +27368,7 @@
         <v>44308</v>
       </c>
       <c r="C380" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D380" t="inlineStr">
         <is>
@@ -27425,7 +27425,7 @@
         <v>44308</v>
       </c>
       <c r="C381" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D381" t="inlineStr">
         <is>
@@ -27482,7 +27482,7 @@
         <v>44309</v>
       </c>
       <c r="C382" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D382" t="inlineStr">
         <is>
@@ -27544,7 +27544,7 @@
         <v>44312</v>
       </c>
       <c r="C383" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D383" t="inlineStr">
         <is>
@@ -27601,7 +27601,7 @@
         <v>44327</v>
       </c>
       <c r="C384" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D384" t="inlineStr">
         <is>
@@ -27663,7 +27663,7 @@
         <v>44330</v>
       </c>
       <c r="C385" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D385" t="inlineStr">
         <is>
@@ -27720,7 +27720,7 @@
         <v>44336</v>
       </c>
       <c r="C386" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D386" t="inlineStr">
         <is>
@@ -27777,7 +27777,7 @@
         <v>44337</v>
       </c>
       <c r="C387" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D387" t="inlineStr">
         <is>
@@ -27834,7 +27834,7 @@
         <v>44341</v>
       </c>
       <c r="C388" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D388" t="inlineStr">
         <is>
@@ -27896,7 +27896,7 @@
         <v>44342</v>
       </c>
       <c r="C389" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D389" t="inlineStr">
         <is>
@@ -27958,7 +27958,7 @@
         <v>44342</v>
       </c>
       <c r="C390" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D390" t="inlineStr">
         <is>
@@ -28020,7 +28020,7 @@
         <v>44347</v>
       </c>
       <c r="C391" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D391" t="inlineStr">
         <is>
@@ -28077,7 +28077,7 @@
         <v>44354</v>
       </c>
       <c r="C392" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D392" t="inlineStr">
         <is>
@@ -28134,7 +28134,7 @@
         <v>44354</v>
       </c>
       <c r="C393" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D393" t="inlineStr">
         <is>
@@ -28191,7 +28191,7 @@
         <v>44361</v>
       </c>
       <c r="C394" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D394" t="inlineStr">
         <is>
@@ -28248,7 +28248,7 @@
         <v>44365</v>
       </c>
       <c r="C395" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D395" t="inlineStr">
         <is>
@@ -28310,7 +28310,7 @@
         <v>44365</v>
       </c>
       <c r="C396" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D396" t="inlineStr">
         <is>
@@ -28372,7 +28372,7 @@
         <v>44368</v>
       </c>
       <c r="C397" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D397" t="inlineStr">
         <is>
@@ -28429,7 +28429,7 @@
         <v>44371</v>
       </c>
       <c r="C398" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D398" t="inlineStr">
         <is>
@@ -28491,7 +28491,7 @@
         <v>44376</v>
       </c>
       <c r="C399" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D399" t="inlineStr">
         <is>
@@ -28553,7 +28553,7 @@
         <v>44376</v>
       </c>
       <c r="C400" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D400" t="inlineStr">
         <is>
@@ -28615,7 +28615,7 @@
         <v>44376</v>
       </c>
       <c r="C401" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D401" t="inlineStr">
         <is>
@@ -28672,7 +28672,7 @@
         <v>44376</v>
       </c>
       <c r="C402" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D402" t="inlineStr">
         <is>
@@ -28729,7 +28729,7 @@
         <v>44377</v>
       </c>
       <c r="C403" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D403" t="inlineStr">
         <is>
@@ -28791,7 +28791,7 @@
         <v>44406</v>
       </c>
       <c r="C404" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D404" t="inlineStr">
         <is>
@@ -28853,7 +28853,7 @@
         <v>44420</v>
       </c>
       <c r="C405" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D405" t="inlineStr">
         <is>
@@ -28910,7 +28910,7 @@
         <v>44425</v>
       </c>
       <c r="C406" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D406" t="inlineStr">
         <is>
@@ -28972,7 +28972,7 @@
         <v>44425</v>
       </c>
       <c r="C407" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D407" t="inlineStr">
         <is>
@@ -29034,7 +29034,7 @@
         <v>44425</v>
       </c>
       <c r="C408" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D408" t="inlineStr">
         <is>
@@ -29096,7 +29096,7 @@
         <v>44425</v>
       </c>
       <c r="C409" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D409" t="inlineStr">
         <is>
@@ -29158,7 +29158,7 @@
         <v>44432</v>
       </c>
       <c r="C410" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D410" t="inlineStr">
         <is>
@@ -29215,7 +29215,7 @@
         <v>44450</v>
       </c>
       <c r="C411" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D411" t="inlineStr">
         <is>
@@ -29272,7 +29272,7 @@
         <v>44460</v>
       </c>
       <c r="C412" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D412" t="inlineStr">
         <is>
@@ -29329,7 +29329,7 @@
         <v>44461</v>
       </c>
       <c r="C413" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D413" t="inlineStr">
         <is>
@@ -29386,7 +29386,7 @@
         <v>44461</v>
       </c>
       <c r="C414" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D414" t="inlineStr">
         <is>
@@ -29443,7 +29443,7 @@
         <v>44462</v>
       </c>
       <c r="C415" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D415" t="inlineStr">
         <is>
@@ -29500,7 +29500,7 @@
         <v>44466</v>
       </c>
       <c r="C416" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D416" t="inlineStr">
         <is>
@@ -29557,7 +29557,7 @@
         <v>44466</v>
       </c>
       <c r="C417" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D417" t="inlineStr">
         <is>
@@ -29619,7 +29619,7 @@
         <v>44467</v>
       </c>
       <c r="C418" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D418" t="inlineStr">
         <is>
@@ -29676,7 +29676,7 @@
         <v>44476</v>
       </c>
       <c r="C419" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D419" t="inlineStr">
         <is>
@@ -29738,7 +29738,7 @@
         <v>44476</v>
       </c>
       <c r="C420" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D420" t="inlineStr">
         <is>
@@ -29800,7 +29800,7 @@
         <v>44482</v>
       </c>
       <c r="C421" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D421" t="inlineStr">
         <is>
@@ -29857,7 +29857,7 @@
         <v>44482</v>
       </c>
       <c r="C422" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D422" t="inlineStr">
         <is>
@@ -29919,7 +29919,7 @@
         <v>44488</v>
       </c>
       <c r="C423" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D423" t="inlineStr">
         <is>
@@ -29976,7 +29976,7 @@
         <v>44491</v>
       </c>
       <c r="C424" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D424" t="inlineStr">
         <is>
@@ -30038,7 +30038,7 @@
         <v>44491</v>
       </c>
       <c r="C425" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D425" t="inlineStr">
         <is>
@@ -30100,7 +30100,7 @@
         <v>44495</v>
       </c>
       <c r="C426" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D426" t="inlineStr">
         <is>
@@ -30162,7 +30162,7 @@
         <v>44496</v>
       </c>
       <c r="C427" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D427" t="inlineStr">
         <is>
@@ -30219,7 +30219,7 @@
         <v>44496</v>
       </c>
       <c r="C428" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D428" t="inlineStr">
         <is>
@@ -30276,7 +30276,7 @@
         <v>44498</v>
       </c>
       <c r="C429" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D429" t="inlineStr">
         <is>
@@ -30333,7 +30333,7 @@
         <v>44501</v>
       </c>
       <c r="C430" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D430" t="inlineStr">
         <is>
@@ -30395,7 +30395,7 @@
         <v>44501</v>
       </c>
       <c r="C431" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D431" t="inlineStr">
         <is>
@@ -30457,7 +30457,7 @@
         <v>44501</v>
       </c>
       <c r="C432" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D432" t="inlineStr">
         <is>
@@ -30519,7 +30519,7 @@
         <v>44504</v>
       </c>
       <c r="C433" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D433" t="inlineStr">
         <is>
@@ -30581,7 +30581,7 @@
         <v>44504</v>
       </c>
       <c r="C434" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D434" t="inlineStr">
         <is>
@@ -30638,7 +30638,7 @@
         <v>44511</v>
       </c>
       <c r="C435" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D435" t="inlineStr">
         <is>
@@ -30695,7 +30695,7 @@
         <v>44512</v>
       </c>
       <c r="C436" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D436" t="inlineStr">
         <is>
@@ -30752,7 +30752,7 @@
         <v>44512</v>
       </c>
       <c r="C437" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D437" t="inlineStr">
         <is>
@@ -30809,7 +30809,7 @@
         <v>44512</v>
       </c>
       <c r="C438" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D438" t="inlineStr">
         <is>
@@ -30866,7 +30866,7 @@
         <v>44515</v>
       </c>
       <c r="C439" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D439" t="inlineStr">
         <is>
@@ -30928,7 +30928,7 @@
         <v>44515</v>
       </c>
       <c r="C440" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D440" t="inlineStr">
         <is>
@@ -30990,7 +30990,7 @@
         <v>44515</v>
       </c>
       <c r="C441" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D441" t="inlineStr">
         <is>
@@ -31052,7 +31052,7 @@
         <v>44515</v>
       </c>
       <c r="C442" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D442" t="inlineStr">
         <is>
@@ -31114,7 +31114,7 @@
         <v>44519</v>
       </c>
       <c r="C443" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D443" t="inlineStr">
         <is>
@@ -31176,7 +31176,7 @@
         <v>44522</v>
       </c>
       <c r="C444" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D444" t="inlineStr">
         <is>
@@ -31233,7 +31233,7 @@
         <v>44522</v>
       </c>
       <c r="C445" s="1" t="n">
-        <v>45352</v>
+        <v>45353</v>
       </c>
       <c r="D445" t="inlineStr">
  